--- a/Taller_final.xlsx
+++ b/Taller_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eafit-my.sharepoint.com/personal/darmendar_eafit_edu_co/Documents/MAF/Finanzas Corporativas/Taller final/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidarmendariz/finanzas-corporativas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="764" documentId="13_ncr:1_{9A198AE5-DFB1-4B20-96FE-55380C251E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30E17729-1738-0C4A-8CDA-E2F8C3AA2AFC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BC65EF-C6ED-C344-8350-33BA99DCCD94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20240" firstSheet="1" activeTab="10" xr2:uid="{4A5FEAB5-AF17-D144-BB0B-4790A386B114}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20240" activeTab="10" xr2:uid="{4A5FEAB5-AF17-D144-BB0B-4790A386B114}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="2" r:id="rId1"/>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2352,14 +2352,12 @@
     <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="42" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="20" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2375,12 +2373,14 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="20" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma" xfId="6" builtinId="3"/>
@@ -2645,34 +2645,34 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-2195711924.9955101</c:v>
+                  <c:v>-1793478653.7849333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5414741026.4728117</c:v>
+                  <c:v>6862201586.9203444</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7106394547.2652617</c:v>
+                  <c:v>8683790747.3030453</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9005404496.5502529</c:v>
+                  <c:v>10720217143.950525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11137745768.895601</c:v>
+                  <c:v>12998272906.196072</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13529006405.409296</c:v>
+                  <c:v>15543929387.198647</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>16182203815.408293</c:v>
+                  <c:v>18357655711.156792</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19172528835.372379</c:v>
+                  <c:v>21520522347.328396</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>22565041869.693596</c:v>
+                  <c:v>25100818510.761791</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>26394705688.86586</c:v>
+                  <c:v>29132766304.14537</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3062,34 +3062,34 @@
                 <c:formatCode>0.0\x</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>8.1286530415287981</c:v>
+                  <c:v>14.96471979451398</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>65.838542427979178</c:v>
+                  <c:v>78.617761323886896</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>87.755807934357804</c:v>
+                  <c:v>103.29684494837487</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>117.63261973378687</c:v>
+                  <c:v>136.743255629239</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>159.3923777326539</c:v>
+                  <c:v>183.25666315287984</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>219.7438275785882</c:v>
+                  <c:v>250.18309750589123</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>310.80697237045035</c:v>
+                  <c:v>350.77714791932891</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>459.6738798683748</c:v>
+                  <c:v>514.71499066288914</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>734.41710270278793</c:v>
+                  <c:v>816.50516372521986</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1779.915399049032</c:v>
+                  <c:v>1966.0518176842911</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3471,34 +3471,34 @@
                 <c:formatCode>0.0\x</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.80895198682443781</c:v>
+                  <c:v>1.0653044900613822</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.494236405247559</c:v>
+                  <c:v>5.1106863155835649</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.2644910722477762</c:v>
+                  <c:v>4.9224288924288082</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.3754789785983643</c:v>
+                  <c:v>6.1481050730758042</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.7938153926541371</c:v>
+                  <c:v>7.705310216552598</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.6208663706453592</c:v>
+                  <c:v>9.7025466023144791</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.98309772194906</c:v>
+                  <c:v>12.274503363325364</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>14.13850832497668</c:v>
+                  <c:v>15.697996625822482</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>18.450503419735949</c:v>
+                  <c:v>20.362159977095107</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>14.502165921754102</c:v>
+                  <c:v>15.915731551638485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3885,31 +3885,31 @@
                 <c:formatCode>0.0\x</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>5.550966462910953</c:v>
+                  <c:v>3.9749201466934818</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6340329887364039</c:v>
+                  <c:v>0.53682484210639336</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.477059962457897</c:v>
+                  <c:v>0.40877809883829974</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.35539875043134411</c:v>
+                  <c:v>0.30780934218288158</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.26064928638597801</c:v>
+                  <c:v>0.22793441779244636</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1866872178843462</c:v>
+                  <c:v>0.16468568885592963</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.12906548119843894</c:v>
+                  <c:v>0.11476053772556309</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.3859490787008661E-2</c:v>
+                  <c:v>7.5105725861286693E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.8497304908023432E-2</c:v>
+                  <c:v>4.3723075514740542E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -4292,34 +4292,34 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>3.5552954778061065E-2</c:v>
+                  <c:v>6.5754886223256911E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.81189287854670089</c:v>
+                  <c:v>0.9935691448714028</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1509994165403077</c:v>
+                  <c:v>1.398696739354045</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.6980512719201346</c:v>
+                  <c:v>2.0614052039292154</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.6965970399616053</c:v>
+                  <c:v>3.305657344133226</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.0051666692588759</c:v>
+                  <c:v>6.3788967054391819</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15.230378912991371</c:v>
+                  <c:v>24.60250191963048</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-24.269563097624886</c:v>
+                  <c:v>-18.779593361439836</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-7.8931985349709581</c:v>
+                  <c:v>-7.7266983681312933</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-5.1322792624758007</c:v>
+                  <c:v>-5.2365998091655221</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4692,34 +4692,34 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1513250000</c:v>
+                  <c:v>2113250000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11923669800</c:v>
+                  <c:v>14082805800</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14086279564.056005</c:v>
+                  <c:v>16439236884.504004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16544796493.694756</c:v>
+                  <c:v>19102734044.070896</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19336327637.347153</c:v>
+                  <c:v>22111623373.128967</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22497523116.991997</c:v>
+                  <c:v>25503126769.407661</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>26033296965.235657</c:v>
+                  <c:v>29278357060.639275</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>30050265943.069538</c:v>
+                  <c:v>33552701489.819916</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>34641100225.799545</c:v>
+                  <c:v>38423646557.836823</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>39855490867.963867</c:v>
+                  <c:v>43939778486.000443</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5095,34 +5095,34 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-156488080.83863837</c:v>
+                  <c:v>-216488080.83863842</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-3494649548.1143785</c:v>
+                  <c:v>-3710563148.114378</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-4097371420.9662528</c:v>
+                  <c:v>-4332667153.0110521</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4773745405.0413704</c:v>
+                  <c:v>-5029539160.0789814</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-5532871174.7724819</c:v>
+                  <c:v>-5810400748.3506641</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-6383407714.9464569</c:v>
+                  <c:v>-6683968080.1880207</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-7324488314.407423</c:v>
+                  <c:v>-7648994323.9477835</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-8385001117.956502</c:v>
+                  <c:v>-8735244672.6315422</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-9588610068.1000595</c:v>
+                  <c:v>-9966864701.3037872</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-10948379136.027424</c:v>
+                  <c:v>-11356807897.831085</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5510,34 +5510,34 @@
                 <c:formatCode>0.0\x</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-9.6700655531738402</c:v>
+                  <c:v>-9.7615073855965875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-3.411978693667209</c:v>
+                  <c:v>-3.7953284280194919</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-3.4378820265052132</c:v>
+                  <c:v>-3.794253355713999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-3.4657894566858189</c:v>
+                  <c:v>-3.7981082234522097</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-3.4948089385331271</c:v>
+                  <c:v>-3.8055246670215572</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-3.5243750864158465</c:v>
+                  <c:v>-3.8155668105300493</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-3.554281998652058</c:v>
+                  <c:v>-3.827739415229189</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-3.5838117992276488</c:v>
+                  <c:v>-3.8410717440971203</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-3.612734273244206</c:v>
+                  <c:v>-3.8551387732604159</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-3.6403097091160173</c:v>
+                  <c:v>-3.8690254234547745</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5919,34 +5919,34 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.15520512820512822</c:v>
+                  <c:v>0.21674358974358973</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.32701741654571842</c:v>
+                  <c:v>0.38623367198838898</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.34112810471835048</c:v>
+                  <c:v>0.39810978448393902</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.35465088371867143</c:v>
+                  <c:v>0.40948231141763392</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.36761107636676876</c:v>
+                  <c:v>0.42037339358652531</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3800328723064087</c:v>
+                  <c:v>0.43080415868768379</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.39193938081913327</c:v>
+                  <c:v>0.44079476960111491</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.40335268107635375</c:v>
+                  <c:v>0.45036447028165705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.4142938699583239</c:v>
+                  <c:v>0.45953162938229491</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.42478310756219528</c:v>
+                  <c:v>0.46831378172488458</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6334,34 +6334,34 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.60653846153846158</c:v>
+                  <c:v>0.66807692307692312</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.64021044992743104</c:v>
+                  <c:v>0.69942670537010154</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.65187624941807931</c:v>
+                  <c:v>0.70885792918366786</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.66309252966181187</c:v>
+                  <c:v>0.7179239573607743</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6738767800867127</c:v>
+                  <c:v>0.72663909730646925</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.68424580034409155</c:v>
+                  <c:v>0.7350170867253667</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.69421572802449438</c:v>
+                  <c:v>0.74307111680647608</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.70380206523235489</c:v>
+                  <c:v>0.75081385443765813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.71301970406775894</c:v>
+                  <c:v>0.75825746349172995</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.72188295106166223</c:v>
+                  <c:v>0.76541362522435141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6743,34 +6743,34 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>7.3174358974358977E-2</c:v>
+                  <c:v>0.13471282051282052</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.30508217897705769</c:v>
+                  <c:v>0.3642984344197282</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.32175930993381924</c:v>
+                  <c:v>0.37874098969940778</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.33750653401897623</c:v>
+                  <c:v>0.39233796171793872</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.35240574139353087</c:v>
+                  <c:v>0.40516805861328742</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.36652248319868075</c:v>
+                  <c:v>0.4172937695799559</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.37989814312274206</c:v>
+                  <c:v>0.42875353190472371</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.39261728609063085</c:v>
+                  <c:v>0.43962907529593415</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.40472857800648554</c:v>
+                  <c:v>0.4499663374304565</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.4162587732225741</c:v>
+                  <c:v>0.45978944738526339</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7157,34 +7157,34 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-1.6050059573193678E-2</c:v>
+                  <c:v>-2.2203905727039838E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-9.5843921051640191E-2</c:v>
+                  <c:v>-0.10176554659590724</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-9.9226239320703222E-2</c:v>
+                  <c:v>-0.10492440729726207</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.10232903300993026</c:v>
+                  <c:v>-0.10781217577982644</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.10518774640683672</c:v>
+                  <c:v>-0.11046397812881238</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.10782986004275938</c:v>
+                  <c:v>-0.11290698868088685</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.11027244911005209</c:v>
+                  <c:v>-0.11515798798825023</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.11254851082394469</c:v>
+                  <c:v>-0.11724968974447506</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.11467598738898983</c:v>
+                  <c:v>-0.11919976333138693</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.11668872747240676</c:v>
+                  <c:v>-0.12104179488867572</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14756,10 +14756,10 @@
       <c r="H2" s="26"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="159" t="s">
+      <c r="B3" s="157" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="159"/>
+      <c r="C3" s="157"/>
       <c r="H3" s="26"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
@@ -14978,7 +14978,7 @@
       <c r="D20" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="160" t="s">
+      <c r="E20" s="158" t="s">
         <v>30</v>
       </c>
     </row>
@@ -14992,7 +14992,7 @@
       <c r="D21" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="160"/>
+      <c r="E21" s="158"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
@@ -15004,7 +15004,7 @@
       <c r="D22" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="160"/>
+      <c r="E22" s="158"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
@@ -15013,7 +15013,7 @@
       <c r="C23" s="10">
         <v>0.02</v>
       </c>
-      <c r="E23" s="160"/>
+      <c r="E23" s="158"/>
     </row>
     <row r="24" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
@@ -15039,7 +15039,7 @@
       <c r="D25" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="160" t="s">
+      <c r="E25" s="158" t="s">
         <v>41</v>
       </c>
     </row>
@@ -15053,7 +15053,7 @@
       <c r="D26" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="160"/>
+      <c r="E26" s="158"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
@@ -15065,17 +15065,17 @@
       <c r="D27" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="160"/>
+      <c r="E27" s="158"/>
     </row>
     <row r="28" spans="2:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="164">
+      <c r="C28" s="153">
         <v>30</v>
       </c>
       <c r="D28" s="39"/>
-      <c r="E28" s="160" t="s">
+      <c r="E28" s="158" t="s">
         <v>46</v>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
         <v>90</v>
       </c>
       <c r="D29" s="39"/>
-      <c r="E29" s="160"/>
+      <c r="E29" s="158"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
@@ -15099,7 +15099,7 @@
       <c r="D30" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="160"/>
+      <c r="E30" s="158"/>
     </row>
     <row r="31" spans="2:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
@@ -15109,7 +15109,7 @@
         <v>0.06</v>
       </c>
       <c r="D31" s="11"/>
-      <c r="E31" s="160"/>
+      <c r="E31" s="158"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
@@ -15121,7 +15121,7 @@
       <c r="D32" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="160"/>
+      <c r="E32" s="158"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
@@ -15131,7 +15131,7 @@
         <v>0.02</v>
       </c>
       <c r="D33" s="39"/>
-      <c r="E33" s="160"/>
+      <c r="E33" s="158"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
@@ -15143,7 +15143,7 @@
       <c r="D34" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="160"/>
+      <c r="E34" s="158"/>
     </row>
     <row r="35" spans="2:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
@@ -15155,7 +15155,7 @@
       <c r="D35" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="160"/>
+      <c r="E35" s="158"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
@@ -15616,44 +15616,44 @@
       </c>
       <c r="C9" s="135"/>
       <c r="D9" s="112">
-        <f>2000000</f>
-        <v>2000000</v>
+        <f>Datos!C22</f>
+        <v>1600000</v>
       </c>
       <c r="E9" s="112">
         <f>D9*(1+D4)*(1+Datos!$C$23)</f>
-        <v>2159136</v>
+        <v>1727308.8</v>
       </c>
       <c r="F9" s="112">
         <f>E9*(1+E4)*(1+Datos!$C$23)</f>
-        <v>2352957.320448</v>
+        <v>1882365.8563584001</v>
       </c>
       <c r="G9" s="112">
         <f>F9*(1+F4)*(1+Datos!$C$23)</f>
-        <v>2557937.550376148</v>
+        <v>2046350.0403009185</v>
       </c>
       <c r="H9" s="112">
         <f>G9*(1+G4)*(1+Datos!$C$23)</f>
-        <v>2775295.7357818112</v>
+        <v>2220236.5886254488</v>
       </c>
       <c r="I9" s="112">
         <f>H9*(1+H4)*(1+Datos!$C$23)</f>
-        <v>3005603.6524156649</v>
+        <v>2404482.9219325315</v>
       </c>
       <c r="J9" s="112">
         <f>I9*(1+I4)*(1+Datos!$C$23)</f>
-        <v>3245060.095403621</v>
+        <v>2596048.0763228964</v>
       </c>
       <c r="K9" s="112">
         <f>J9*(1+J4)*(1+Datos!$C$23)</f>
-        <v>3502435.5467503686</v>
+        <v>2801948.437400294</v>
       </c>
       <c r="L9" s="112">
         <f>K9*(1+K4)*(1+Datos!$C$23)</f>
-        <v>3782546.3320372761</v>
+        <v>3026037.0656298199</v>
       </c>
       <c r="M9" s="112">
         <f>L9*(1+L4)*(1+Datos!$C$23)</f>
-        <v>4084287.6180365537</v>
+        <v>3267430.094429242</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="13" x14ac:dyDescent="0.15">
@@ -15821,50 +15821,50 @@
     <row r="16" spans="1:14" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="110">
         <f t="shared" ref="A16:A37" si="1">D16/$D$15</f>
-        <v>0.30769230769230771</v>
+        <v>0.24615384615384617</v>
       </c>
       <c r="B16" s="122" t="s">
         <v>307</v>
       </c>
       <c r="D16" s="112">
         <f>D9*D10</f>
-        <v>3000000000</v>
+        <v>2400000000</v>
       </c>
       <c r="E16" s="112">
         <f t="shared" ref="E16:M16" si="2">E9*E10</f>
-        <v>10795680000</v>
+        <v>8636544000</v>
       </c>
       <c r="F16" s="112">
         <f t="shared" si="2"/>
-        <v>11764786602.24</v>
+        <v>9411829281.7919998</v>
       </c>
       <c r="G16" s="112">
         <f t="shared" si="2"/>
-        <v>12789687751.880739</v>
+        <v>10231750201.504593</v>
       </c>
       <c r="H16" s="112">
         <f t="shared" si="2"/>
-        <v>13876478678.909056</v>
+        <v>11101182943.127243</v>
       </c>
       <c r="I16" s="112">
         <f t="shared" si="2"/>
-        <v>15028018262.078325</v>
+        <v>12022414609.662657</v>
       </c>
       <c r="J16" s="112">
         <f t="shared" si="2"/>
-        <v>16225300477.018105</v>
+        <v>12980240381.614483</v>
       </c>
       <c r="K16" s="112">
         <f t="shared" si="2"/>
-        <v>17512177733.751842</v>
+        <v>14009742187.001471</v>
       </c>
       <c r="L16" s="112">
         <f t="shared" si="2"/>
-        <v>18912731660.186382</v>
+        <v>15130185328.149099</v>
       </c>
       <c r="M16" s="112">
         <f t="shared" si="2"/>
-        <v>20421438090.18277</v>
+        <v>16337150472.14621</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="13" x14ac:dyDescent="0.15">
@@ -15968,7 +15968,7 @@
     <row r="19" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A19" s="110">
         <f t="shared" si="1"/>
-        <v>0.60653846153846158</v>
+        <v>0.66807692307692312</v>
       </c>
       <c r="B19" s="124" t="s">
         <v>310</v>
@@ -15976,43 +15976,43 @@
       <c r="C19" s="107"/>
       <c r="D19" s="120">
         <f>D15-D16-D17-D18</f>
-        <v>5913750000</v>
+        <v>6513750000</v>
       </c>
       <c r="E19" s="120">
         <f t="shared" ref="E19:M19" si="4">E15-E16-E17-E18</f>
-        <v>23343276600</v>
+        <v>25502412600</v>
       </c>
       <c r="F19" s="120">
         <f t="shared" si="4"/>
-        <v>26918072605.166405</v>
+        <v>29271029925.614403</v>
       </c>
       <c r="G19" s="120">
         <f t="shared" si="4"/>
-        <v>30933888687.125103</v>
+        <v>33491826237.501244</v>
       </c>
       <c r="H19" s="120">
         <f t="shared" si="4"/>
-        <v>35445891173.194046</v>
+        <v>38221186908.975861</v>
       </c>
       <c r="I19" s="120">
         <f t="shared" si="4"/>
-        <v>40506589910.29155</v>
+        <v>43512193562.707214</v>
       </c>
       <c r="J19" s="120">
         <f t="shared" si="4"/>
-        <v>46111018922.946358</v>
+        <v>49356079018.349976</v>
       </c>
       <c r="K19" s="120">
         <f t="shared" si="4"/>
-        <v>52434110949.941345</v>
+        <v>55936546496.691719</v>
       </c>
       <c r="L19" s="120">
         <f t="shared" si="4"/>
-        <v>59619001927.462395</v>
+        <v>63401548259.49968</v>
       </c>
       <c r="M19" s="120">
         <f t="shared" si="4"/>
-        <v>67731034618.800926</v>
+        <v>71815322236.837494</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="13" x14ac:dyDescent="0.15">
@@ -16294,7 +16294,7 @@
     <row r="26" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A26" s="110">
         <f t="shared" si="1"/>
-        <v>7.3174358974358977E-2</v>
+        <v>0.13471282051282052</v>
       </c>
       <c r="B26" s="124" t="s">
         <v>314</v>
@@ -16302,43 +16302,43 @@
       <c r="C26" s="107"/>
       <c r="D26" s="120">
         <f>D19-D20-D21-D22-D23-D24-D25</f>
-        <v>713450000</v>
+        <v>1313450000</v>
       </c>
       <c r="E26" s="120">
         <f t="shared" ref="E26:M26" si="6">E19-E20-E21-E22-E23-E24</f>
-        <v>11123869800</v>
+        <v>13283005800</v>
       </c>
       <c r="F26" s="120">
         <f t="shared" si="6"/>
-        <v>13286479564.056005</v>
+        <v>15639436884.504004</v>
       </c>
       <c r="G26" s="120">
         <f t="shared" si="6"/>
-        <v>15744996493.694756</v>
+        <v>18302934044.070896</v>
       </c>
       <c r="H26" s="120">
         <f t="shared" si="6"/>
-        <v>18536527637.347153</v>
+        <v>21311823373.128967</v>
       </c>
       <c r="I26" s="120">
         <f t="shared" si="6"/>
-        <v>21697723116.991997</v>
+        <v>24703326769.407661</v>
       </c>
       <c r="J26" s="120">
         <f t="shared" si="6"/>
-        <v>25233496965.235657</v>
+        <v>28478557060.639275</v>
       </c>
       <c r="K26" s="120">
         <f t="shared" si="6"/>
-        <v>29250465943.069538</v>
+        <v>32752901489.819916</v>
       </c>
       <c r="L26" s="120">
         <f t="shared" si="6"/>
-        <v>33841300225.799545</v>
+        <v>37623846557.836823</v>
       </c>
       <c r="M26" s="120">
         <f t="shared" si="6"/>
-        <v>39055690867.963867</v>
+        <v>43139978486.000443</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="13" x14ac:dyDescent="0.15">
@@ -16384,7 +16384,7 @@
     <row r="28" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A28" s="110">
         <f t="shared" si="1"/>
-        <v>6.4172331381285974E-2</v>
+        <v>0.12571079291974752</v>
       </c>
       <c r="B28" s="124" t="s">
         <v>316</v>
@@ -16392,98 +16392,98 @@
       <c r="C28" s="107"/>
       <c r="D28" s="120">
         <f>D26-D27</f>
-        <v>625680230.96753824</v>
+        <v>1225680230.9675384</v>
       </c>
       <c r="E28" s="120">
         <f t="shared" ref="E28:M28" si="7">E26-E27</f>
-        <v>10954912994.612511</v>
+        <v>13114048994.612511</v>
       </c>
       <c r="F28" s="120">
         <f t="shared" si="7"/>
-        <v>13135076712.47501</v>
+        <v>15488034032.923008</v>
       </c>
       <c r="G28" s="120">
         <f t="shared" si="7"/>
-        <v>15611147595.920252</v>
+        <v>18169085146.296391</v>
       </c>
       <c r="H28" s="120">
         <f t="shared" si="7"/>
-        <v>18420232693.379143</v>
+        <v>21195528429.160957</v>
       </c>
       <c r="I28" s="120">
         <f t="shared" si="7"/>
-        <v>21598982126.830479</v>
+        <v>24604585779.246143</v>
       </c>
       <c r="J28" s="120">
         <f t="shared" si="7"/>
-        <v>25152309928.88063</v>
+        <v>28397370024.284248</v>
       </c>
       <c r="K28" s="120">
         <f t="shared" si="7"/>
-        <v>29186832860.521004</v>
+        <v>32689268407.271381</v>
       </c>
       <c r="L28" s="120">
         <f t="shared" si="7"/>
-        <v>33795221097.057503</v>
+        <v>37577767429.09478</v>
       </c>
       <c r="M28" s="120">
         <f t="shared" si="7"/>
-        <v>39033748425.70575</v>
+        <v>43118036043.742325</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A29" s="110">
         <f t="shared" si="1"/>
-        <v>2.246031598345009E-2</v>
+        <v>4.3998777521911635E-2</v>
       </c>
       <c r="B29" s="122" t="s">
         <v>317</v>
       </c>
       <c r="D29" s="112">
         <f t="shared" ref="D29:M29" si="8">IF(D28&lt;0,0,D28*D5)</f>
-        <v>218988080.83863837</v>
+        <v>428988080.83863842</v>
       </c>
       <c r="E29" s="112">
         <f t="shared" si="8"/>
-        <v>3834219548.1143785</v>
+        <v>4589917148.114378</v>
       </c>
       <c r="F29" s="112">
         <f t="shared" si="8"/>
-        <v>4597276849.3662529</v>
+        <v>5420811911.5230522</v>
       </c>
       <c r="G29" s="112">
         <f t="shared" si="8"/>
-        <v>5463901658.5720882</v>
+        <v>6359179801.2037363</v>
       </c>
       <c r="H29" s="112">
         <f t="shared" si="8"/>
-        <v>6447081442.6826992</v>
+        <v>7418434950.2063351</v>
       </c>
       <c r="I29" s="112">
         <f t="shared" si="8"/>
-        <v>7559643744.390667</v>
+        <v>8611605022.7361488</v>
       </c>
       <c r="J29" s="112">
         <f t="shared" si="8"/>
-        <v>8803308475.1082211</v>
+        <v>9939079508.4994869</v>
       </c>
       <c r="K29" s="112">
         <f t="shared" si="8"/>
-        <v>10215391501.18235</v>
+        <v>11441243942.544983</v>
       </c>
       <c r="L29" s="112">
         <f t="shared" si="8"/>
-        <v>11828327383.970125</v>
+        <v>13152218600.183172</v>
       </c>
       <c r="M29" s="112">
         <f t="shared" si="8"/>
-        <v>13661811948.997011</v>
+        <v>15091312615.309813</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A30" s="110">
         <f t="shared" si="1"/>
-        <v>4.1712015397835887E-2</v>
+        <v>8.1712015397835888E-2</v>
       </c>
       <c r="B30" s="124" t="s">
         <v>318</v>
@@ -16491,43 +16491,43 @@
       <c r="C30" s="107"/>
       <c r="D30" s="120">
         <f>D28-D29</f>
-        <v>406692150.12889987</v>
+        <v>796692150.12889993</v>
       </c>
       <c r="E30" s="120">
         <f t="shared" ref="E30:M30" si="9">E28-E29</f>
-        <v>7120693446.4981327</v>
+        <v>8524131846.4981327</v>
       </c>
       <c r="F30" s="120">
         <f t="shared" si="9"/>
-        <v>8537799863.108757</v>
+        <v>10067222121.399956</v>
       </c>
       <c r="G30" s="120">
         <f t="shared" si="9"/>
-        <v>10147245937.348164</v>
+        <v>11809905345.092655</v>
       </c>
       <c r="H30" s="120">
         <f t="shared" si="9"/>
-        <v>11973151250.696444</v>
+        <v>13777093478.954622</v>
       </c>
       <c r="I30" s="120">
         <f t="shared" si="9"/>
-        <v>14039338382.439812</v>
+        <v>15992980756.509995</v>
       </c>
       <c r="J30" s="120">
         <f t="shared" si="9"/>
-        <v>16349001453.772409</v>
+        <v>18458290515.78476</v>
       </c>
       <c r="K30" s="120">
         <f t="shared" si="9"/>
-        <v>18971441359.338654</v>
+        <v>21248024464.726398</v>
       </c>
       <c r="L30" s="120">
         <f t="shared" si="9"/>
-        <v>21966893713.087379</v>
+        <v>24425548828.911606</v>
       </c>
       <c r="M30" s="120">
         <f t="shared" si="9"/>
-        <v>25371936476.70874</v>
+        <v>28026723428.43251</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.15">
@@ -16551,43 +16551,43 @@
       <c r="C32" s="107"/>
       <c r="D32" s="120">
         <f t="shared" ref="D32:M32" si="10">D26+D22+D23</f>
-        <v>1513250000</v>
+        <v>2113250000</v>
       </c>
       <c r="E32" s="120">
         <f t="shared" si="10"/>
-        <v>11923669800</v>
+        <v>14082805800</v>
       </c>
       <c r="F32" s="120">
         <f t="shared" si="10"/>
-        <v>14086279564.056005</v>
+        <v>16439236884.504004</v>
       </c>
       <c r="G32" s="120">
         <f t="shared" si="10"/>
-        <v>16544796493.694756</v>
+        <v>19102734044.070896</v>
       </c>
       <c r="H32" s="120">
         <f t="shared" si="10"/>
-        <v>19336327637.347153</v>
+        <v>22111623373.128967</v>
       </c>
       <c r="I32" s="120">
         <f t="shared" si="10"/>
-        <v>22497523116.991997</v>
+        <v>25503126769.407661</v>
       </c>
       <c r="J32" s="120">
         <f t="shared" si="10"/>
-        <v>26033296965.235657</v>
+        <v>29278357060.639275</v>
       </c>
       <c r="K32" s="120">
         <f t="shared" si="10"/>
-        <v>30050265943.069538</v>
+        <v>33552701489.819916</v>
       </c>
       <c r="L32" s="120">
         <f t="shared" si="10"/>
-        <v>34641100225.799545</v>
+        <v>38423646557.836823</v>
       </c>
       <c r="M32" s="120">
         <f t="shared" si="10"/>
-        <v>39855490867.963867</v>
+        <v>43939778486.000443</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.15">
@@ -16692,99 +16692,99 @@
     <row r="36" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A36" s="110">
         <f t="shared" si="1"/>
-        <v>7.6923076923076927E-2</v>
+        <v>6.1538461538461542E-2</v>
       </c>
       <c r="B36" s="122" t="s">
         <v>322</v>
       </c>
       <c r="D36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!D16</f>
-        <v>750000000</v>
+        <v>600000000</v>
       </c>
       <c r="E36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!E16</f>
-        <v>2698920000</v>
+        <v>2159136000</v>
       </c>
       <c r="F36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!F16</f>
-        <v>2941196650.5599999</v>
+        <v>2352957320.448</v>
       </c>
       <c r="G36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!G16</f>
-        <v>3197421937.9701848</v>
+        <v>2557937550.3761482</v>
       </c>
       <c r="H36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!H16</f>
-        <v>3469119669.7272639</v>
+        <v>2775295735.7818108</v>
       </c>
       <c r="I36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!I16</f>
-        <v>3757004565.5195813</v>
+        <v>3005603652.4156642</v>
       </c>
       <c r="J36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!J16</f>
-        <v>4056325119.2545261</v>
+        <v>3245060095.4036207</v>
       </c>
       <c r="K36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!K16</f>
-        <v>4378044433.4379606</v>
+        <v>3502435546.7503676</v>
       </c>
       <c r="L36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!L16</f>
-        <v>4728182915.0465956</v>
+        <v>3782546332.0372748</v>
       </c>
       <c r="M36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!M16</f>
-        <v>5105359522.5456924</v>
+        <v>4084287618.0365524</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="110">
         <f t="shared" si="1"/>
-        <v>2.246031598345009E-2</v>
+        <v>4.3998777521911635E-2</v>
       </c>
       <c r="B37" s="122" t="s">
         <v>323</v>
       </c>
       <c r="D37" s="112">
         <f>D29</f>
-        <v>218988080.83863837</v>
+        <v>428988080.83863842</v>
       </c>
       <c r="E37" s="112">
         <f t="shared" ref="E37:M37" si="12">E29</f>
-        <v>3834219548.1143785</v>
+        <v>4589917148.114378</v>
       </c>
       <c r="F37" s="112">
         <f t="shared" si="12"/>
-        <v>4597276849.3662529</v>
+        <v>5420811911.5230522</v>
       </c>
       <c r="G37" s="112">
         <f t="shared" si="12"/>
-        <v>5463901658.5720882</v>
+        <v>6359179801.2037363</v>
       </c>
       <c r="H37" s="112">
         <f t="shared" si="12"/>
-        <v>6447081442.6826992</v>
+        <v>7418434950.2063351</v>
       </c>
       <c r="I37" s="112">
         <f t="shared" si="12"/>
-        <v>7559643744.390667</v>
+        <v>8611605022.7361488</v>
       </c>
       <c r="J37" s="112">
         <f t="shared" si="12"/>
-        <v>8803308475.1082211</v>
+        <v>9939079508.4994869</v>
       </c>
       <c r="K37" s="112">
         <f t="shared" si="12"/>
-        <v>10215391501.18235</v>
+        <v>11441243942.544983</v>
       </c>
       <c r="L37" s="112">
         <f t="shared" si="12"/>
-        <v>11828327383.970125</v>
+        <v>13152218600.183172</v>
       </c>
       <c r="M37" s="112">
         <f t="shared" si="12"/>
-        <v>13661811948.997011</v>
+        <v>15091312615.309813</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="13" x14ac:dyDescent="0.15">
@@ -16795,43 +16795,43 @@
       <c r="C38" s="107"/>
       <c r="D38" s="120">
         <f>D35-D36-D37</f>
-        <v>-156488080.83863837</v>
+        <v>-216488080.83863842</v>
       </c>
       <c r="E38" s="120">
         <f>E35-E36-E37</f>
-        <v>-3494649548.1143785</v>
+        <v>-3710563148.114378</v>
       </c>
       <c r="F38" s="120">
         <f t="shared" ref="F38:M38" si="13">F35-F36-F37</f>
-        <v>-4097371420.9662528</v>
+        <v>-4332667153.0110521</v>
       </c>
       <c r="G38" s="120">
         <f t="shared" si="13"/>
-        <v>-4773745405.0413704</v>
+        <v>-5029539160.0789814</v>
       </c>
       <c r="H38" s="120">
         <f t="shared" si="13"/>
-        <v>-5532871174.7724819</v>
+        <v>-5810400748.3506641</v>
       </c>
       <c r="I38" s="120">
         <f t="shared" si="13"/>
-        <v>-6383407714.9464569</v>
+        <v>-6683968080.1880207</v>
       </c>
       <c r="J38" s="120">
         <f t="shared" si="13"/>
-        <v>-7324488314.407423</v>
+        <v>-7648994323.9477835</v>
       </c>
       <c r="K38" s="120">
         <f t="shared" si="13"/>
-        <v>-8385001117.956502</v>
+        <v>-8735244672.6315422</v>
       </c>
       <c r="L38" s="120">
         <f t="shared" si="13"/>
-        <v>-9588610068.1000595</v>
+        <v>-9966864701.3037872</v>
       </c>
       <c r="M38" s="120">
         <f t="shared" si="13"/>
-        <v>-10948379136.027424</v>
+        <v>-11356807897.831085</v>
       </c>
       <c r="O38" s="108" t="s">
         <v>325</v>
@@ -16848,43 +16848,43 @@
       <c r="C39" s="107"/>
       <c r="D39" s="120">
         <f>D38</f>
-        <v>-156488080.83863837</v>
+        <v>-216488080.83863842</v>
       </c>
       <c r="E39" s="120">
         <f>E38-D38</f>
-        <v>-3338161467.2757401</v>
+        <v>-3494075067.2757397</v>
       </c>
       <c r="F39" s="120">
         <f t="shared" ref="F39:M39" si="14">F38-E38</f>
-        <v>-602721872.85187435</v>
+        <v>-622104004.89667416</v>
       </c>
       <c r="G39" s="120">
         <f t="shared" si="14"/>
-        <v>-676373984.07511759</v>
+        <v>-696872007.06792927</v>
       </c>
       <c r="H39" s="120">
         <f t="shared" si="14"/>
-        <v>-759125769.73111153</v>
+        <v>-780861588.27168274</v>
       </c>
       <c r="I39" s="120">
         <f t="shared" si="14"/>
-        <v>-850536540.17397499</v>
+        <v>-873567331.83735657</v>
       </c>
       <c r="J39" s="120">
         <f t="shared" si="14"/>
-        <v>-941080599.46096611</v>
+        <v>-965026243.75976276</v>
       </c>
       <c r="K39" s="120">
         <f t="shared" si="14"/>
-        <v>-1060512803.5490789</v>
+        <v>-1086250348.6837587</v>
       </c>
       <c r="L39" s="120">
         <f t="shared" si="14"/>
-        <v>-1203608950.1435575</v>
+        <v>-1231620028.672245</v>
       </c>
       <c r="M39" s="120">
         <f t="shared" si="14"/>
-        <v>-1359769067.9273643</v>
+        <v>-1389943196.527298</v>
       </c>
       <c r="O39" s="108" t="s">
         <v>327</v>
@@ -17100,43 +17100,43 @@
       <c r="C45" s="107"/>
       <c r="D45" s="120">
         <f>D43+D38</f>
-        <v>13043711919.161362</v>
+        <v>12983711919.161362</v>
       </c>
       <c r="E45" s="120">
         <f>E43+E38</f>
-        <v>8905750451.885622</v>
+        <v>8689836851.885622</v>
       </c>
       <c r="F45" s="120">
         <f t="shared" ref="F45:L45" si="18">F43+F38</f>
-        <v>7503228579.0337467</v>
+        <v>7267932846.9889479</v>
       </c>
       <c r="G45" s="120">
         <f t="shared" si="18"/>
-        <v>6027054594.9586296</v>
+        <v>5771260839.9210186</v>
       </c>
       <c r="H45" s="120">
         <f t="shared" si="18"/>
-        <v>4468128825.2275181</v>
+        <v>4190599251.6493359</v>
       </c>
       <c r="I45" s="120">
         <f t="shared" si="18"/>
-        <v>2817792285.0535431</v>
+        <v>2517231919.8119793</v>
       </c>
       <c r="J45" s="120">
         <f t="shared" si="18"/>
-        <v>1076911685.592577</v>
+        <v>752405676.05221653</v>
       </c>
       <c r="K45" s="120">
         <f t="shared" si="18"/>
-        <v>-783401117.95650196</v>
+        <v>-1133644672.6315422</v>
       </c>
       <c r="L45" s="120">
         <f t="shared" si="18"/>
-        <v>-2786810068.1000595</v>
+        <v>-3165064701.3037872</v>
       </c>
       <c r="M45" s="120">
         <f>M43+M38</f>
-        <v>-4946379136.0274239</v>
+        <v>-5354807897.8310852</v>
       </c>
       <c r="O45" s="108" t="s">
         <v>335</v>
@@ -17223,43 +17223,43 @@
       <c r="C49" s="112"/>
       <c r="D49" s="112">
         <f>D26</f>
-        <v>713450000</v>
+        <v>1313450000</v>
       </c>
       <c r="E49" s="112">
         <f t="shared" ref="E49:M49" si="19">E26</f>
-        <v>11123869800</v>
+        <v>13283005800</v>
       </c>
       <c r="F49" s="112">
         <f t="shared" si="19"/>
-        <v>13286479564.056005</v>
+        <v>15639436884.504004</v>
       </c>
       <c r="G49" s="112">
         <f t="shared" si="19"/>
-        <v>15744996493.694756</v>
+        <v>18302934044.070896</v>
       </c>
       <c r="H49" s="112">
         <f t="shared" si="19"/>
-        <v>18536527637.347153</v>
+        <v>21311823373.128967</v>
       </c>
       <c r="I49" s="112">
         <f t="shared" si="19"/>
-        <v>21697723116.991997</v>
+        <v>24703326769.407661</v>
       </c>
       <c r="J49" s="112">
         <f t="shared" si="19"/>
-        <v>25233496965.235657</v>
+        <v>28478557060.639275</v>
       </c>
       <c r="K49" s="112">
         <f t="shared" si="19"/>
-        <v>29250465943.069538</v>
+        <v>32752901489.819916</v>
       </c>
       <c r="L49" s="112">
         <f t="shared" si="19"/>
-        <v>33841300225.799545</v>
+        <v>37623846557.836823</v>
       </c>
       <c r="M49" s="112">
         <f t="shared" si="19"/>
-        <v>39055690867.963867</v>
+        <v>43139978486.000443</v>
       </c>
       <c r="O49" s="108" t="s">
         <v>339</v>
@@ -17276,43 +17276,43 @@
       <c r="C50" s="112"/>
       <c r="D50" s="112">
         <f t="shared" ref="D50:M50" si="20">IF(D49&lt;0,0,D49*D5)</f>
-        <v>249707499.99999997</v>
+        <v>459707500</v>
       </c>
       <c r="E50" s="112">
         <f t="shared" si="20"/>
-        <v>3893354429.9999995</v>
+        <v>4649052030</v>
       </c>
       <c r="F50" s="112">
         <f t="shared" si="20"/>
-        <v>4650267847.4196014</v>
+        <v>5473802909.5764008</v>
       </c>
       <c r="G50" s="112">
         <f t="shared" si="20"/>
-        <v>5510748772.7931643</v>
+        <v>6406026915.4248133</v>
       </c>
       <c r="H50" s="112">
         <f t="shared" si="20"/>
-        <v>6487784673.0715027</v>
+        <v>7459138180.5951385</v>
       </c>
       <c r="I50" s="112">
         <f t="shared" si="20"/>
-        <v>7594203090.9471979</v>
+        <v>8646164369.2926807</v>
       </c>
       <c r="J50" s="112">
         <f t="shared" si="20"/>
-        <v>8831723937.8324795</v>
+        <v>9967494971.2237453</v>
       </c>
       <c r="K50" s="112">
         <f t="shared" si="20"/>
-        <v>10237663080.074337</v>
+        <v>11463515521.43697</v>
       </c>
       <c r="L50" s="112">
         <f t="shared" si="20"/>
-        <v>11844455079.02984</v>
+        <v>13168346295.242887</v>
       </c>
       <c r="M50" s="112">
         <f t="shared" si="20"/>
-        <v>13669491803.787354</v>
+        <v>15098992470.100153</v>
       </c>
     </row>
     <row r="51" spans="2:16" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.15">
@@ -17322,43 +17322,43 @@
       <c r="C51" s="120"/>
       <c r="D51" s="120">
         <f>D49-D50</f>
-        <v>463742500</v>
+        <v>853742500</v>
       </c>
       <c r="E51" s="120">
         <f t="shared" ref="E51:M51" si="21">E49-E50</f>
-        <v>7230515370</v>
+        <v>8633953770</v>
       </c>
       <c r="F51" s="120">
         <f t="shared" si="21"/>
-        <v>8636211716.636404</v>
+        <v>10165633974.927603</v>
       </c>
       <c r="G51" s="120">
         <f t="shared" si="21"/>
-        <v>10234247720.901592</v>
+        <v>11896907128.646084</v>
       </c>
       <c r="H51" s="120">
         <f t="shared" si="21"/>
-        <v>12048742964.27565</v>
+        <v>13852685192.533829</v>
       </c>
       <c r="I51" s="120">
         <f t="shared" si="21"/>
-        <v>14103520026.0448</v>
+        <v>16057162400.114981</v>
       </c>
       <c r="J51" s="120">
         <f t="shared" si="21"/>
-        <v>16401773027.403177</v>
+        <v>18511062089.415527</v>
       </c>
       <c r="K51" s="120">
         <f t="shared" si="21"/>
-        <v>19012802862.995201</v>
+        <v>21289385968.382946</v>
       </c>
       <c r="L51" s="120">
         <f t="shared" si="21"/>
-        <v>21996845146.769707</v>
+        <v>24455500262.593933</v>
       </c>
       <c r="M51" s="120">
         <f t="shared" si="21"/>
-        <v>25386199064.176514</v>
+        <v>28040986015.900291</v>
       </c>
     </row>
     <row r="52" spans="2:16" ht="13" x14ac:dyDescent="0.15">
@@ -17424,43 +17424,43 @@
       <c r="C54" s="120"/>
       <c r="D54" s="120">
         <f t="shared" ref="D54:M54" si="22">D51+D52+D53</f>
-        <v>1263542500</v>
+        <v>1653542500</v>
       </c>
       <c r="E54" s="120">
         <f t="shared" si="22"/>
-        <v>8030315370</v>
+        <v>9433753770</v>
       </c>
       <c r="F54" s="120">
         <f t="shared" si="22"/>
-        <v>9436011716.636404</v>
+        <v>10965433974.927603</v>
       </c>
       <c r="G54" s="120">
         <f t="shared" si="22"/>
-        <v>11034047720.901592</v>
+        <v>12696707128.646084</v>
       </c>
       <c r="H54" s="120">
         <f t="shared" si="22"/>
-        <v>12848542964.27565</v>
+        <v>14652485192.533829</v>
       </c>
       <c r="I54" s="120">
         <f t="shared" si="22"/>
-        <v>14903320026.0448</v>
+        <v>16856962400.114981</v>
       </c>
       <c r="J54" s="120">
         <f t="shared" si="22"/>
-        <v>17201573027.403175</v>
+        <v>19310862089.415527</v>
       </c>
       <c r="K54" s="120">
         <f t="shared" si="22"/>
-        <v>19812602862.995201</v>
+        <v>22089185968.382946</v>
       </c>
       <c r="L54" s="120">
         <f t="shared" si="22"/>
-        <v>22796645146.769707</v>
+        <v>25255300262.593933</v>
       </c>
       <c r="M54" s="120">
         <f t="shared" si="22"/>
-        <v>26185999064.176514</v>
+        <v>28840786015.900291</v>
       </c>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.15">
@@ -17539,43 +17539,43 @@
       <c r="C58" s="107"/>
       <c r="D58" s="137">
         <f t="shared" ref="D58:M58" si="23">D32</f>
-        <v>1513250000</v>
+        <v>2113250000</v>
       </c>
       <c r="E58" s="137">
         <f t="shared" si="23"/>
-        <v>11923669800</v>
+        <v>14082805800</v>
       </c>
       <c r="F58" s="137">
         <f t="shared" si="23"/>
-        <v>14086279564.056005</v>
+        <v>16439236884.504004</v>
       </c>
       <c r="G58" s="137">
         <f t="shared" si="23"/>
-        <v>16544796493.694756</v>
+        <v>19102734044.070896</v>
       </c>
       <c r="H58" s="137">
         <f t="shared" si="23"/>
-        <v>19336327637.347153</v>
+        <v>22111623373.128967</v>
       </c>
       <c r="I58" s="137">
         <f t="shared" si="23"/>
-        <v>22497523116.991997</v>
+        <v>25503126769.407661</v>
       </c>
       <c r="J58" s="137">
         <f t="shared" si="23"/>
-        <v>26033296965.235657</v>
+        <v>29278357060.639275</v>
       </c>
       <c r="K58" s="137">
         <f t="shared" si="23"/>
-        <v>30050265943.069538</v>
+        <v>33552701489.819916</v>
       </c>
       <c r="L58" s="137">
         <f t="shared" si="23"/>
-        <v>34641100225.799545</v>
+        <v>38423646557.836823</v>
       </c>
       <c r="M58" s="137">
         <f t="shared" si="23"/>
-        <v>39855490867.963867</v>
+        <v>43939778486.000443</v>
       </c>
       <c r="N58" s="107"/>
     </row>
@@ -17586,43 +17586,43 @@
       <c r="C59" s="107"/>
       <c r="D59" s="137">
         <f t="shared" ref="D59:M59" si="24">D50</f>
-        <v>249707499.99999997</v>
+        <v>459707500</v>
       </c>
       <c r="E59" s="137">
         <f t="shared" si="24"/>
-        <v>3893354429.9999995</v>
+        <v>4649052030</v>
       </c>
       <c r="F59" s="137">
         <f t="shared" si="24"/>
-        <v>4650267847.4196014</v>
+        <v>5473802909.5764008</v>
       </c>
       <c r="G59" s="137">
         <f t="shared" si="24"/>
-        <v>5510748772.7931643</v>
+        <v>6406026915.4248133</v>
       </c>
       <c r="H59" s="137">
         <f t="shared" si="24"/>
-        <v>6487784673.0715027</v>
+        <v>7459138180.5951385</v>
       </c>
       <c r="I59" s="137">
         <f t="shared" si="24"/>
-        <v>7594203090.9471979</v>
+        <v>8646164369.2926807</v>
       </c>
       <c r="J59" s="137">
         <f t="shared" si="24"/>
-        <v>8831723937.8324795</v>
+        <v>9967494971.2237453</v>
       </c>
       <c r="K59" s="137">
         <f t="shared" si="24"/>
-        <v>10237663080.074337</v>
+        <v>11463515521.43697</v>
       </c>
       <c r="L59" s="137">
         <f t="shared" si="24"/>
-        <v>11844455079.02984</v>
+        <v>13168346295.242887</v>
       </c>
       <c r="M59" s="137">
         <f t="shared" si="24"/>
-        <v>13669491803.787354</v>
+        <v>15098992470.100153</v>
       </c>
       <c r="N59" s="107"/>
     </row>
@@ -17632,43 +17632,43 @@
       </c>
       <c r="D60" s="138">
         <f>D58-D59</f>
-        <v>1263542500</v>
+        <v>1653542500</v>
       </c>
       <c r="E60" s="138">
         <f t="shared" ref="E60:M60" si="25">E58-E59</f>
-        <v>8030315370</v>
+        <v>9433753770</v>
       </c>
       <c r="F60" s="138">
         <f t="shared" si="25"/>
-        <v>9436011716.636404</v>
+        <v>10965433974.927603</v>
       </c>
       <c r="G60" s="138">
         <f t="shared" si="25"/>
-        <v>11034047720.901592</v>
+        <v>12696707128.646084</v>
       </c>
       <c r="H60" s="138">
         <f t="shared" si="25"/>
-        <v>12848542964.27565</v>
+        <v>14652485192.533829</v>
       </c>
       <c r="I60" s="138">
         <f t="shared" si="25"/>
-        <v>14903320026.0448</v>
+        <v>16856962400.114981</v>
       </c>
       <c r="J60" s="138">
         <f t="shared" si="25"/>
-        <v>17201573027.403175</v>
+        <v>19310862089.415527</v>
       </c>
       <c r="K60" s="138">
         <f t="shared" si="25"/>
-        <v>19812602862.995201</v>
+        <v>22089185968.382946</v>
       </c>
       <c r="L60" s="138">
         <f t="shared" si="25"/>
-        <v>22796645146.769707</v>
+        <v>25255300262.593933</v>
       </c>
       <c r="M60" s="138">
         <f t="shared" si="25"/>
-        <v>26185999064.176514</v>
+        <v>28840786015.900291</v>
       </c>
     </row>
     <row r="61" spans="2:16" ht="13" x14ac:dyDescent="0.15">
@@ -17678,43 +17678,43 @@
       <c r="C61" s="112"/>
       <c r="D61" s="112">
         <f t="shared" ref="D61:M61" si="26">-D39</f>
-        <v>156488080.83863837</v>
+        <v>216488080.83863842</v>
       </c>
       <c r="E61" s="112">
         <f t="shared" si="26"/>
-        <v>3338161467.2757401</v>
+        <v>3494075067.2757397</v>
       </c>
       <c r="F61" s="112">
         <f t="shared" si="26"/>
-        <v>602721872.85187435</v>
+        <v>622104004.89667416</v>
       </c>
       <c r="G61" s="112">
         <f t="shared" si="26"/>
-        <v>676373984.07511759</v>
+        <v>696872007.06792927</v>
       </c>
       <c r="H61" s="112">
         <f t="shared" si="26"/>
-        <v>759125769.73111153</v>
+        <v>780861588.27168274</v>
       </c>
       <c r="I61" s="112">
         <f t="shared" si="26"/>
-        <v>850536540.17397499</v>
+        <v>873567331.83735657</v>
       </c>
       <c r="J61" s="112">
         <f t="shared" si="26"/>
-        <v>941080599.46096611</v>
+        <v>965026243.75976276</v>
       </c>
       <c r="K61" s="112">
         <f t="shared" si="26"/>
-        <v>1060512803.5490789</v>
+        <v>1086250348.6837587</v>
       </c>
       <c r="L61" s="112">
         <f t="shared" si="26"/>
-        <v>1203608950.1435575</v>
+        <v>1231620028.672245</v>
       </c>
       <c r="M61" s="112">
         <f t="shared" si="26"/>
-        <v>1359769067.9273643</v>
+        <v>1389943196.527298</v>
       </c>
     </row>
     <row r="62" spans="2:16" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.15">
@@ -17724,43 +17724,43 @@
       <c r="C62" s="120"/>
       <c r="D62" s="120">
         <f>D60+D61</f>
-        <v>1420030580.8386383</v>
+        <v>1870030580.8386383</v>
       </c>
       <c r="E62" s="120">
         <f>E54+E61</f>
-        <v>11368476837.27574</v>
+        <v>12927828837.27574</v>
       </c>
       <c r="F62" s="120">
         <f>F54+F61</f>
-        <v>10038733589.488277</v>
+        <v>11587537979.824276</v>
       </c>
       <c r="G62" s="120">
         <f>G54+G61</f>
-        <v>11710421704.976709</v>
+        <v>13393579135.714012</v>
       </c>
       <c r="H62" s="120">
         <f t="shared" ref="H62:M62" si="27">H54+H61</f>
-        <v>13607668734.006762</v>
+        <v>15433346780.805511</v>
       </c>
       <c r="I62" s="120">
         <f t="shared" si="27"/>
-        <v>15753856566.218775</v>
+        <v>17730529731.952339</v>
       </c>
       <c r="J62" s="120">
         <f t="shared" si="27"/>
-        <v>18142653626.864143</v>
+        <v>20275888333.175289</v>
       </c>
       <c r="K62" s="120">
         <f t="shared" si="27"/>
-        <v>20873115666.544281</v>
+        <v>23175436317.066704</v>
       </c>
       <c r="L62" s="120">
         <f t="shared" si="27"/>
-        <v>24000254096.913265</v>
+        <v>26486920291.266178</v>
       </c>
       <c r="M62" s="120">
         <f t="shared" si="27"/>
-        <v>27545768132.103878</v>
+        <v>30230729212.427589</v>
       </c>
     </row>
     <row r="63" spans="2:16" ht="13" x14ac:dyDescent="0.15">
@@ -17813,43 +17813,43 @@
       </c>
       <c r="D64" s="120">
         <f>D62+D63</f>
-        <v>1420030580.8386383</v>
+        <v>1870030580.8386383</v>
       </c>
       <c r="E64" s="120">
         <f t="shared" ref="E64:L64" si="28">E62+E63</f>
-        <v>11368476837.27574</v>
+        <v>12927828837.27574</v>
       </c>
       <c r="F64" s="120">
         <f>F62+F63</f>
-        <v>10038733589.488277</v>
+        <v>11587537979.824276</v>
       </c>
       <c r="G64" s="120">
         <f>G62+G63</f>
-        <v>11710421704.976709</v>
+        <v>13393579135.714012</v>
       </c>
       <c r="H64" s="120">
         <f>H62+H63</f>
-        <v>3807668734.0067616</v>
+        <v>5633346780.8055115</v>
       </c>
       <c r="I64" s="120">
         <f t="shared" si="28"/>
-        <v>15753856566.218775</v>
+        <v>17730529731.952339</v>
       </c>
       <c r="J64" s="120">
         <f t="shared" si="28"/>
-        <v>18142653626.864143</v>
+        <v>20275888333.175289</v>
       </c>
       <c r="K64" s="120">
         <f t="shared" si="28"/>
-        <v>20873115666.544281</v>
+        <v>23175436317.066704</v>
       </c>
       <c r="L64" s="120">
         <f t="shared" si="28"/>
-        <v>24000254096.913265</v>
+        <v>26486920291.266178</v>
       </c>
       <c r="M64" s="120">
         <f>M62+M63</f>
-        <v>27545768132.103878</v>
+        <v>30230729212.427589</v>
       </c>
       <c r="N64" s="121">
         <f>P49</f>
@@ -17916,43 +17916,43 @@
       </c>
       <c r="D66" s="112">
         <f t="shared" ref="D66:N66" si="29">D64*D65</f>
-        <v>1179537260.6334753</v>
+        <v>1553326230.0031278</v>
       </c>
       <c r="E66" s="112">
         <f t="shared" si="29"/>
-        <v>7843866903.4200974</v>
+        <v>8919767370.884388</v>
       </c>
       <c r="F66" s="112">
         <f t="shared" si="29"/>
-        <v>5753350477.9872265</v>
+        <v>6640993764.863471</v>
       </c>
       <c r="G66" s="112">
         <f t="shared" si="29"/>
-        <v>5574788608.3949623</v>
+        <v>6376061791.1550627</v>
       </c>
       <c r="H66" s="112">
         <f t="shared" si="29"/>
-        <v>1505667216.0945742</v>
+        <v>2227595454.6669092</v>
       </c>
       <c r="I66" s="112">
         <f t="shared" si="29"/>
-        <v>5174527397.9237785</v>
+        <v>5823787432.1151438</v>
       </c>
       <c r="J66" s="112">
         <f t="shared" si="29"/>
-        <v>4949924562.4919052</v>
+        <v>5531942556.5241737</v>
       </c>
       <c r="K66" s="112">
         <f t="shared" si="29"/>
-        <v>4730412548.2766924</v>
+        <v>5252180676.6852341</v>
       </c>
       <c r="L66" s="112">
         <f t="shared" si="29"/>
-        <v>4517951300.7960358</v>
+        <v>4986056210.1047745</v>
       </c>
       <c r="M66" s="112">
         <f t="shared" si="29"/>
-        <v>4307195260.8930149</v>
+        <v>4727029319.8087358</v>
       </c>
       <c r="N66" s="112">
         <f t="shared" si="29"/>
@@ -18007,49 +18007,49 @@
       <c r="N67" s="112"/>
     </row>
     <row r="68" spans="2:14" ht="13" x14ac:dyDescent="0.15">
-      <c r="B68" s="167" t="s">
+      <c r="B68" s="156" t="s">
         <v>375</v>
       </c>
       <c r="C68" s="137"/>
       <c r="D68" s="112">
         <f>D64+D67-D27*(1-D5)</f>
-        <v>9762980230.9675388</v>
+        <v>10212980230.967539</v>
       </c>
       <c r="E68" s="112">
         <f t="shared" ref="E68:M68" si="31">E64+E67-E27*(1-E5)</f>
-        <v>10418654913.773872</v>
+        <v>11978006913.773872</v>
       </c>
       <c r="F68" s="112">
         <f t="shared" si="31"/>
-        <v>9100321735.9606304</v>
+        <v>10649126126.296629</v>
       </c>
       <c r="G68" s="112">
         <f t="shared" si="31"/>
-        <v>10783419921.423283</v>
+        <v>12466577352.160585</v>
       </c>
       <c r="H68" s="112">
         <f t="shared" si="31"/>
-        <v>2892077020.4275541</v>
+        <v>4717755067.2263041</v>
       </c>
       <c r="I68" s="112">
         <f t="shared" si="31"/>
-        <v>14849674922.613787</v>
+        <v>16826348088.347351</v>
       </c>
       <c r="J68" s="112">
         <f t="shared" si="31"/>
-        <v>17249882053.233376</v>
+        <v>19383116759.544521</v>
       </c>
       <c r="K68" s="112">
         <f t="shared" si="31"/>
-        <v>19991754162.887733</v>
+        <v>22294074813.410156</v>
       </c>
       <c r="L68" s="112">
         <f t="shared" si="31"/>
-        <v>23130302663.230938</v>
+        <v>25616968857.583851</v>
       </c>
       <c r="M68" s="112">
         <f t="shared" si="31"/>
-        <v>25851505544.636105</v>
+        <v>28536466624.959816</v>
       </c>
       <c r="N68" s="112"/>
     </row>
@@ -18087,7 +18087,7 @@
       </c>
       <c r="C71" s="141">
         <f>NPV(WACC!B18,'Estado de resultados'!D64:N64)+'Estado de resultados'!C64</f>
-        <v>31891803211.901283</v>
+        <v>38393322481.800545</v>
       </c>
       <c r="D71" s="112"/>
       <c r="E71" s="112"/>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="C72" s="143">
         <f>MIRR(C64:N64,WACC!B18,WACC!B18)</f>
-        <v>0.34109457050803416</v>
+        <v>0.35734543802520369</v>
       </c>
       <c r="D72" s="112"/>
       <c r="E72" s="112"/>
@@ -18125,9 +18125,9 @@
       <c r="B73" s="142" t="s">
         <v>351</v>
       </c>
-      <c r="C73" s="166">
+      <c r="C73" s="155">
         <f>2+ABS(SUM(C66:E66))/F66</f>
-        <v>2.8649909048627014</v>
+        <v>2.5310811188790496</v>
       </c>
       <c r="D73" s="120"/>
       <c r="E73" s="120"/>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="C76" s="148">
         <f>ABS(SUM(D66:N66)/C64)</f>
-        <v>3.2779859437072347</v>
+        <v>3.742380177271468</v>
       </c>
       <c r="D76" s="120"/>
       <c r="E76" s="120"/>
@@ -18177,44 +18177,44 @@
         <v>355</v>
       </c>
       <c r="D79" s="116">
-        <f>D51/D45</f>
-        <v>3.5552954778061065E-2</v>
+        <f t="shared" ref="D79:M79" si="32">D51/D45</f>
+        <v>6.5754886223256911E-2</v>
       </c>
       <c r="E79" s="116">
-        <f>E51/E45</f>
-        <v>0.81189287854670089</v>
+        <f t="shared" si="32"/>
+        <v>0.9935691448714028</v>
       </c>
       <c r="F79" s="116">
-        <f>F51/F45</f>
-        <v>1.1509994165403077</v>
+        <f t="shared" si="32"/>
+        <v>1.398696739354045</v>
       </c>
       <c r="G79" s="116">
-        <f>G51/G45</f>
-        <v>1.6980512719201346</v>
+        <f t="shared" si="32"/>
+        <v>2.0614052039292154</v>
       </c>
       <c r="H79" s="116">
-        <f>H51/H45</f>
-        <v>2.6965970399616053</v>
+        <f t="shared" si="32"/>
+        <v>3.305657344133226</v>
       </c>
       <c r="I79" s="116">
-        <f>I51/I45</f>
-        <v>5.0051666692588759</v>
+        <f t="shared" si="32"/>
+        <v>6.3788967054391819</v>
       </c>
       <c r="J79" s="116">
-        <f>J51/J45</f>
-        <v>15.230378912991371</v>
+        <f t="shared" si="32"/>
+        <v>24.60250191963048</v>
       </c>
       <c r="K79" s="116">
-        <f>K51/K45</f>
-        <v>-24.269563097624886</v>
+        <f t="shared" si="32"/>
+        <v>-18.779593361439836</v>
       </c>
       <c r="L79" s="116">
-        <f>L51/L45</f>
-        <v>-7.8931985349709581</v>
+        <f t="shared" si="32"/>
+        <v>-7.7266983681312933</v>
       </c>
       <c r="M79" s="116">
-        <f>M51/M45</f>
-        <v>-5.1322792624758007</v>
+        <f t="shared" si="32"/>
+        <v>-5.2365998091655221</v>
       </c>
     </row>
     <row r="80" spans="2:14" ht="13" x14ac:dyDescent="0.15">
@@ -18222,44 +18222,44 @@
         <v>356</v>
       </c>
       <c r="D80" s="116">
-        <f>D19/D15</f>
-        <v>0.60653846153846158</v>
+        <f t="shared" ref="D80:M80" si="33">D19/D15</f>
+        <v>0.66807692307692312</v>
       </c>
       <c r="E80" s="116">
-        <f>E19/E15</f>
-        <v>0.64021044992743104</v>
+        <f t="shared" si="33"/>
+        <v>0.69942670537010154</v>
       </c>
       <c r="F80" s="116">
-        <f>F19/F15</f>
-        <v>0.65187624941807931</v>
+        <f t="shared" si="33"/>
+        <v>0.70885792918366786</v>
       </c>
       <c r="G80" s="116">
-        <f>G19/G15</f>
-        <v>0.66309252966181187</v>
+        <f t="shared" si="33"/>
+        <v>0.7179239573607743</v>
       </c>
       <c r="H80" s="116">
-        <f>H19/H15</f>
-        <v>0.6738767800867127</v>
+        <f t="shared" si="33"/>
+        <v>0.72663909730646925</v>
       </c>
       <c r="I80" s="116">
-        <f>I19/I15</f>
-        <v>0.68424580034409155</v>
+        <f t="shared" si="33"/>
+        <v>0.7350170867253667</v>
       </c>
       <c r="J80" s="116">
-        <f>J19/J15</f>
-        <v>0.69421572802449438</v>
+        <f t="shared" si="33"/>
+        <v>0.74307111680647608</v>
       </c>
       <c r="K80" s="116">
-        <f>K19/K15</f>
-        <v>0.70380206523235489</v>
+        <f t="shared" si="33"/>
+        <v>0.75081385443765813</v>
       </c>
       <c r="L80" s="116">
-        <f>L19/L15</f>
-        <v>0.71301970406775894</v>
+        <f t="shared" si="33"/>
+        <v>0.75825746349172995</v>
       </c>
       <c r="M80" s="116">
-        <f>M19/M15</f>
-        <v>0.72188295106166223</v>
+        <f t="shared" si="33"/>
+        <v>0.76541362522435141</v>
       </c>
     </row>
     <row r="81" spans="2:13" ht="13" x14ac:dyDescent="0.15">
@@ -18267,44 +18267,44 @@
         <v>357</v>
       </c>
       <c r="D81" s="116">
-        <f>D26/D15</f>
-        <v>7.3174358974358977E-2</v>
+        <f t="shared" ref="D81:M81" si="34">D26/D15</f>
+        <v>0.13471282051282052</v>
       </c>
       <c r="E81" s="116">
-        <f>E26/E15</f>
-        <v>0.30508217897705769</v>
+        <f t="shared" si="34"/>
+        <v>0.3642984344197282</v>
       </c>
       <c r="F81" s="116">
-        <f>F26/F15</f>
-        <v>0.32175930993381924</v>
+        <f t="shared" si="34"/>
+        <v>0.37874098969940778</v>
       </c>
       <c r="G81" s="116">
-        <f>G26/G15</f>
-        <v>0.33750653401897623</v>
+        <f t="shared" si="34"/>
+        <v>0.39233796171793872</v>
       </c>
       <c r="H81" s="116">
-        <f>H26/H15</f>
-        <v>0.35240574139353087</v>
+        <f t="shared" si="34"/>
+        <v>0.40516805861328742</v>
       </c>
       <c r="I81" s="116">
-        <f>I26/I15</f>
-        <v>0.36652248319868075</v>
+        <f t="shared" si="34"/>
+        <v>0.4172937695799559</v>
       </c>
       <c r="J81" s="116">
-        <f>J26/J15</f>
-        <v>0.37989814312274206</v>
+        <f t="shared" si="34"/>
+        <v>0.42875353190472371</v>
       </c>
       <c r="K81" s="116">
-        <f>K26/K15</f>
-        <v>0.39261728609063085</v>
+        <f t="shared" si="34"/>
+        <v>0.43962907529593415</v>
       </c>
       <c r="L81" s="116">
-        <f>L26/L15</f>
-        <v>0.40472857800648554</v>
+        <f t="shared" si="34"/>
+        <v>0.4499663374304565</v>
       </c>
       <c r="M81" s="116">
-        <f>M26/M15</f>
-        <v>0.4162587732225741</v>
+        <f t="shared" si="34"/>
+        <v>0.45978944738526339</v>
       </c>
     </row>
     <row r="82" spans="2:13" ht="13" x14ac:dyDescent="0.15">
@@ -18312,44 +18312,44 @@
         <v>358</v>
       </c>
       <c r="D82" s="116">
-        <f>D32/D15</f>
-        <v>0.15520512820512822</v>
+        <f t="shared" ref="D82:M82" si="35">D32/D15</f>
+        <v>0.21674358974358973</v>
       </c>
       <c r="E82" s="116">
-        <f>E32/E15</f>
-        <v>0.32701741654571842</v>
+        <f t="shared" si="35"/>
+        <v>0.38623367198838898</v>
       </c>
       <c r="F82" s="116">
-        <f>F32/F15</f>
-        <v>0.34112810471835048</v>
+        <f t="shared" si="35"/>
+        <v>0.39810978448393902</v>
       </c>
       <c r="G82" s="116">
-        <f>G32/G15</f>
-        <v>0.35465088371867143</v>
+        <f t="shared" si="35"/>
+        <v>0.40948231141763392</v>
       </c>
       <c r="H82" s="116">
-        <f>H32/H15</f>
-        <v>0.36761107636676876</v>
+        <f t="shared" si="35"/>
+        <v>0.42037339358652531</v>
       </c>
       <c r="I82" s="116">
-        <f>I32/I15</f>
-        <v>0.3800328723064087</v>
+        <f t="shared" si="35"/>
+        <v>0.43080415868768379</v>
       </c>
       <c r="J82" s="116">
-        <f>J32/J15</f>
-        <v>0.39193938081913327</v>
+        <f t="shared" si="35"/>
+        <v>0.44079476960111491</v>
       </c>
       <c r="K82" s="116">
-        <f>K32/K15</f>
-        <v>0.40335268107635375</v>
+        <f t="shared" si="35"/>
+        <v>0.45036447028165705</v>
       </c>
       <c r="L82" s="116">
-        <f>L32/L15</f>
-        <v>0.4142938699583239</v>
+        <f t="shared" si="35"/>
+        <v>0.45953162938229491</v>
       </c>
       <c r="M82" s="116">
-        <f>M32/M15</f>
-        <v>0.42478310756219528</v>
+        <f t="shared" si="35"/>
+        <v>0.46831378172488458</v>
       </c>
     </row>
     <row r="83" spans="2:13" ht="13" x14ac:dyDescent="0.15">
@@ -18357,44 +18357,44 @@
         <v>359</v>
       </c>
       <c r="D83" s="116">
-        <f>D38/D15</f>
-        <v>-1.6050059573193678E-2</v>
+        <f t="shared" ref="D83:M83" si="36">D38/D15</f>
+        <v>-2.2203905727039838E-2</v>
       </c>
       <c r="E83" s="116">
-        <f>E38/E15</f>
-        <v>-9.5843921051640191E-2</v>
+        <f t="shared" si="36"/>
+        <v>-0.10176554659590724</v>
       </c>
       <c r="F83" s="116">
-        <f>F38/F15</f>
-        <v>-9.9226239320703222E-2</v>
+        <f t="shared" si="36"/>
+        <v>-0.10492440729726207</v>
       </c>
       <c r="G83" s="116">
-        <f>G38/G15</f>
-        <v>-0.10232903300993026</v>
+        <f t="shared" si="36"/>
+        <v>-0.10781217577982644</v>
       </c>
       <c r="H83" s="116">
-        <f>H38/H15</f>
-        <v>-0.10518774640683672</v>
+        <f t="shared" si="36"/>
+        <v>-0.11046397812881238</v>
       </c>
       <c r="I83" s="116">
-        <f>I38/I15</f>
-        <v>-0.10782986004275938</v>
+        <f t="shared" si="36"/>
+        <v>-0.11290698868088685</v>
       </c>
       <c r="J83" s="116">
-        <f>J38/J15</f>
-        <v>-0.11027244911005209</v>
+        <f t="shared" si="36"/>
+        <v>-0.11515798798825023</v>
       </c>
       <c r="K83" s="116">
-        <f>K38/K15</f>
-        <v>-0.11254851082394469</v>
+        <f t="shared" si="36"/>
+        <v>-0.11724968974447506</v>
       </c>
       <c r="L83" s="116">
-        <f>L38/L15</f>
-        <v>-0.11467598738898983</v>
+        <f t="shared" si="36"/>
+        <v>-0.11919976333138693</v>
       </c>
       <c r="M83" s="116">
-        <f>M38/M15</f>
-        <v>-0.11668872747240676</v>
+        <f t="shared" si="36"/>
+        <v>-0.12104179488867572</v>
       </c>
     </row>
     <row r="85" spans="2:13" ht="13" x14ac:dyDescent="0.15">
@@ -18403,43 +18403,43 @@
       </c>
       <c r="D85" s="118">
         <f>D82/D83</f>
-        <v>-9.6700655531738402</v>
+        <v>-9.7615073855965875</v>
       </c>
       <c r="E85" s="118">
-        <f t="shared" ref="E85:M85" si="32">E82/E83</f>
-        <v>-3.411978693667209</v>
+        <f t="shared" ref="E85:M85" si="37">E82/E83</f>
+        <v>-3.7953284280194919</v>
       </c>
       <c r="F85" s="118">
-        <f t="shared" si="32"/>
-        <v>-3.4378820265052132</v>
+        <f t="shared" si="37"/>
+        <v>-3.794253355713999</v>
       </c>
       <c r="G85" s="118">
-        <f t="shared" si="32"/>
-        <v>-3.4657894566858189</v>
+        <f t="shared" si="37"/>
+        <v>-3.7981082234522097</v>
       </c>
       <c r="H85" s="118">
-        <f t="shared" si="32"/>
-        <v>-3.4948089385331271</v>
+        <f t="shared" si="37"/>
+        <v>-3.8055246670215572</v>
       </c>
       <c r="I85" s="118">
-        <f t="shared" si="32"/>
-        <v>-3.5243750864158465</v>
+        <f t="shared" si="37"/>
+        <v>-3.8155668105300493</v>
       </c>
       <c r="J85" s="118">
-        <f t="shared" si="32"/>
-        <v>-3.554281998652058</v>
+        <f t="shared" si="37"/>
+        <v>-3.827739415229189</v>
       </c>
       <c r="K85" s="118">
-        <f t="shared" si="32"/>
-        <v>-3.5838117992276488</v>
+        <f t="shared" si="37"/>
+        <v>-3.8410717440971203</v>
       </c>
       <c r="L85" s="118">
-        <f t="shared" si="32"/>
-        <v>-3.612734273244206</v>
+        <f t="shared" si="37"/>
+        <v>-3.8551387732604159</v>
       </c>
       <c r="M85" s="118">
-        <f t="shared" si="32"/>
-        <v>-3.6403097091160173</v>
+        <f t="shared" si="37"/>
+        <v>-3.8690254234547745</v>
       </c>
     </row>
     <row r="86" spans="2:13" ht="13" x14ac:dyDescent="0.15">
@@ -18448,43 +18448,43 @@
       </c>
       <c r="D86" s="119">
         <f>(D79-WACC!$B$18)*'Estado de resultados'!D45</f>
-        <v>-2195711924.9955101</v>
+        <v>-1793478653.7849333</v>
       </c>
       <c r="E86" s="119">
         <f>(E79-WACC!$B$18)*'Estado de resultados'!E45</f>
-        <v>5414741026.4728117</v>
+        <v>6862201586.9203444</v>
       </c>
       <c r="F86" s="119">
         <f>(F79-WACC!$B$18)*'Estado de resultados'!F45</f>
-        <v>7106394547.2652617</v>
+        <v>8683790747.3030453</v>
       </c>
       <c r="G86" s="119">
         <f>(G79-WACC!$B$18)*'Estado de resultados'!G45</f>
-        <v>9005404496.5502529</v>
+        <v>10720217143.950525</v>
       </c>
       <c r="H86" s="119">
         <f>(H79-WACC!$B$18)*'Estado de resultados'!H45</f>
-        <v>11137745768.895601</v>
+        <v>12998272906.196072</v>
       </c>
       <c r="I86" s="119">
         <f>(I79-WACC!$B$18)*'Estado de resultados'!I45</f>
-        <v>13529006405.409296</v>
+        <v>15543929387.198647</v>
       </c>
       <c r="J86" s="119">
         <f>(J79-WACC!$B$18)*'Estado de resultados'!J45</f>
-        <v>16182203815.408293</v>
+        <v>18357655711.156792</v>
       </c>
       <c r="K86" s="119">
         <f>(K79-WACC!$B$18)*'Estado de resultados'!K45</f>
-        <v>19172528835.372379</v>
+        <v>21520522347.328396</v>
       </c>
       <c r="L86" s="119">
         <f>(L79-WACC!$B$18)*'Estado de resultados'!L45</f>
-        <v>22565041869.693596</v>
+        <v>25100818510.761791</v>
       </c>
       <c r="M86" s="119">
         <f>(M79-WACC!$B$18)*'Estado de resultados'!M45</f>
-        <v>26394705688.86586</v>
+        <v>29132766304.14537</v>
       </c>
     </row>
     <row r="88" spans="2:13" ht="26" x14ac:dyDescent="0.15">
@@ -18492,44 +18492,44 @@
         <v>362</v>
       </c>
       <c r="D88" s="118">
-        <f>D26/D27</f>
-        <v>8.1286530415287981</v>
+        <f t="shared" ref="D88:M88" si="38">D26/D27</f>
+        <v>14.96471979451398</v>
       </c>
       <c r="E88" s="118">
-        <f>E26/E27</f>
-        <v>65.838542427979178</v>
+        <f t="shared" si="38"/>
+        <v>78.617761323886896</v>
       </c>
       <c r="F88" s="118">
-        <f>F26/F27</f>
-        <v>87.755807934357804</v>
+        <f t="shared" si="38"/>
+        <v>103.29684494837487</v>
       </c>
       <c r="G88" s="118">
-        <f>G26/G27</f>
-        <v>117.63261973378687</v>
+        <f t="shared" si="38"/>
+        <v>136.743255629239</v>
       </c>
       <c r="H88" s="118">
-        <f>H26/H27</f>
-        <v>159.3923777326539</v>
+        <f t="shared" si="38"/>
+        <v>183.25666315287984</v>
       </c>
       <c r="I88" s="118">
-        <f>I26/I27</f>
-        <v>219.7438275785882</v>
+        <f t="shared" si="38"/>
+        <v>250.18309750589123</v>
       </c>
       <c r="J88" s="118">
-        <f>J26/J27</f>
-        <v>310.80697237045035</v>
+        <f t="shared" si="38"/>
+        <v>350.77714791932891</v>
       </c>
       <c r="K88" s="118">
-        <f>K26/K27</f>
-        <v>459.6738798683748</v>
+        <f t="shared" si="38"/>
+        <v>514.71499066288914</v>
       </c>
       <c r="L88" s="118">
-        <f>L26/L27</f>
-        <v>734.41710270278793</v>
+        <f t="shared" si="38"/>
+        <v>816.50516372521986</v>
       </c>
       <c r="M88" s="118">
-        <f>M26/M27</f>
-        <v>1779.915399049032</v>
+        <f t="shared" si="38"/>
+        <v>1966.0518176842911</v>
       </c>
     </row>
     <row r="89" spans="2:13" ht="13" x14ac:dyDescent="0.15">
@@ -18573,44 +18573,44 @@
         <v>364</v>
       </c>
       <c r="D90" s="118">
-        <f>D62/D89</f>
-        <v>0.80895198682443781</v>
+        <f t="shared" ref="D90:M90" si="39">D62/D89</f>
+        <v>1.0653044900613822</v>
       </c>
       <c r="E90" s="118">
-        <f>E62/E89</f>
-        <v>4.494236405247559</v>
+        <f t="shared" si="39"/>
+        <v>5.1106863155835649</v>
       </c>
       <c r="F90" s="118">
-        <f>F62/F89</f>
-        <v>4.2644910722477762</v>
+        <f t="shared" si="39"/>
+        <v>4.9224288924288082</v>
       </c>
       <c r="G90" s="118">
-        <f>G62/G89</f>
-        <v>5.3754789785983643</v>
+        <f t="shared" si="39"/>
+        <v>6.1481050730758042</v>
       </c>
       <c r="H90" s="118">
-        <f>H62/H89</f>
-        <v>6.7938153926541371</v>
+        <f t="shared" si="39"/>
+        <v>7.705310216552598</v>
       </c>
       <c r="I90" s="118">
-        <f>I62/I89</f>
-        <v>8.6208663706453592</v>
+        <f t="shared" si="39"/>
+        <v>9.7025466023144791</v>
       </c>
       <c r="J90" s="118">
-        <f>J62/J89</f>
-        <v>10.98309772194906</v>
+        <f t="shared" si="39"/>
+        <v>12.274503363325364</v>
       </c>
       <c r="K90" s="118">
-        <f>K62/K89</f>
-        <v>14.13850832497668</v>
+        <f t="shared" si="39"/>
+        <v>15.697996625822482</v>
       </c>
       <c r="L90" s="118">
-        <f>L62/L89</f>
-        <v>18.450503419735949</v>
+        <f t="shared" si="39"/>
+        <v>20.362159977095107</v>
       </c>
       <c r="M90" s="118">
-        <f>M62/M89</f>
-        <v>14.502165921754102</v>
+        <f t="shared" si="39"/>
+        <v>15.915731551638485</v>
       </c>
     </row>
     <row r="91" spans="2:13" ht="13" x14ac:dyDescent="0.15">
@@ -18654,43 +18654,43 @@
         <v>366</v>
       </c>
       <c r="D92" s="118">
-        <f>D91/D32</f>
-        <v>5.550966462910953</v>
+        <f t="shared" ref="D92:M92" si="40">D91/D32</f>
+        <v>3.9749201466934818</v>
       </c>
       <c r="E92" s="118">
-        <f>E91/E32</f>
-        <v>0.6340329887364039</v>
+        <f t="shared" si="40"/>
+        <v>0.53682484210639336</v>
       </c>
       <c r="F92" s="118">
-        <f>F91/F32</f>
-        <v>0.477059962457897</v>
+        <f t="shared" si="40"/>
+        <v>0.40877809883829974</v>
       </c>
       <c r="G92" s="118">
-        <f>G91/G32</f>
-        <v>0.35539875043134411</v>
+        <f t="shared" si="40"/>
+        <v>0.30780934218288158</v>
       </c>
       <c r="H92" s="118">
-        <f>H91/H32</f>
-        <v>0.26064928638597801</v>
+        <f t="shared" si="40"/>
+        <v>0.22793441779244636</v>
       </c>
       <c r="I92" s="118">
-        <f>I91/I32</f>
-        <v>0.1866872178843462</v>
+        <f t="shared" si="40"/>
+        <v>0.16468568885592963</v>
       </c>
       <c r="J92" s="118">
-        <f>J91/J32</f>
-        <v>0.12906548119843894</v>
+        <f t="shared" si="40"/>
+        <v>0.11476053772556309</v>
       </c>
       <c r="K92" s="118">
-        <f>K91/K32</f>
-        <v>8.3859490787008661E-2</v>
+        <f t="shared" si="40"/>
+        <v>7.5105725861286693E-2</v>
       </c>
       <c r="L92" s="118">
-        <f>L91/L32</f>
-        <v>4.8497304908023432E-2</v>
+        <f t="shared" si="40"/>
+        <v>4.3723075514740542E-2</v>
       </c>
       <c r="M92" s="118">
-        <f>M91/M32</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
@@ -22371,7 +22371,7 @@
       <c r="A16" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="B16" s="165">
+      <c r="B16" s="154">
         <f>SUM(B14:K14)</f>
         <v>26880322416.543213</v>
       </c>
@@ -22670,10 +22670,10 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="161" t="s">
+      <c r="A26" s="159" t="s">
         <v>136</v>
       </c>
-      <c r="B26" s="161"/>
+      <c r="B26" s="159"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="43" t="s">
@@ -22845,22 +22845,22 @@
       <c r="D42" s="55"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A44" s="162" t="s">
+      <c r="A44" s="160" t="s">
         <v>167</v>
       </c>
-      <c r="B44" s="162"/>
-      <c r="C44" s="162"/>
-      <c r="D44" s="162"/>
-      <c r="E44" s="162"/>
-      <c r="F44" s="162"/>
-      <c r="G44" s="162"/>
-      <c r="I44" s="163"/>
-      <c r="J44" s="163"/>
-      <c r="K44" s="163"/>
-      <c r="L44" s="163"/>
-      <c r="M44" s="163"/>
-      <c r="N44" s="163"/>
-      <c r="O44" s="163"/>
+      <c r="B44" s="160"/>
+      <c r="C44" s="160"/>
+      <c r="D44" s="160"/>
+      <c r="E44" s="160"/>
+      <c r="F44" s="160"/>
+      <c r="G44" s="160"/>
+      <c r="I44" s="161"/>
+      <c r="J44" s="161"/>
+      <c r="K44" s="161"/>
+      <c r="L44" s="161"/>
+      <c r="M44" s="161"/>
+      <c r="N44" s="161"/>
+      <c r="O44" s="161"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
@@ -24185,15 +24185,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="162" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
       <c r="P1" s="63" t="s">
         <v>189</v>
       </c>
@@ -24205,17 +24205,17 @@
       <c r="V1" s="63"/>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A3" s="153" t="s">
+      <c r="A3" s="163" t="s">
         <v>190</v>
       </c>
-      <c r="B3" s="153"/>
+      <c r="B3" s="163"/>
       <c r="D3" s="64" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="154" t="s">
+      <c r="P3" s="164" t="s">
         <v>190</v>
       </c>
-      <c r="Q3" s="154"/>
+      <c r="Q3" s="164"/>
       <c r="S3" s="64" t="s">
         <v>191</v>
       </c>
@@ -24480,13 +24480,13 @@
         <f>AG9*AG10</f>
         <v>682.10548276114309</v>
       </c>
-      <c r="AM13" s="156" t="s">
+      <c r="AM13" s="166" t="s">
         <v>233</v>
       </c>
-      <c r="AN13" s="157"/>
-      <c r="AO13" s="157"/>
-      <c r="AP13" s="157"/>
-      <c r="AQ13" s="157"/>
+      <c r="AN13" s="167"/>
+      <c r="AO13" s="167"/>
+      <c r="AP13" s="167"/>
+      <c r="AQ13" s="167"/>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -24572,22 +24572,22 @@
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A17" s="153" t="s">
+      <c r="A17" s="163" t="s">
         <v>243</v>
       </c>
-      <c r="B17" s="153"/>
-      <c r="C17" s="153"/>
-      <c r="D17" s="153"/>
-      <c r="E17" s="153"/>
-      <c r="F17" s="153"/>
-      <c r="G17" s="153"/>
-      <c r="I17" s="153" t="s">
+      <c r="B17" s="163"/>
+      <c r="C17" s="163"/>
+      <c r="D17" s="163"/>
+      <c r="E17" s="163"/>
+      <c r="F17" s="163"/>
+      <c r="G17" s="163"/>
+      <c r="I17" s="163" t="s">
         <v>233</v>
       </c>
-      <c r="J17" s="153"/>
-      <c r="K17" s="153"/>
-      <c r="L17" s="153"/>
-      <c r="M17" s="153"/>
+      <c r="J17" s="163"/>
+      <c r="K17" s="163"/>
+      <c r="L17" s="163"/>
+      <c r="M17" s="163"/>
       <c r="P17" s="64" t="s">
         <v>244</v>
       </c>
@@ -24668,22 +24668,22 @@
       <c r="M19" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="P19" s="155" t="s">
+      <c r="P19" s="165" t="s">
         <v>243</v>
       </c>
-      <c r="Q19" s="155"/>
-      <c r="R19" s="155"/>
-      <c r="S19" s="155"/>
-      <c r="T19" s="155"/>
-      <c r="U19" s="155"/>
-      <c r="V19" s="155"/>
-      <c r="X19" s="155" t="s">
+      <c r="Q19" s="165"/>
+      <c r="R19" s="165"/>
+      <c r="S19" s="165"/>
+      <c r="T19" s="165"/>
+      <c r="U19" s="165"/>
+      <c r="V19" s="165"/>
+      <c r="X19" s="165" t="s">
         <v>233</v>
       </c>
-      <c r="Y19" s="155"/>
-      <c r="Z19" s="155"/>
-      <c r="AA19" s="155"/>
-      <c r="AB19" s="155"/>
+      <c r="Y19" s="165"/>
+      <c r="Z19" s="165"/>
+      <c r="AA19" s="165"/>
+      <c r="AB19" s="165"/>
       <c r="AF19" s="72" t="s">
         <v>249</v>
       </c>
@@ -26141,13 +26141,13 @@
         <f t="shared" si="5"/>
         <v>6510</v>
       </c>
-      <c r="I32" s="153" t="s">
+      <c r="I32" s="163" t="s">
         <v>253</v>
       </c>
-      <c r="J32" s="153"/>
-      <c r="K32" s="153"/>
-      <c r="L32" s="153"/>
-      <c r="M32" s="153"/>
+      <c r="J32" s="163"/>
+      <c r="K32" s="163"/>
+      <c r="L32" s="163"/>
+      <c r="M32" s="163"/>
       <c r="P32" s="79">
         <v>11</v>
       </c>
@@ -28219,15 +28219,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P19:V19"/>
+    <mergeCell ref="X19:AB19"/>
+    <mergeCell ref="AM13:AQ13"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="I17:M17"/>
     <mergeCell ref="I32:M32"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P19:V19"/>
-    <mergeCell ref="X19:AB19"/>
-    <mergeCell ref="AM13:AQ13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D9" r:id="rId1" xr:uid="{FE201A1B-6C8C-4A0F-801E-10AC66BA1A74}"/>

--- a/Taller_final.xlsx
+++ b/Taller_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidarmendariz/finanzas-corporativas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eafit-my.sharepoint.com/personal/darmendar_eafit_edu_co/Documents/MAF/Finanzas Corporativas/Taller final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BC65EF-C6ED-C344-8350-33BA99DCCD94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="709" documentId="13_ncr:1_{9A198AE5-DFB1-4B20-96FE-55380C251E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16E6B8CF-74D6-1942-A6F2-13ED21277ACB}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20240" activeTab="10" xr2:uid="{4A5FEAB5-AF17-D144-BB0B-4790A386B114}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20200" activeTab="2" xr2:uid="{4A5FEAB5-AF17-D144-BB0B-4790A386B114}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="2" r:id="rId1"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="375">
   <si>
     <r>
       <t xml:space="preserve">Según el estatuto tributario de los impuestos administrados por la dirección general de impuestos nacionales
@@ -1499,13 +1499,10 @@
     <t>FCL descontado</t>
   </si>
   <si>
-    <t>Política de dividendos</t>
-  </si>
-  <si>
-    <t>Δ Deuda</t>
-  </si>
-  <si>
-    <t>Equity Cash Flow</t>
+    <t>VPN del Proyecto asumiendo multa</t>
+  </si>
+  <si>
+    <t>Multa considerada</t>
   </si>
 </sst>
 </file>
@@ -1527,7 +1524,7 @@
     <numFmt numFmtId="171" formatCode="0.0"/>
     <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1688,18 +1685,6 @@
       <color rgb="FFFF0000"/>
       <name val="Arial Nova Cond"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Nova Cond"/>
     </font>
   </fonts>
   <fills count="16">
@@ -2098,7 +2083,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2352,12 +2337,7 @@
     <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="42" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="172" fontId="20" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2373,14 +2353,14 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma" xfId="6" builtinId="3"/>
@@ -2640,39 +2620,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Estado de resultados'!$D$86:$M$86</c:f>
+              <c:f>'Estado de resultados'!$D$84:$M$84</c:f>
               <c:numCache>
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-1793478653.7849333</c:v>
+                  <c:v>-2228779375.3255625</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6862201586.9203444</c:v>
+                  <c:v>5299869634.522913</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8683790747.3030453</c:v>
+                  <c:v>6960356196.8722801</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10720217143.950525</c:v>
+                  <c:v>8823082767.5671406</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12998272906.196072</c:v>
+                  <c:v>10913365772.851055</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15543929387.198647</c:v>
+                  <c:v>13256107779.996792</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18357655711.156792</c:v>
+                  <c:v>15854016990.570087</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21520522347.328396</c:v>
+                  <c:v>18780685616.550236</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25100818510.761791</c:v>
+                  <c:v>22099630860.323975</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>29132766304.14537</c:v>
+                  <c:v>25844781248.580288</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3057,39 +3037,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Estado de resultados'!$D$88:$M$88</c:f>
+              <c:f>'Estado de resultados'!$D$86:$M$86</c:f>
               <c:numCache>
                 <c:formatCode>0.0\x</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>14.96471979451398</c:v>
+                  <c:v>5.6238042487891438</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>78.617761323886896</c:v>
+                  <c:v>71.709779148660303</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>103.29684494837487</c:v>
+                  <c:v>94.947383974939228</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>136.743255629239</c:v>
+                  <c:v>126.54177993389611</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>183.25666315287984</c:v>
+                  <c:v>170.60297427875173</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>250.18309750589123</c:v>
+                  <c:v>234.15623931383431</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>350.77714791932891</c:v>
+                  <c:v>329.88645010627937</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>514.71499066288914</c:v>
+                  <c:v>486.16826535952748</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>816.50516372521986</c:v>
+                  <c:v>774.27308389223572</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1966.0518176842911</c:v>
+                  <c:v>1871.0964705705787</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3466,39 +3446,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Estado de resultados'!$D$90:$M$90</c:f>
+              <c:f>'Estado de resultados'!$D$88:$M$88</c:f>
               <c:numCache>
                 <c:formatCode>0.0\x</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.0653044900613822</c:v>
+                  <c:v>0.32076030726993726</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.1106863155835649</c:v>
+                  <c:v>3.6853300476169677</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.9224288924288082</c:v>
+                  <c:v>4.3690545612813434</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.1481050730758042</c:v>
+                  <c:v>5.4979017576853888</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.705310216552598</c:v>
+                  <c:v>6.9368368302814751</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.7025466023144791</c:v>
+                  <c:v>8.7886020149714206</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12.274503363325364</c:v>
+                  <c:v>11.185461356218461</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15.697996625822482</c:v>
+                  <c:v>14.373653423098013</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>20.362159977095107</c:v>
+                  <c:v>18.721701366388462</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>15.915731551638485</c:v>
+                  <c:v>14.692999424182331</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3880,36 +3860,36 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Estado de resultados'!$D$92:$M$92</c:f>
+              <c:f>'Estado de resultados'!$D$90:$M$90</c:f>
               <c:numCache>
                 <c:formatCode>0.0\x</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>3.9749201466934818</c:v>
+                  <c:v>4.7006155567991046</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.53682484210639336</c:v>
+                  <c:v>0.58533615855585863</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.40877809883829974</c:v>
+                  <c:v>0.44283055306381452</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30780934218288158</c:v>
+                  <c:v>0.33150521051659215</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.22793441779244636</c:v>
+                  <c:v>0.24418529722095608</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.16468568885592963</c:v>
+                  <c:v>0.1755807411854434</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.11476053772556309</c:v>
+                  <c:v>0.12181723815691056</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.5105725861286693E-2</c:v>
+                  <c:v>7.9404628226345531E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.3723075514740542E-2</c:v>
+                  <c:v>4.6055624797924695E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -4287,39 +4267,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Estado de resultados'!$D$79:$M$79</c:f>
+              <c:f>'Estado de resultados'!$D$77:$M$77</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>6.5754886223256911E-2</c:v>
+                  <c:v>4.5578334591551986E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9935691448714028</c:v>
+                  <c:v>0.62345911859579217</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.398696739354045</c:v>
+                  <c:v>0.79926331009640328</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.0614052039292154</c:v>
+                  <c:v>1.0267107457749316</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.305657344133226</c:v>
+                  <c:v>1.3260871011330753</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.3788967054391819</c:v>
+                  <c:v>1.7287817665522114</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>24.60250191963048</c:v>
+                  <c:v>2.2831497157736638</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-18.779593361439836</c:v>
+                  <c:v>3.0873629873159598</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-7.7266983681312933</c:v>
+                  <c:v>4.3340615500292294</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-5.2365998091655221</c:v>
+                  <c:v>6.4629009352057816</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4692,34 +4672,34 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2113250000</c:v>
+                  <c:v>1787000000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14082805800</c:v>
+                  <c:v>12915655200</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16439236884.504004</c:v>
+                  <c:v>15175104683.961605</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19102734044.070896</c:v>
+                  <c:v>17737277766.575859</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>22111623373.128967</c:v>
+                  <c:v>20640063334.523586</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25503126769.407661</c:v>
+                  <c:v>23920618922.345699</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>29278357060.639275</c:v>
+                  <c:v>27582303217.809334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>33552701489.819916</c:v>
+                  <c:v>31736185362.100761</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38423646557.836823</c:v>
+                  <c:v>36477629114.168533</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>43939778486.000443</c:v>
+                  <c:v>41856226264.858498</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5095,34 +5075,34 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-216488080.83863842</c:v>
+                  <c:v>878418838.32272315</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-3710563148.114378</c:v>
+                  <c:v>231231561.88562155</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-4332667153.0110521</c:v>
+                  <c:v>90100582.07478714</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-5029539160.0789814</c:v>
+                  <c:v>-77857249.49361515</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-5810400748.3506641</c:v>
+                  <c:v>-276019524.4179678</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-6683968080.1880207</c:v>
+                  <c:v>-508065568.40728664</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-7648994323.9477835</c:v>
+                  <c:v>-776570593.80531597</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-8735244672.6315422</c:v>
+                  <c:v>-1088387731.8024025</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-9966864701.3037872</c:v>
+                  <c:v>-1451024830.6780167</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-11356807897.831085</c:v>
+                  <c:v>-1872789705.7827473</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5505,39 +5485,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Estado de resultados'!$D$85:$M$85</c:f>
+              <c:f>'Estado de resultados'!$D$83:$M$83</c:f>
               <c:numCache>
                 <c:formatCode>0.0\x</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-9.7615073855965875</c:v>
+                  <c:v>2.0343370634128779</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-3.7953284280194919</c:v>
+                  <c:v>55.855935472981479</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-3.794253355713999</c:v>
+                  <c:v>168.42404715394238</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-3.7981082234522097</c:v>
+                  <c:v>-227.81793451399079</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-3.8055246670215572</c:v>
+                  <c:v>-74.777548356575608</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-3.8155668105300493</c:v>
+                  <c:v>-47.081755603579758</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-3.827739415229189</c:v>
+                  <c:v>-35.518088680968177</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-3.8410717440971203</c:v>
+                  <c:v>-29.158896627348689</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-3.8551387732604159</c:v>
+                  <c:v>-25.139217705270919</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-3.8690254234547745</c:v>
+                  <c:v>-22.349666989099749</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5914,39 +5894,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Estado de resultados'!$D$82:$M$82</c:f>
+              <c:f>'Estado de resultados'!$D$80:$M$80</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.21674358974358973</c:v>
+                  <c:v>0.18328205128205127</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.38623367198838898</c:v>
+                  <c:v>0.35422351233671989</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.39810978448393902</c:v>
+                  <c:v>0.36749623463044617</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.40948231141763392</c:v>
+                  <c:v>0.38021266910578227</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.42037339358652531</c:v>
+                  <c:v>0.39239694532417757</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.43080415868768379</c:v>
+                  <c:v>0.40407210469938687</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.44079476960111491</c:v>
+                  <c:v>0.41526015161237639</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.45036447028165705</c:v>
+                  <c:v>0.42598210202834252</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.45953162938229491</c:v>
+                  <c:v>0.43625802974231315</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.46831378172488458</c:v>
+                  <c:v>0.44610711037320377</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6329,39 +6309,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Estado de resultados'!$D$80:$M$80</c:f>
+              <c:f>'Estado de resultados'!$D$78:$M$78</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.66807692307692312</c:v>
+                  <c:v>0.62961538461538458</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.69942670537010154</c:v>
+                  <c:v>0.66241654571843256</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.70885792918366786</c:v>
+                  <c:v>0.673244379330175</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.7179239573607743</c:v>
+                  <c:v>0.68365431504892271</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.72663909730646925</c:v>
+                  <c:v>0.69366264904412145</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.7350170867253667</c:v>
+                  <c:v>0.70328503273706977</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.74307111680647608</c:v>
+                  <c:v>0.71253649881773762</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.75081385443765813</c:v>
+                  <c:v>0.72143148618434361</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.75825746349172995</c:v>
+                  <c:v>0.72998386385174818</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.76541362522435141</c:v>
+                  <c:v>0.73820695387267088</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6738,39 +6718,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Estado de resultados'!$D$81:$M$81</c:f>
+              <c:f>'Estado de resultados'!$D$79:$M$79</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.13471282051282052</c:v>
+                  <c:v>0.10125128205128205</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3642984344197282</c:v>
+                  <c:v>0.33228827476805911</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.37874098969940778</c:v>
+                  <c:v>0.34812743984591493</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.39233796171793872</c:v>
+                  <c:v>0.36306831940608708</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.40516805861328742</c:v>
+                  <c:v>0.37719161035093962</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4172937695799559</c:v>
+                  <c:v>0.39056171559165892</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.42875353190472371</c:v>
+                  <c:v>0.40321891391598519</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.43962907529593415</c:v>
+                  <c:v>0.41524670704261962</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.4499663374304565</c:v>
+                  <c:v>0.42669273779047479</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.45978944738526339</c:v>
+                  <c:v>0.43758277603358253</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7152,39 +7132,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Estado de resultados'!$D$83:$M$83</c:f>
+              <c:f>'Estado de resultados'!$D$81:$M$81</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-2.2203905727039838E-2</c:v>
+                  <c:v>9.0094239827971601E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.10176554659590724</c:v>
+                  <c:v>6.3417344877889333E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.10492440729726207</c:v>
+                  <c:v>2.1819700977411408E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.10781217577982644</c:v>
+                  <c:v>-1.6689321229994411E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.11046397812881238</c:v>
+                  <c:v>-5.2475235407964792E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.11290698868088685</c:v>
+                  <c:v>-8.582349989274065E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.11515798798825023</c:v>
+                  <c:v>-1.1691511762987605E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.11724968974447506</c:v>
+                  <c:v>-1.4608992496266328E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.11919976333138693</c:v>
+                  <c:v>-1.7353683589399971E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.12104179488867572</c:v>
+                  <c:v>-1.996034708663787E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13954,13 +13934,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>146050</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>412750</xdr:colOff>
-      <xdr:row>112</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -13990,13 +13970,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>577850</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>793750</xdr:colOff>
-      <xdr:row>112</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14026,13 +14006,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>971550</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>158750</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14062,13 +14042,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>158750</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>425450</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14098,13 +14078,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>546138</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>92710</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>758228</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>92710</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14134,13 +14114,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>996950</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14170,13 +14150,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14206,13 +14186,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>781050</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14242,13 +14222,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>146050</xdr:colOff>
-      <xdr:row>134</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>412750</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>150</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14278,13 +14258,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>565150</xdr:colOff>
-      <xdr:row>134</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>781050</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>150</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14314,13 +14294,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1085850</xdr:colOff>
-      <xdr:row>134</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>273050</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>150</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14350,13 +14330,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>501650</xdr:colOff>
-      <xdr:row>134</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>806450</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>150</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14702,7 +14682,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="6">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="6">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -14756,10 +14736,10 @@
       <c r="H2" s="26"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="154" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="157"/>
+      <c r="C3" s="154"/>
       <c r="H3" s="26"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
@@ -14978,7 +14958,7 @@
       <c r="D20" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="158" t="s">
+      <c r="E20" s="155" t="s">
         <v>30</v>
       </c>
     </row>
@@ -14992,19 +14972,19 @@
       <c r="D21" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="158"/>
+      <c r="E21" s="155"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>33</v>
       </c>
       <c r="C22" s="15">
-        <v>1600000</v>
+        <v>1850000</v>
       </c>
       <c r="D22" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="158"/>
+      <c r="E22" s="155"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
@@ -15013,7 +14993,7 @@
       <c r="C23" s="10">
         <v>0.02</v>
       </c>
-      <c r="E23" s="158"/>
+      <c r="E23" s="155"/>
     </row>
     <row r="24" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
@@ -15039,7 +15019,7 @@
       <c r="D25" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="158" t="s">
+      <c r="E25" s="155" t="s">
         <v>41</v>
       </c>
     </row>
@@ -15053,29 +15033,29 @@
       <c r="D26" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="158"/>
+      <c r="E26" s="155"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="11">
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D27" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="158"/>
+      <c r="E27" s="155"/>
     </row>
     <row r="28" spans="2:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="153">
-        <v>30</v>
+      <c r="C28">
+        <v>60</v>
       </c>
       <c r="D28" s="39"/>
-      <c r="E28" s="158" t="s">
+      <c r="E28" s="155" t="s">
         <v>46</v>
       </c>
     </row>
@@ -15084,10 +15064,10 @@
         <v>47</v>
       </c>
       <c r="C29">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D29" s="39"/>
-      <c r="E29" s="158"/>
+      <c r="E29" s="155"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
@@ -15099,7 +15079,7 @@
       <c r="D30" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="158"/>
+      <c r="E30" s="155"/>
     </row>
     <row r="31" spans="2:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
@@ -15109,7 +15089,7 @@
         <v>0.06</v>
       </c>
       <c r="D31" s="11"/>
-      <c r="E31" s="158"/>
+      <c r="E31" s="155"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
@@ -15121,7 +15101,7 @@
       <c r="D32" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="158"/>
+      <c r="E32" s="155"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
@@ -15131,7 +15111,7 @@
         <v>0.02</v>
       </c>
       <c r="D33" s="39"/>
-      <c r="E33" s="158"/>
+      <c r="E33" s="155"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
@@ -15143,7 +15123,7 @@
       <c r="D34" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="158"/>
+      <c r="E34" s="155"/>
     </row>
     <row r="35" spans="2:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
@@ -15155,15 +15135,7 @@
       <c r="D35" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="158"/>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>373</v>
-      </c>
-      <c r="C36" s="36">
-        <v>0.9</v>
-      </c>
+      <c r="E35" s="155"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C37" s="151"/>
@@ -15400,7 +15372,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F41A9445-2C08-43B0-8FE5-992216A9CA7B}">
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11" style="108"/>
@@ -15617,43 +15589,43 @@
       <c r="C9" s="135"/>
       <c r="D9" s="112">
         <f>Datos!C22</f>
-        <v>1600000</v>
+        <v>1850000</v>
       </c>
       <c r="E9" s="112">
         <f>D9*(1+D4)*(1+Datos!$C$23)</f>
-        <v>1727308.8</v>
+        <v>1997200.8</v>
       </c>
       <c r="F9" s="112">
         <f>E9*(1+E4)*(1+Datos!$C$23)</f>
-        <v>1882365.8563584001</v>
+        <v>2176485.5214144001</v>
       </c>
       <c r="G9" s="112">
         <f>F9*(1+F4)*(1+Datos!$C$23)</f>
-        <v>2046350.0403009185</v>
+        <v>2366092.2340979371</v>
       </c>
       <c r="H9" s="112">
         <f>G9*(1+G4)*(1+Datos!$C$23)</f>
-        <v>2220236.5886254488</v>
+        <v>2567148.5555981756</v>
       </c>
       <c r="I9" s="112">
         <f>H9*(1+H4)*(1+Datos!$C$23)</f>
-        <v>2404482.9219325315</v>
+        <v>2780183.3784844899</v>
       </c>
       <c r="J9" s="112">
         <f>I9*(1+I4)*(1+Datos!$C$23)</f>
-        <v>2596048.0763228964</v>
+        <v>3001680.5882483493</v>
       </c>
       <c r="K9" s="112">
         <f>J9*(1+J4)*(1+Datos!$C$23)</f>
-        <v>2801948.437400294</v>
+        <v>3239752.8807440903</v>
       </c>
       <c r="L9" s="112">
         <f>K9*(1+K4)*(1+Datos!$C$23)</f>
-        <v>3026037.0656298199</v>
+        <v>3498855.3571344796</v>
       </c>
       <c r="M9" s="112">
         <f>L9*(1+L4)*(1+Datos!$C$23)</f>
-        <v>3267430.094429242</v>
+        <v>3777966.0466838116</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="13" x14ac:dyDescent="0.15">
@@ -15821,50 +15793,50 @@
     <row r="16" spans="1:14" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="110">
         <f t="shared" ref="A16:A37" si="1">D16/$D$15</f>
-        <v>0.24615384615384617</v>
+        <v>0.2846153846153846</v>
       </c>
       <c r="B16" s="122" t="s">
         <v>307</v>
       </c>
       <c r="D16" s="112">
         <f>D9*D10</f>
-        <v>2400000000</v>
+        <v>2775000000</v>
       </c>
       <c r="E16" s="112">
         <f t="shared" ref="E16:M16" si="2">E9*E10</f>
-        <v>8636544000</v>
+        <v>9986004000</v>
       </c>
       <c r="F16" s="112">
         <f t="shared" si="2"/>
-        <v>9411829281.7919998</v>
+        <v>10882427607.072001</v>
       </c>
       <c r="G16" s="112">
         <f t="shared" si="2"/>
-        <v>10231750201.504593</v>
+        <v>11830461170.489685</v>
       </c>
       <c r="H16" s="112">
         <f t="shared" si="2"/>
-        <v>11101182943.127243</v>
+        <v>12835742777.990877</v>
       </c>
       <c r="I16" s="112">
         <f t="shared" si="2"/>
-        <v>12022414609.662657</v>
+        <v>13900916892.422449</v>
       </c>
       <c r="J16" s="112">
         <f t="shared" si="2"/>
-        <v>12980240381.614483</v>
+        <v>15008402941.241747</v>
       </c>
       <c r="K16" s="112">
         <f t="shared" si="2"/>
-        <v>14009742187.001471</v>
+        <v>16198764403.720451</v>
       </c>
       <c r="L16" s="112">
         <f t="shared" si="2"/>
-        <v>15130185328.149099</v>
+        <v>17494276785.672398</v>
       </c>
       <c r="M16" s="112">
         <f t="shared" si="2"/>
-        <v>16337150472.14621</v>
+        <v>18889830233.41906</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="13" x14ac:dyDescent="0.15">
@@ -15968,7 +15940,7 @@
     <row r="19" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A19" s="110">
         <f t="shared" si="1"/>
-        <v>0.66807692307692312</v>
+        <v>0.62961538461538458</v>
       </c>
       <c r="B19" s="124" t="s">
         <v>310</v>
@@ -15976,43 +15948,43 @@
       <c r="C19" s="107"/>
       <c r="D19" s="120">
         <f>D15-D16-D17-D18</f>
-        <v>6513750000</v>
+        <v>6138750000</v>
       </c>
       <c r="E19" s="120">
         <f t="shared" ref="E19:M19" si="4">E15-E16-E17-E18</f>
-        <v>25502412600</v>
+        <v>24152952600</v>
       </c>
       <c r="F19" s="120">
         <f t="shared" si="4"/>
-        <v>29271029925.614403</v>
+        <v>27800431600.334404</v>
       </c>
       <c r="G19" s="120">
         <f t="shared" si="4"/>
-        <v>33491826237.501244</v>
+        <v>31893115268.516151</v>
       </c>
       <c r="H19" s="120">
         <f t="shared" si="4"/>
-        <v>38221186908.975861</v>
+        <v>36486627074.112228</v>
       </c>
       <c r="I19" s="120">
         <f t="shared" si="4"/>
-        <v>43512193562.707214</v>
+        <v>41633691279.947426</v>
       </c>
       <c r="J19" s="120">
         <f t="shared" si="4"/>
-        <v>49356079018.349976</v>
+        <v>47327916458.722717</v>
       </c>
       <c r="K19" s="120">
         <f t="shared" si="4"/>
-        <v>55936546496.691719</v>
+        <v>53747524279.97274</v>
       </c>
       <c r="L19" s="120">
         <f t="shared" si="4"/>
-        <v>63401548259.49968</v>
+        <v>61037456801.976387</v>
       </c>
       <c r="M19" s="120">
         <f t="shared" si="4"/>
-        <v>71815322236.837494</v>
+        <v>69262642475.564651</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="13" x14ac:dyDescent="0.15">
@@ -16205,50 +16177,50 @@
     <row r="24" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A24" s="110">
         <f>D24/$D$15</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="B24" s="122" t="s">
         <v>44</v>
       </c>
       <c r="D24" s="112">
         <f>D15*Datos!$C$27</f>
-        <v>195000000</v>
+        <v>146250000</v>
       </c>
       <c r="E24" s="112">
         <f>E15*Datos!$C$27</f>
-        <v>729237600</v>
+        <v>546928200</v>
       </c>
       <c r="F24" s="112">
         <f>F15*Datos!$C$27</f>
-        <v>825864498.95040011</v>
+        <v>619398374.21280003</v>
       </c>
       <c r="G24" s="112">
         <f>G15*Datos!$C$27</f>
-        <v>933018765.96021664</v>
+        <v>699764074.47016251</v>
       </c>
       <c r="H24" s="112">
         <f>H15*Datos!$C$27</f>
-        <v>1051999185.0329956</v>
+        <v>788999388.77474666</v>
       </c>
       <c r="I24" s="112">
         <f>I15*Datos!$C$27</f>
-        <v>1183977742.7913101</v>
+        <v>887983307.09348261</v>
       </c>
       <c r="J24" s="112">
         <f>J15*Datos!$C$27</f>
-        <v>1328434867.1892779</v>
+        <v>996326150.39195848</v>
       </c>
       <c r="K24" s="112">
         <f>K15*Datos!$C$27</f>
-        <v>1490024355.9993143</v>
+        <v>1117518266.9994857</v>
       </c>
       <c r="L24" s="112">
         <f>L15*Datos!$C$27</f>
-        <v>1672296055.4199984</v>
+        <v>1254222041.5649989</v>
       </c>
       <c r="M24" s="112">
         <f>M15*Datos!$C$27</f>
-        <v>1876510160.5236673</v>
+        <v>1407382620.3927505</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="13" x14ac:dyDescent="0.15">
@@ -16294,7 +16266,7 @@
     <row r="26" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A26" s="110">
         <f t="shared" si="1"/>
-        <v>0.13471282051282052</v>
+        <v>0.10125128205128205</v>
       </c>
       <c r="B26" s="124" t="s">
         <v>314</v>
@@ -16302,56 +16274,56 @@
       <c r="C26" s="107"/>
       <c r="D26" s="120">
         <f>D19-D20-D21-D22-D23-D24-D25</f>
-        <v>1313450000</v>
+        <v>987200000</v>
       </c>
       <c r="E26" s="120">
         <f t="shared" ref="E26:M26" si="6">E19-E20-E21-E22-E23-E24</f>
-        <v>13283005800</v>
+        <v>12115855200</v>
       </c>
       <c r="F26" s="120">
         <f t="shared" si="6"/>
-        <v>15639436884.504004</v>
+        <v>14375304683.961605</v>
       </c>
       <c r="G26" s="120">
         <f t="shared" si="6"/>
-        <v>18302934044.070896</v>
+        <v>16937477766.575857</v>
       </c>
       <c r="H26" s="120">
         <f t="shared" si="6"/>
-        <v>21311823373.128967</v>
+        <v>19840263334.523586</v>
       </c>
       <c r="I26" s="120">
         <f t="shared" si="6"/>
-        <v>24703326769.407661</v>
+        <v>23120818922.345699</v>
       </c>
       <c r="J26" s="120">
         <f t="shared" si="6"/>
-        <v>28478557060.639275</v>
+        <v>26782503217.809334</v>
       </c>
       <c r="K26" s="120">
         <f t="shared" si="6"/>
-        <v>32752901489.819916</v>
+        <v>30936385362.100761</v>
       </c>
       <c r="L26" s="120">
         <f t="shared" si="6"/>
-        <v>37623846557.836823</v>
+        <v>35677829114.168533</v>
       </c>
       <c r="M26" s="120">
         <f t="shared" si="6"/>
-        <v>43139978486.000443</v>
+        <v>41056426264.858498</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A27" s="110">
         <f t="shared" si="1"/>
-        <v>9.0020275930729962E-3</v>
+        <v>1.8004055186145992E-2</v>
       </c>
       <c r="B27" s="122" t="s">
         <v>315</v>
       </c>
       <c r="D27" s="112" cm="1">
-        <f t="array" ref="D27:M27">TRANSPOSE(Bancos!Y22:Y31)*100000</f>
-        <v>87769769.032461718</v>
+        <f t="array" ref="D27:M27">TRANSPOSE(Bancos!J20:J29)*100000</f>
+        <v>175539538.06492344</v>
       </c>
       <c r="E27" s="112">
         <v>168956805.38748878</v>
@@ -16384,7 +16356,7 @@
     <row r="28" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A28" s="110">
         <f t="shared" si="1"/>
-        <v>0.12571079291974752</v>
+        <v>8.3247226865136068E-2</v>
       </c>
       <c r="B28" s="124" t="s">
         <v>316</v>
@@ -16392,98 +16364,98 @@
       <c r="C28" s="107"/>
       <c r="D28" s="120">
         <f>D26-D27</f>
-        <v>1225680230.9675384</v>
+        <v>811660461.93507659</v>
       </c>
       <c r="E28" s="120">
         <f t="shared" ref="E28:M28" si="7">E26-E27</f>
-        <v>13114048994.612511</v>
+        <v>11946898394.612511</v>
       </c>
       <c r="F28" s="120">
         <f t="shared" si="7"/>
-        <v>15488034032.923008</v>
+        <v>14223901832.38061</v>
       </c>
       <c r="G28" s="120">
         <f t="shared" si="7"/>
-        <v>18169085146.296391</v>
+        <v>16803628868.801353</v>
       </c>
       <c r="H28" s="120">
         <f t="shared" si="7"/>
-        <v>21195528429.160957</v>
+        <v>19723968390.555576</v>
       </c>
       <c r="I28" s="120">
         <f t="shared" si="7"/>
-        <v>24604585779.246143</v>
+        <v>23022077932.184181</v>
       </c>
       <c r="J28" s="120">
         <f t="shared" si="7"/>
-        <v>28397370024.284248</v>
+        <v>26701316181.454308</v>
       </c>
       <c r="K28" s="120">
         <f t="shared" si="7"/>
-        <v>32689268407.271381</v>
+        <v>30872752279.552227</v>
       </c>
       <c r="L28" s="120">
         <f t="shared" si="7"/>
-        <v>37577767429.09478</v>
+        <v>35631749985.426491</v>
       </c>
       <c r="M28" s="120">
         <f t="shared" si="7"/>
-        <v>43118036043.742325</v>
+        <v>41034483822.60038</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A29" s="110">
         <f t="shared" si="1"/>
-        <v>4.3998777521911635E-2</v>
+        <v>2.9136529402797619E-2</v>
       </c>
       <c r="B29" s="122" t="s">
         <v>317</v>
       </c>
       <c r="D29" s="112">
         <f t="shared" ref="D29:M29" si="8">IF(D28&lt;0,0,D28*D5)</f>
-        <v>428988080.83863842</v>
+        <v>284081161.67727679</v>
       </c>
       <c r="E29" s="112">
         <f t="shared" si="8"/>
-        <v>4589917148.114378</v>
+        <v>4181414438.1143785</v>
       </c>
       <c r="F29" s="112">
         <f t="shared" si="8"/>
-        <v>5420811911.5230522</v>
+        <v>4978365641.3332129</v>
       </c>
       <c r="G29" s="112">
         <f t="shared" si="8"/>
-        <v>6359179801.2037363</v>
+        <v>5881270104.0804729</v>
       </c>
       <c r="H29" s="112">
         <f t="shared" si="8"/>
-        <v>7418434950.2063351</v>
+        <v>6903388936.6944513</v>
       </c>
       <c r="I29" s="112">
         <f t="shared" si="8"/>
-        <v>8611605022.7361488</v>
+        <v>8057727276.2644625</v>
       </c>
       <c r="J29" s="112">
         <f t="shared" si="8"/>
-        <v>9939079508.4994869</v>
+        <v>9345460663.5090065</v>
       </c>
       <c r="K29" s="112">
         <f t="shared" si="8"/>
-        <v>11441243942.544983</v>
+        <v>10805463297.843279</v>
       </c>
       <c r="L29" s="112">
         <f t="shared" si="8"/>
-        <v>13152218600.183172</v>
+        <v>12471112494.899271</v>
       </c>
       <c r="M29" s="112">
         <f t="shared" si="8"/>
-        <v>15091312615.309813</v>
+        <v>14362069337.910131</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A30" s="110">
         <f t="shared" si="1"/>
-        <v>8.1712015397835888E-2</v>
+        <v>5.4110697462338445E-2</v>
       </c>
       <c r="B30" s="124" t="s">
         <v>318</v>
@@ -16491,43 +16463,43 @@
       <c r="C30" s="107"/>
       <c r="D30" s="120">
         <f>D28-D29</f>
-        <v>796692150.12889993</v>
+        <v>527579300.2577998</v>
       </c>
       <c r="E30" s="120">
         <f t="shared" ref="E30:M30" si="9">E28-E29</f>
-        <v>8524131846.4981327</v>
+        <v>7765483956.4981327</v>
       </c>
       <c r="F30" s="120">
         <f t="shared" si="9"/>
-        <v>10067222121.399956</v>
+        <v>9245536191.0473976</v>
       </c>
       <c r="G30" s="120">
         <f t="shared" si="9"/>
-        <v>11809905345.092655</v>
+        <v>10922358764.720881</v>
       </c>
       <c r="H30" s="120">
         <f t="shared" si="9"/>
-        <v>13777093478.954622</v>
+        <v>12820579453.861126</v>
       </c>
       <c r="I30" s="120">
         <f t="shared" si="9"/>
-        <v>15992980756.509995</v>
+        <v>14964350655.91972</v>
       </c>
       <c r="J30" s="120">
         <f t="shared" si="9"/>
-        <v>18458290515.78476</v>
+        <v>17355855517.945301</v>
       </c>
       <c r="K30" s="120">
         <f t="shared" si="9"/>
-        <v>21248024464.726398</v>
+        <v>20067288981.708946</v>
       </c>
       <c r="L30" s="120">
         <f t="shared" si="9"/>
-        <v>24425548828.911606</v>
+        <v>23160637490.527222</v>
       </c>
       <c r="M30" s="120">
         <f t="shared" si="9"/>
-        <v>28026723428.43251</v>
+        <v>26672414484.690247</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.15">
@@ -16551,43 +16523,43 @@
       <c r="C32" s="107"/>
       <c r="D32" s="120">
         <f t="shared" ref="D32:M32" si="10">D26+D22+D23</f>
-        <v>2113250000</v>
+        <v>1787000000</v>
       </c>
       <c r="E32" s="120">
         <f t="shared" si="10"/>
-        <v>14082805800</v>
+        <v>12915655200</v>
       </c>
       <c r="F32" s="120">
         <f t="shared" si="10"/>
-        <v>16439236884.504004</v>
+        <v>15175104683.961605</v>
       </c>
       <c r="G32" s="120">
         <f t="shared" si="10"/>
-        <v>19102734044.070896</v>
+        <v>17737277766.575859</v>
       </c>
       <c r="H32" s="120">
         <f t="shared" si="10"/>
-        <v>22111623373.128967</v>
+        <v>20640063334.523586</v>
       </c>
       <c r="I32" s="120">
         <f t="shared" si="10"/>
-        <v>25503126769.407661</v>
+        <v>23920618922.345699</v>
       </c>
       <c r="J32" s="120">
         <f t="shared" si="10"/>
-        <v>29278357060.639275</v>
+        <v>27582303217.809334</v>
       </c>
       <c r="K32" s="120">
         <f t="shared" si="10"/>
-        <v>33552701489.819916</v>
+        <v>31736185362.100761</v>
       </c>
       <c r="L32" s="120">
         <f t="shared" si="10"/>
-        <v>38423646557.836823</v>
+        <v>36477629114.168533</v>
       </c>
       <c r="M32" s="120">
         <f t="shared" si="10"/>
-        <v>43939778486.000443</v>
+        <v>41856226264.858498</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.15">
@@ -16597,50 +16569,50 @@
     <row r="34" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A34" s="110">
         <f t="shared" si="1"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="B34" s="122" t="s">
         <v>320</v>
       </c>
       <c r="D34" s="112">
         <f>(Datos!$C$28/360)*'Estado de resultados'!D15</f>
-        <v>812500000</v>
+        <v>1625000000</v>
       </c>
       <c r="E34" s="112">
         <f>(Datos!$C$28/360)*'Estado de resultados'!E15</f>
-        <v>3038490000</v>
+        <v>6076980000</v>
       </c>
       <c r="F34" s="112">
         <f>(Datos!$C$28/360)*'Estado de resultados'!F15</f>
-        <v>3441102078.96</v>
+        <v>6882204157.9200001</v>
       </c>
       <c r="G34" s="112">
         <f>(Datos!$C$28/360)*'Estado de resultados'!G15</f>
-        <v>3887578191.5009027</v>
+        <v>7775156383.0018053</v>
       </c>
       <c r="H34" s="112">
         <f>(Datos!$C$28/360)*'Estado de resultados'!H15</f>
-        <v>4383329937.6374817</v>
+        <v>8766659875.2749634</v>
       </c>
       <c r="I34" s="112">
         <f>(Datos!$C$28/360)*'Estado de resultados'!I15</f>
-        <v>4933240594.9637918</v>
+        <v>9866481189.9275837</v>
       </c>
       <c r="J34" s="112">
         <f>(Datos!$C$28/360)*'Estado de resultados'!J15</f>
-        <v>5535145279.9553242</v>
+        <v>11070290559.910648</v>
       </c>
       <c r="K34" s="112">
         <f>(Datos!$C$28/360)*'Estado de resultados'!K15</f>
-        <v>6208434816.6638088</v>
+        <v>12416869633.327618</v>
       </c>
       <c r="L34" s="112">
         <f>(Datos!$C$28/360)*'Estado de resultados'!L15</f>
-        <v>6967900230.9166603</v>
+        <v>13935800461.833321</v>
       </c>
       <c r="M34" s="112">
         <f>(Datos!$C$28/360)*'Estado de resultados'!M15</f>
-        <v>7818792335.5152798</v>
+        <v>15637584671.03056</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="13" x14ac:dyDescent="0.15">
@@ -16650,141 +16622,141 @@
       </c>
       <c r="D35" s="112">
         <f>D34</f>
-        <v>812500000</v>
+        <v>1625000000</v>
       </c>
       <c r="E35" s="112">
         <f t="shared" ref="E35:M35" si="11">E34</f>
-        <v>3038490000</v>
+        <v>6076980000</v>
       </c>
       <c r="F35" s="112">
         <f t="shared" si="11"/>
-        <v>3441102078.96</v>
+        <v>6882204157.9200001</v>
       </c>
       <c r="G35" s="112">
         <f t="shared" si="11"/>
-        <v>3887578191.5009027</v>
+        <v>7775156383.0018053</v>
       </c>
       <c r="H35" s="112">
         <f t="shared" si="11"/>
-        <v>4383329937.6374817</v>
+        <v>8766659875.2749634</v>
       </c>
       <c r="I35" s="112">
         <f t="shared" si="11"/>
-        <v>4933240594.9637918</v>
+        <v>9866481189.9275837</v>
       </c>
       <c r="J35" s="112">
         <f t="shared" si="11"/>
-        <v>5535145279.9553242</v>
+        <v>11070290559.910648</v>
       </c>
       <c r="K35" s="112">
         <f t="shared" si="11"/>
-        <v>6208434816.6638088</v>
+        <v>12416869633.327618</v>
       </c>
       <c r="L35" s="112">
         <f t="shared" si="11"/>
-        <v>6967900230.9166603</v>
+        <v>13935800461.833321</v>
       </c>
       <c r="M35" s="112">
         <f t="shared" si="11"/>
-        <v>7818792335.5152798</v>
+        <v>15637584671.03056</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A36" s="110">
         <f t="shared" si="1"/>
-        <v>6.1538461538461542E-2</v>
+        <v>4.7435897435897434E-2</v>
       </c>
       <c r="B36" s="122" t="s">
         <v>322</v>
       </c>
       <c r="D36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!D16</f>
-        <v>600000000</v>
+        <v>462500000</v>
       </c>
       <c r="E36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!E16</f>
-        <v>2159136000</v>
+        <v>1664334000</v>
       </c>
       <c r="F36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!F16</f>
-        <v>2352957320.448</v>
+        <v>1813737934.5120001</v>
       </c>
       <c r="G36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!G16</f>
-        <v>2557937550.3761482</v>
+        <v>1971743528.4149475</v>
       </c>
       <c r="H36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!H16</f>
-        <v>2775295735.7818108</v>
+        <v>2139290462.9984794</v>
       </c>
       <c r="I36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!I16</f>
-        <v>3005603652.4156642</v>
+        <v>2316819482.0704079</v>
       </c>
       <c r="J36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!J16</f>
-        <v>3245060095.4036207</v>
+        <v>2501400490.2069578</v>
       </c>
       <c r="K36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!K16</f>
-        <v>3502435546.7503676</v>
+        <v>2699794067.2867417</v>
       </c>
       <c r="L36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!L16</f>
-        <v>3782546332.0372748</v>
+        <v>2915712797.6120663</v>
       </c>
       <c r="M36" s="112">
         <f>(Datos!$C$29/360)*'Estado de resultados'!M16</f>
-        <v>4084287618.0365524</v>
+        <v>3148305038.9031763</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="110">
         <f t="shared" si="1"/>
-        <v>4.3998777521911635E-2</v>
+        <v>2.9136529402797619E-2</v>
       </c>
       <c r="B37" s="122" t="s">
         <v>323</v>
       </c>
       <c r="D37" s="112">
         <f>D29</f>
-        <v>428988080.83863842</v>
+        <v>284081161.67727679</v>
       </c>
       <c r="E37" s="112">
         <f t="shared" ref="E37:M37" si="12">E29</f>
-        <v>4589917148.114378</v>
+        <v>4181414438.1143785</v>
       </c>
       <c r="F37" s="112">
         <f t="shared" si="12"/>
-        <v>5420811911.5230522</v>
+        <v>4978365641.3332129</v>
       </c>
       <c r="G37" s="112">
         <f t="shared" si="12"/>
-        <v>6359179801.2037363</v>
+        <v>5881270104.0804729</v>
       </c>
       <c r="H37" s="112">
         <f t="shared" si="12"/>
-        <v>7418434950.2063351</v>
+        <v>6903388936.6944513</v>
       </c>
       <c r="I37" s="112">
         <f t="shared" si="12"/>
-        <v>8611605022.7361488</v>
+        <v>8057727276.2644625</v>
       </c>
       <c r="J37" s="112">
         <f t="shared" si="12"/>
-        <v>9939079508.4994869</v>
+        <v>9345460663.5090065</v>
       </c>
       <c r="K37" s="112">
         <f t="shared" si="12"/>
-        <v>11441243942.544983</v>
+        <v>10805463297.843279</v>
       </c>
       <c r="L37" s="112">
         <f t="shared" si="12"/>
-        <v>13152218600.183172</v>
+        <v>12471112494.899271</v>
       </c>
       <c r="M37" s="112">
         <f t="shared" si="12"/>
-        <v>15091312615.309813</v>
+        <v>14362069337.910131</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="13" x14ac:dyDescent="0.15">
@@ -16795,43 +16767,43 @@
       <c r="C38" s="107"/>
       <c r="D38" s="120">
         <f>D35-D36-D37</f>
-        <v>-216488080.83863842</v>
+        <v>878418838.32272315</v>
       </c>
       <c r="E38" s="120">
         <f>E35-E36-E37</f>
-        <v>-3710563148.114378</v>
+        <v>231231561.88562155</v>
       </c>
       <c r="F38" s="120">
         <f t="shared" ref="F38:M38" si="13">F35-F36-F37</f>
-        <v>-4332667153.0110521</v>
+        <v>90100582.07478714</v>
       </c>
       <c r="G38" s="120">
         <f t="shared" si="13"/>
-        <v>-5029539160.0789814</v>
+        <v>-77857249.49361515</v>
       </c>
       <c r="H38" s="120">
         <f t="shared" si="13"/>
-        <v>-5810400748.3506641</v>
+        <v>-276019524.4179678</v>
       </c>
       <c r="I38" s="120">
         <f t="shared" si="13"/>
-        <v>-6683968080.1880207</v>
+        <v>-508065568.40728664</v>
       </c>
       <c r="J38" s="120">
         <f t="shared" si="13"/>
-        <v>-7648994323.9477835</v>
+        <v>-776570593.80531597</v>
       </c>
       <c r="K38" s="120">
         <f t="shared" si="13"/>
-        <v>-8735244672.6315422</v>
+        <v>-1088387731.8024025</v>
       </c>
       <c r="L38" s="120">
         <f t="shared" si="13"/>
-        <v>-9966864701.3037872</v>
+        <v>-1451024830.6780167</v>
       </c>
       <c r="M38" s="120">
         <f t="shared" si="13"/>
-        <v>-11356807897.831085</v>
+        <v>-1872789705.7827473</v>
       </c>
       <c r="O38" s="108" t="s">
         <v>325</v>
@@ -16848,43 +16820,43 @@
       <c r="C39" s="107"/>
       <c r="D39" s="120">
         <f>D38</f>
-        <v>-216488080.83863842</v>
+        <v>878418838.32272315</v>
       </c>
       <c r="E39" s="120">
         <f>E38-D38</f>
-        <v>-3494075067.2757397</v>
+        <v>-647187276.4371016</v>
       </c>
       <c r="F39" s="120">
         <f t="shared" ref="F39:M39" si="14">F38-E38</f>
-        <v>-622104004.89667416</v>
+        <v>-141130979.81083441</v>
       </c>
       <c r="G39" s="120">
         <f t="shared" si="14"/>
-        <v>-696872007.06792927</v>
+        <v>-167957831.56840229</v>
       </c>
       <c r="H39" s="120">
         <f t="shared" si="14"/>
-        <v>-780861588.27168274</v>
+        <v>-198162274.92435265</v>
       </c>
       <c r="I39" s="120">
         <f t="shared" si="14"/>
-        <v>-873567331.83735657</v>
+        <v>-232046043.98931885</v>
       </c>
       <c r="J39" s="120">
         <f t="shared" si="14"/>
-        <v>-965026243.75976276</v>
+        <v>-268505025.39802933</v>
       </c>
       <c r="K39" s="120">
         <f t="shared" si="14"/>
-        <v>-1086250348.6837587</v>
+        <v>-311817137.99708652</v>
       </c>
       <c r="L39" s="120">
         <f t="shared" si="14"/>
-        <v>-1231620028.672245</v>
+        <v>-362637098.87561417</v>
       </c>
       <c r="M39" s="120">
         <f t="shared" si="14"/>
-        <v>-1389943196.527298</v>
+        <v>-421764875.10473061</v>
       </c>
       <c r="O39" s="108" t="s">
         <v>327</v>
@@ -17100,43 +17072,43 @@
       <c r="C45" s="107"/>
       <c r="D45" s="120">
         <f>D43+D38</f>
-        <v>12983711919.161362</v>
+        <v>14078618838.322723</v>
       </c>
       <c r="E45" s="120">
         <f>E43+E38</f>
-        <v>8689836851.885622</v>
+        <v>12631631561.885622</v>
       </c>
       <c r="F45" s="120">
         <f t="shared" ref="F45:L45" si="18">F43+F38</f>
-        <v>7267932846.9889479</v>
+        <v>11690700582.074787</v>
       </c>
       <c r="G45" s="120">
         <f t="shared" si="18"/>
-        <v>5771260839.9210186</v>
+        <v>10722942750.506386</v>
       </c>
       <c r="H45" s="120">
         <f t="shared" si="18"/>
-        <v>4190599251.6493359</v>
+        <v>9724980475.5820312</v>
       </c>
       <c r="I45" s="120">
         <f t="shared" si="18"/>
-        <v>2517231919.8119793</v>
+        <v>8693134431.5927124</v>
       </c>
       <c r="J45" s="120">
         <f t="shared" si="18"/>
-        <v>752405676.05221653</v>
+        <v>7624829406.194684</v>
       </c>
       <c r="K45" s="120">
         <f t="shared" si="18"/>
-        <v>-1133644672.6315422</v>
+        <v>6513212268.1975975</v>
       </c>
       <c r="L45" s="120">
         <f t="shared" si="18"/>
-        <v>-3165064701.3037872</v>
+        <v>5350775169.3219833</v>
       </c>
       <c r="M45" s="120">
         <f>M43+M38</f>
-        <v>-5354807897.8310852</v>
+        <v>4129210294.2172527</v>
       </c>
       <c r="O45" s="108" t="s">
         <v>335</v>
@@ -17223,43 +17195,43 @@
       <c r="C49" s="112"/>
       <c r="D49" s="112">
         <f>D26</f>
-        <v>1313450000</v>
+        <v>987200000</v>
       </c>
       <c r="E49" s="112">
         <f t="shared" ref="E49:M49" si="19">E26</f>
-        <v>13283005800</v>
+        <v>12115855200</v>
       </c>
       <c r="F49" s="112">
         <f t="shared" si="19"/>
-        <v>15639436884.504004</v>
+        <v>14375304683.961605</v>
       </c>
       <c r="G49" s="112">
         <f t="shared" si="19"/>
-        <v>18302934044.070896</v>
+        <v>16937477766.575857</v>
       </c>
       <c r="H49" s="112">
         <f t="shared" si="19"/>
-        <v>21311823373.128967</v>
+        <v>19840263334.523586</v>
       </c>
       <c r="I49" s="112">
         <f t="shared" si="19"/>
-        <v>24703326769.407661</v>
+        <v>23120818922.345699</v>
       </c>
       <c r="J49" s="112">
         <f t="shared" si="19"/>
-        <v>28478557060.639275</v>
+        <v>26782503217.809334</v>
       </c>
       <c r="K49" s="112">
         <f t="shared" si="19"/>
-        <v>32752901489.819916</v>
+        <v>30936385362.100761</v>
       </c>
       <c r="L49" s="112">
         <f t="shared" si="19"/>
-        <v>37623846557.836823</v>
+        <v>35677829114.168533</v>
       </c>
       <c r="M49" s="112">
         <f t="shared" si="19"/>
-        <v>43139978486.000443</v>
+        <v>41056426264.858498</v>
       </c>
       <c r="O49" s="108" t="s">
         <v>339</v>
@@ -17276,43 +17248,43 @@
       <c r="C50" s="112"/>
       <c r="D50" s="112">
         <f t="shared" ref="D50:M50" si="20">IF(D49&lt;0,0,D49*D5)</f>
-        <v>459707500</v>
+        <v>345520000</v>
       </c>
       <c r="E50" s="112">
         <f t="shared" si="20"/>
-        <v>4649052030</v>
+        <v>4240549319.9999995</v>
       </c>
       <c r="F50" s="112">
         <f t="shared" si="20"/>
-        <v>5473802909.5764008</v>
+        <v>5031356639.3865614</v>
       </c>
       <c r="G50" s="112">
         <f t="shared" si="20"/>
-        <v>6406026915.4248133</v>
+        <v>5928117218.3015499</v>
       </c>
       <c r="H50" s="112">
         <f t="shared" si="20"/>
-        <v>7459138180.5951385</v>
+        <v>6944092167.0832548</v>
       </c>
       <c r="I50" s="112">
         <f t="shared" si="20"/>
-        <v>8646164369.2926807</v>
+        <v>8092286622.8209944</v>
       </c>
       <c r="J50" s="112">
         <f t="shared" si="20"/>
-        <v>9967494971.2237453</v>
+        <v>9373876126.2332668</v>
       </c>
       <c r="K50" s="112">
         <f t="shared" si="20"/>
-        <v>11463515521.43697</v>
+        <v>10827734876.735266</v>
       </c>
       <c r="L50" s="112">
         <f t="shared" si="20"/>
-        <v>13168346295.242887</v>
+        <v>12487240189.958986</v>
       </c>
       <c r="M50" s="112">
         <f t="shared" si="20"/>
-        <v>15098992470.100153</v>
+        <v>14369749192.700474</v>
       </c>
     </row>
     <row r="51" spans="2:16" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.15">
@@ -17322,43 +17294,43 @@
       <c r="C51" s="120"/>
       <c r="D51" s="120">
         <f>D49-D50</f>
-        <v>853742500</v>
+        <v>641680000</v>
       </c>
       <c r="E51" s="120">
         <f t="shared" ref="E51:M51" si="21">E49-E50</f>
-        <v>8633953770</v>
+        <v>7875305880</v>
       </c>
       <c r="F51" s="120">
         <f t="shared" si="21"/>
-        <v>10165633974.927603</v>
+        <v>9343948044.5750427</v>
       </c>
       <c r="G51" s="120">
         <f t="shared" si="21"/>
-        <v>11896907128.646084</v>
+        <v>11009360548.274307</v>
       </c>
       <c r="H51" s="120">
         <f t="shared" si="21"/>
-        <v>13852685192.533829</v>
+        <v>12896171167.440331</v>
       </c>
       <c r="I51" s="120">
         <f t="shared" si="21"/>
-        <v>16057162400.114981</v>
+        <v>15028532299.524704</v>
       </c>
       <c r="J51" s="120">
         <f t="shared" si="21"/>
-        <v>18511062089.415527</v>
+        <v>17408627091.576065</v>
       </c>
       <c r="K51" s="120">
         <f t="shared" si="21"/>
-        <v>21289385968.382946</v>
+        <v>20108650485.365494</v>
       </c>
       <c r="L51" s="120">
         <f t="shared" si="21"/>
-        <v>24455500262.593933</v>
+        <v>23190588924.209549</v>
       </c>
       <c r="M51" s="120">
         <f t="shared" si="21"/>
-        <v>28040986015.900291</v>
+        <v>26686677072.158024</v>
       </c>
     </row>
     <row r="52" spans="2:16" ht="13" x14ac:dyDescent="0.15">
@@ -17424,43 +17396,43 @@
       <c r="C54" s="120"/>
       <c r="D54" s="120">
         <f t="shared" ref="D54:M54" si="22">D51+D52+D53</f>
-        <v>1653542500</v>
+        <v>1441480000</v>
       </c>
       <c r="E54" s="120">
         <f t="shared" si="22"/>
-        <v>9433753770</v>
+        <v>8675105880</v>
       </c>
       <c r="F54" s="120">
         <f t="shared" si="22"/>
-        <v>10965433974.927603</v>
+        <v>10143748044.575043</v>
       </c>
       <c r="G54" s="120">
         <f t="shared" si="22"/>
-        <v>12696707128.646084</v>
+        <v>11809160548.274307</v>
       </c>
       <c r="H54" s="120">
         <f t="shared" si="22"/>
-        <v>14652485192.533829</v>
+        <v>13695971167.440331</v>
       </c>
       <c r="I54" s="120">
         <f t="shared" si="22"/>
-        <v>16856962400.114981</v>
+        <v>15828332299.524704</v>
       </c>
       <c r="J54" s="120">
         <f t="shared" si="22"/>
-        <v>19310862089.415527</v>
+        <v>18208427091.576065</v>
       </c>
       <c r="K54" s="120">
         <f t="shared" si="22"/>
-        <v>22089185968.382946</v>
+        <v>20908450485.365494</v>
       </c>
       <c r="L54" s="120">
         <f t="shared" si="22"/>
-        <v>25255300262.593933</v>
+        <v>23990388924.209549</v>
       </c>
       <c r="M54" s="120">
         <f t="shared" si="22"/>
-        <v>28840786015.900291</v>
+        <v>27486477072.158024</v>
       </c>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.15">
@@ -17539,43 +17511,43 @@
       <c r="C58" s="107"/>
       <c r="D58" s="137">
         <f t="shared" ref="D58:M58" si="23">D32</f>
-        <v>2113250000</v>
+        <v>1787000000</v>
       </c>
       <c r="E58" s="137">
         <f t="shared" si="23"/>
-        <v>14082805800</v>
+        <v>12915655200</v>
       </c>
       <c r="F58" s="137">
         <f t="shared" si="23"/>
-        <v>16439236884.504004</v>
+        <v>15175104683.961605</v>
       </c>
       <c r="G58" s="137">
         <f t="shared" si="23"/>
-        <v>19102734044.070896</v>
+        <v>17737277766.575859</v>
       </c>
       <c r="H58" s="137">
         <f t="shared" si="23"/>
-        <v>22111623373.128967</v>
+        <v>20640063334.523586</v>
       </c>
       <c r="I58" s="137">
         <f t="shared" si="23"/>
-        <v>25503126769.407661</v>
+        <v>23920618922.345699</v>
       </c>
       <c r="J58" s="137">
         <f t="shared" si="23"/>
-        <v>29278357060.639275</v>
+        <v>27582303217.809334</v>
       </c>
       <c r="K58" s="137">
         <f t="shared" si="23"/>
-        <v>33552701489.819916</v>
+        <v>31736185362.100761</v>
       </c>
       <c r="L58" s="137">
         <f t="shared" si="23"/>
-        <v>38423646557.836823</v>
+        <v>36477629114.168533</v>
       </c>
       <c r="M58" s="137">
         <f t="shared" si="23"/>
-        <v>43939778486.000443</v>
+        <v>41856226264.858498</v>
       </c>
       <c r="N58" s="107"/>
     </row>
@@ -17586,43 +17558,43 @@
       <c r="C59" s="107"/>
       <c r="D59" s="137">
         <f t="shared" ref="D59:M59" si="24">D50</f>
-        <v>459707500</v>
+        <v>345520000</v>
       </c>
       <c r="E59" s="137">
         <f t="shared" si="24"/>
-        <v>4649052030</v>
+        <v>4240549319.9999995</v>
       </c>
       <c r="F59" s="137">
         <f t="shared" si="24"/>
-        <v>5473802909.5764008</v>
+        <v>5031356639.3865614</v>
       </c>
       <c r="G59" s="137">
         <f t="shared" si="24"/>
-        <v>6406026915.4248133</v>
+        <v>5928117218.3015499</v>
       </c>
       <c r="H59" s="137">
         <f t="shared" si="24"/>
-        <v>7459138180.5951385</v>
+        <v>6944092167.0832548</v>
       </c>
       <c r="I59" s="137">
         <f t="shared" si="24"/>
-        <v>8646164369.2926807</v>
+        <v>8092286622.8209944</v>
       </c>
       <c r="J59" s="137">
         <f t="shared" si="24"/>
-        <v>9967494971.2237453</v>
+        <v>9373876126.2332668</v>
       </c>
       <c r="K59" s="137">
         <f t="shared" si="24"/>
-        <v>11463515521.43697</v>
+        <v>10827734876.735266</v>
       </c>
       <c r="L59" s="137">
         <f t="shared" si="24"/>
-        <v>13168346295.242887</v>
+        <v>12487240189.958986</v>
       </c>
       <c r="M59" s="137">
         <f t="shared" si="24"/>
-        <v>15098992470.100153</v>
+        <v>14369749192.700474</v>
       </c>
       <c r="N59" s="107"/>
     </row>
@@ -17632,43 +17604,43 @@
       </c>
       <c r="D60" s="138">
         <f>D58-D59</f>
-        <v>1653542500</v>
+        <v>1441480000</v>
       </c>
       <c r="E60" s="138">
         <f t="shared" ref="E60:M60" si="25">E58-E59</f>
-        <v>9433753770</v>
+        <v>8675105880</v>
       </c>
       <c r="F60" s="138">
         <f t="shared" si="25"/>
-        <v>10965433974.927603</v>
+        <v>10143748044.575043</v>
       </c>
       <c r="G60" s="138">
         <f t="shared" si="25"/>
-        <v>12696707128.646084</v>
+        <v>11809160548.274309</v>
       </c>
       <c r="H60" s="138">
         <f t="shared" si="25"/>
-        <v>14652485192.533829</v>
+        <v>13695971167.440331</v>
       </c>
       <c r="I60" s="138">
         <f t="shared" si="25"/>
-        <v>16856962400.114981</v>
+        <v>15828332299.524704</v>
       </c>
       <c r="J60" s="138">
         <f t="shared" si="25"/>
-        <v>19310862089.415527</v>
+        <v>18208427091.576065</v>
       </c>
       <c r="K60" s="138">
         <f t="shared" si="25"/>
-        <v>22089185968.382946</v>
+        <v>20908450485.365494</v>
       </c>
       <c r="L60" s="138">
         <f t="shared" si="25"/>
-        <v>25255300262.593933</v>
+        <v>23990388924.209549</v>
       </c>
       <c r="M60" s="138">
         <f t="shared" si="25"/>
-        <v>28840786015.900291</v>
+        <v>27486477072.158024</v>
       </c>
     </row>
     <row r="61" spans="2:16" ht="13" x14ac:dyDescent="0.15">
@@ -17678,43 +17650,43 @@
       <c r="C61" s="112"/>
       <c r="D61" s="112">
         <f t="shared" ref="D61:M61" si="26">-D39</f>
-        <v>216488080.83863842</v>
+        <v>-878418838.32272315</v>
       </c>
       <c r="E61" s="112">
         <f t="shared" si="26"/>
-        <v>3494075067.2757397</v>
+        <v>647187276.4371016</v>
       </c>
       <c r="F61" s="112">
         <f t="shared" si="26"/>
-        <v>622104004.89667416</v>
+        <v>141130979.81083441</v>
       </c>
       <c r="G61" s="112">
         <f t="shared" si="26"/>
-        <v>696872007.06792927</v>
+        <v>167957831.56840229</v>
       </c>
       <c r="H61" s="112">
         <f t="shared" si="26"/>
-        <v>780861588.27168274</v>
+        <v>198162274.92435265</v>
       </c>
       <c r="I61" s="112">
         <f t="shared" si="26"/>
-        <v>873567331.83735657</v>
+        <v>232046043.98931885</v>
       </c>
       <c r="J61" s="112">
         <f t="shared" si="26"/>
-        <v>965026243.75976276</v>
+        <v>268505025.39802933</v>
       </c>
       <c r="K61" s="112">
         <f t="shared" si="26"/>
-        <v>1086250348.6837587</v>
+        <v>311817137.99708652</v>
       </c>
       <c r="L61" s="112">
         <f t="shared" si="26"/>
-        <v>1231620028.672245</v>
+        <v>362637098.87561417</v>
       </c>
       <c r="M61" s="112">
         <f t="shared" si="26"/>
-        <v>1389943196.527298</v>
+        <v>421764875.10473061</v>
       </c>
     </row>
     <row r="62" spans="2:16" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.15">
@@ -17724,43 +17696,43 @@
       <c r="C62" s="120"/>
       <c r="D62" s="120">
         <f>D60+D61</f>
-        <v>1870030580.8386383</v>
+        <v>563061161.67727685</v>
       </c>
       <c r="E62" s="120">
         <f>E54+E61</f>
-        <v>12927828837.27574</v>
+        <v>9322293156.4371014</v>
       </c>
       <c r="F62" s="120">
         <f>F54+F61</f>
-        <v>11587537979.824276</v>
+        <v>10284879024.385878</v>
       </c>
       <c r="G62" s="120">
         <f>G54+G61</f>
-        <v>13393579135.714012</v>
+        <v>11977118379.842709</v>
       </c>
       <c r="H62" s="120">
         <f t="shared" ref="H62:M62" si="27">H54+H61</f>
-        <v>15433346780.805511</v>
+        <v>13894133442.364683</v>
       </c>
       <c r="I62" s="120">
         <f t="shared" si="27"/>
-        <v>17730529731.952339</v>
+        <v>16060378343.514023</v>
       </c>
       <c r="J62" s="120">
         <f t="shared" si="27"/>
-        <v>20275888333.175289</v>
+        <v>18476932116.974094</v>
       </c>
       <c r="K62" s="120">
         <f t="shared" si="27"/>
-        <v>23175436317.066704</v>
+        <v>21220267623.362579</v>
       </c>
       <c r="L62" s="120">
         <f t="shared" si="27"/>
-        <v>26486920291.266178</v>
+        <v>24353026023.085163</v>
       </c>
       <c r="M62" s="120">
         <f t="shared" si="27"/>
-        <v>30230729212.427589</v>
+        <v>27908241947.262756</v>
       </c>
     </row>
     <row r="63" spans="2:16" ht="13" x14ac:dyDescent="0.15">
@@ -17813,43 +17785,43 @@
       </c>
       <c r="D64" s="120">
         <f>D62+D63</f>
-        <v>1870030580.8386383</v>
+        <v>563061161.67727685</v>
       </c>
       <c r="E64" s="120">
         <f t="shared" ref="E64:L64" si="28">E62+E63</f>
-        <v>12927828837.27574</v>
+        <v>9322293156.4371014</v>
       </c>
       <c r="F64" s="120">
         <f>F62+F63</f>
-        <v>11587537979.824276</v>
+        <v>10284879024.385878</v>
       </c>
       <c r="G64" s="120">
         <f>G62+G63</f>
-        <v>13393579135.714012</v>
+        <v>11977118379.842709</v>
       </c>
       <c r="H64" s="120">
         <f>H62+H63</f>
-        <v>5633346780.8055115</v>
+        <v>4094133442.3646832</v>
       </c>
       <c r="I64" s="120">
         <f t="shared" si="28"/>
-        <v>17730529731.952339</v>
+        <v>16060378343.514023</v>
       </c>
       <c r="J64" s="120">
         <f t="shared" si="28"/>
-        <v>20275888333.175289</v>
+        <v>18476932116.974094</v>
       </c>
       <c r="K64" s="120">
         <f t="shared" si="28"/>
-        <v>23175436317.066704</v>
+        <v>21220267623.362579</v>
       </c>
       <c r="L64" s="120">
         <f t="shared" si="28"/>
-        <v>26486920291.266178</v>
+        <v>24353026023.085163</v>
       </c>
       <c r="M64" s="120">
         <f>M62+M63</f>
-        <v>30230729212.427589</v>
+        <v>27908241947.262756</v>
       </c>
       <c r="N64" s="121">
         <f>P49</f>
@@ -17916,159 +17888,111 @@
       </c>
       <c r="D66" s="112">
         <f t="shared" ref="D66:N66" si="29">D64*D65</f>
-        <v>1553326230.0031278</v>
+        <v>467702336.25650817</v>
       </c>
       <c r="E66" s="112">
         <f t="shared" si="29"/>
-        <v>8919767370.884388</v>
+        <v>6432068939.437561</v>
       </c>
       <c r="F66" s="112">
         <f t="shared" si="29"/>
-        <v>6640993764.863471</v>
+        <v>5894420160.0241489</v>
       </c>
       <c r="G66" s="112">
         <f t="shared" si="29"/>
-        <v>6376061791.1550627</v>
+        <v>5701750525.0873337</v>
       </c>
       <c r="H66" s="112">
         <f t="shared" si="29"/>
-        <v>2227595454.6669092</v>
+        <v>1618944013.5455811</v>
       </c>
       <c r="I66" s="112">
         <f t="shared" si="29"/>
-        <v>5823787432.1151438</v>
+        <v>5275207845.7879324</v>
       </c>
       <c r="J66" s="112">
         <f t="shared" si="29"/>
-        <v>5531942556.5241737</v>
+        <v>5041126949.0302162</v>
       </c>
       <c r="K66" s="112">
         <f t="shared" si="29"/>
-        <v>5252180676.6852341</v>
+        <v>4809086570.8292618</v>
       </c>
       <c r="L66" s="112">
         <f t="shared" si="29"/>
-        <v>4986056210.1047745</v>
+        <v>4584359196.9915028</v>
       </c>
       <c r="M66" s="112">
         <f t="shared" si="29"/>
-        <v>4727029319.8087358</v>
+        <v>4363873495.1452866</v>
       </c>
       <c r="N66" s="112">
         <f t="shared" si="29"/>
         <v>354581674.98952663</v>
       </c>
     </row>
-    <row r="67" spans="2:14" ht="13" x14ac:dyDescent="0.15">
-      <c r="B67" s="122" t="s">
-        <v>374</v>
-      </c>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.15">
       <c r="C67" s="137"/>
-      <c r="D67" s="112">
-        <f>D91</f>
-        <v>8400000000</v>
-      </c>
-      <c r="E67" s="112">
-        <f>E91-D91</f>
-        <v>-840000000</v>
-      </c>
-      <c r="F67" s="112">
-        <f t="shared" ref="F67:M67" si="30">F91-E91</f>
-        <v>-840000000</v>
-      </c>
-      <c r="G67" s="112">
-        <f t="shared" si="30"/>
-        <v>-840000000</v>
-      </c>
-      <c r="H67" s="112">
-        <f t="shared" si="30"/>
-        <v>-840000000</v>
-      </c>
-      <c r="I67" s="112">
-        <f t="shared" si="30"/>
-        <v>-840000000</v>
-      </c>
-      <c r="J67" s="112">
-        <f t="shared" si="30"/>
-        <v>-840000000</v>
-      </c>
-      <c r="K67" s="112">
-        <f t="shared" si="30"/>
-        <v>-840000000</v>
-      </c>
-      <c r="L67" s="112">
-        <f t="shared" si="30"/>
-        <v>-840000000</v>
-      </c>
-      <c r="M67" s="112">
-        <f t="shared" si="30"/>
-        <v>-1680000000</v>
-      </c>
+      <c r="D67" s="112"/>
+      <c r="E67" s="112"/>
+      <c r="F67" s="112"/>
+      <c r="G67" s="112"/>
+      <c r="H67" s="112"/>
+      <c r="I67" s="112"/>
+      <c r="J67" s="112"/>
+      <c r="K67" s="112"/>
+      <c r="L67" s="112"/>
+      <c r="M67" s="112"/>
       <c r="N67" s="112"/>
     </row>
     <row r="68" spans="2:14" ht="13" x14ac:dyDescent="0.15">
-      <c r="B68" s="156" t="s">
-        <v>375</v>
-      </c>
-      <c r="C68" s="137"/>
-      <c r="D68" s="112">
-        <f>D64+D67-D27*(1-D5)</f>
-        <v>10212980230.967539</v>
-      </c>
-      <c r="E68" s="112">
-        <f t="shared" ref="E68:M68" si="31">E64+E67-E27*(1-E5)</f>
-        <v>11978006913.773872</v>
-      </c>
-      <c r="F68" s="112">
-        <f t="shared" si="31"/>
-        <v>10649126126.296629</v>
-      </c>
-      <c r="G68" s="112">
-        <f t="shared" si="31"/>
-        <v>12466577352.160585</v>
-      </c>
-      <c r="H68" s="112">
-        <f t="shared" si="31"/>
-        <v>4717755067.2263041</v>
-      </c>
-      <c r="I68" s="112">
-        <f t="shared" si="31"/>
-        <v>16826348088.347351</v>
-      </c>
-      <c r="J68" s="112">
-        <f t="shared" si="31"/>
-        <v>19383116759.544521</v>
-      </c>
-      <c r="K68" s="112">
-        <f t="shared" si="31"/>
-        <v>22294074813.410156</v>
-      </c>
-      <c r="L68" s="112">
-        <f t="shared" si="31"/>
-        <v>25616968857.583851</v>
-      </c>
-      <c r="M68" s="112">
-        <f t="shared" si="31"/>
-        <v>28536466624.959816</v>
-      </c>
-      <c r="N68" s="112"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="C69" s="137"/>
-      <c r="D69" s="110"/>
-      <c r="E69" s="110"/>
-      <c r="F69" s="110"/>
-      <c r="G69" s="110"/>
-      <c r="H69" s="110"/>
-      <c r="I69" s="110"/>
-      <c r="J69" s="110"/>
-      <c r="K69" s="110"/>
-      <c r="L69" s="110"/>
-      <c r="M69" s="110"/>
-      <c r="N69" s="112"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="C70" s="137"/>
+      <c r="B68" s="140" t="s">
+        <v>349</v>
+      </c>
+      <c r="C68" s="141">
+        <f>NPV(WACC!B18,'Estado de resultados'!D64:N64)+'Estado de resultados'!C64</f>
+        <v>30543121707.124863</v>
+      </c>
+      <c r="D68" s="112"/>
+      <c r="E68" s="112"/>
+      <c r="F68" s="112"/>
+      <c r="G68" s="112"/>
+      <c r="H68" s="112"/>
+      <c r="I68" s="112"/>
+      <c r="J68" s="112"/>
+      <c r="K68" s="112"/>
+      <c r="L68" s="112"/>
+      <c r="M68" s="112"/>
+      <c r="N68" s="117"/>
+    </row>
+    <row r="69" spans="2:14" ht="13" x14ac:dyDescent="0.15">
+      <c r="B69" s="142" t="s">
+        <v>373</v>
+      </c>
+      <c r="C69" s="144">
+        <f>C68-'Costo de oportunidad'!B18</f>
+        <v>27743121707.124863</v>
+      </c>
+      <c r="D69" s="112"/>
+      <c r="E69" s="112"/>
+      <c r="F69" s="112"/>
+      <c r="G69" s="112"/>
+      <c r="H69" s="112"/>
+      <c r="I69" s="112"/>
+      <c r="J69" s="112"/>
+      <c r="K69" s="112"/>
+      <c r="L69" s="112"/>
+      <c r="M69" s="112"/>
+      <c r="N69" s="117"/>
+    </row>
+    <row r="70" spans="2:14" ht="13" x14ac:dyDescent="0.15">
+      <c r="B70" s="142" t="s">
+        <v>350</v>
+      </c>
+      <c r="C70" s="143">
+        <f>MIRR(C64:N64,WACC!B18,WACC!B18)</f>
+        <v>0.33746284156373307</v>
+      </c>
       <c r="D70" s="112"/>
       <c r="E70" s="112"/>
       <c r="F70" s="112"/>
@@ -18079,623 +18003,583 @@
       <c r="K70" s="112"/>
       <c r="L70" s="112"/>
       <c r="M70" s="112"/>
-      <c r="N70" s="112"/>
-    </row>
-    <row r="71" spans="2:14" ht="13" x14ac:dyDescent="0.15">
-      <c r="B71" s="140" t="s">
-        <v>349</v>
-      </c>
-      <c r="C71" s="141">
-        <f>NPV(WACC!B18,'Estado de resultados'!D64:N64)+'Estado de resultados'!C64</f>
-        <v>38393322481.800545</v>
-      </c>
-      <c r="D71" s="112"/>
-      <c r="E71" s="112"/>
-      <c r="F71" s="112"/>
-      <c r="G71" s="112"/>
-      <c r="H71" s="112"/>
-      <c r="I71" s="112"/>
-      <c r="J71" s="112"/>
-      <c r="K71" s="112"/>
-      <c r="L71" s="112"/>
-      <c r="M71" s="112"/>
-      <c r="N71" s="117"/>
+      <c r="N70" s="117"/>
+    </row>
+    <row r="71" spans="2:14" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+      <c r="B71" s="142" t="s">
+        <v>351</v>
+      </c>
+      <c r="C71" s="153">
+        <f>2+ABS(SUM(C66:E66))/F66</f>
+        <v>3.2045677999779443</v>
+      </c>
+      <c r="D71" s="120"/>
+      <c r="E71" s="120"/>
+      <c r="F71" s="120"/>
+      <c r="G71" s="120"/>
+      <c r="H71" s="120"/>
+      <c r="I71" s="120"/>
+      <c r="J71" s="120"/>
+      <c r="K71" s="120"/>
+      <c r="L71" s="120"/>
+      <c r="M71" s="120"/>
+      <c r="N71" s="121"/>
     </row>
     <row r="72" spans="2:14" ht="13" x14ac:dyDescent="0.15">
-      <c r="B72" s="142" t="s">
-        <v>350</v>
-      </c>
-      <c r="C72" s="143">
-        <f>MIRR(C64:N64,WACC!B18,WACC!B18)</f>
-        <v>0.35734543802520369</v>
-      </c>
-      <c r="D72" s="112"/>
-      <c r="E72" s="112"/>
-      <c r="F72" s="112"/>
-      <c r="G72" s="112"/>
-      <c r="H72" s="112"/>
-      <c r="I72" s="112"/>
-      <c r="J72" s="112"/>
-      <c r="K72" s="112"/>
-      <c r="L72" s="112"/>
-      <c r="M72" s="112"/>
-      <c r="N72" s="117"/>
+      <c r="B72" s="145" t="s">
+        <v>352</v>
+      </c>
+      <c r="C72" s="146"/>
     </row>
     <row r="73" spans="2:14" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.15">
-      <c r="B73" s="142" t="s">
-        <v>351</v>
-      </c>
-      <c r="C73" s="155">
-        <f>2+ABS(SUM(C66:E66))/F66</f>
-        <v>2.5310811188790496</v>
-      </c>
-      <c r="D73" s="120"/>
-      <c r="E73" s="120"/>
-      <c r="F73" s="120"/>
-      <c r="G73" s="120"/>
-      <c r="H73" s="120"/>
-      <c r="I73" s="120"/>
-      <c r="J73" s="120"/>
-      <c r="K73" s="120"/>
-      <c r="L73" s="120"/>
-      <c r="M73" s="120"/>
-      <c r="N73" s="121"/>
-    </row>
-    <row r="74" spans="2:14" ht="13" x14ac:dyDescent="0.15">
-      <c r="B74" s="145" t="s">
-        <v>352</v>
-      </c>
-      <c r="C74" s="146"/>
-    </row>
-    <row r="75" spans="2:14" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.15">
-      <c r="B75" s="145" t="s">
+      <c r="B73" s="145" t="s">
         <v>353</v>
       </c>
-      <c r="C75" s="146"/>
-    </row>
-    <row r="76" spans="2:14" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.15">
-      <c r="B76" s="147" t="s">
+      <c r="C73" s="146"/>
+    </row>
+    <row r="74" spans="2:14" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+      <c r="B74" s="147" t="s">
         <v>354</v>
       </c>
-      <c r="C76" s="148">
+      <c r="C74" s="148">
         <f>ABS(SUM(D66:N66)/C64)</f>
-        <v>3.742380177271468</v>
-      </c>
-      <c r="D76" s="120"/>
-      <c r="E76" s="120"/>
-      <c r="F76" s="120"/>
-      <c r="G76" s="120"/>
-      <c r="H76" s="120"/>
-      <c r="I76" s="120"/>
-      <c r="J76" s="120"/>
-      <c r="K76" s="120"/>
-      <c r="L76" s="120"/>
-      <c r="M76" s="120"/>
+        <v>3.181651550508918</v>
+      </c>
+      <c r="D74" s="120"/>
+      <c r="E74" s="120"/>
+      <c r="F74" s="120"/>
+      <c r="G74" s="120"/>
+      <c r="H74" s="120"/>
+      <c r="I74" s="120"/>
+      <c r="J74" s="120"/>
+      <c r="K74" s="120"/>
+      <c r="L74" s="120"/>
+      <c r="M74" s="120"/>
+    </row>
+    <row r="77" spans="2:14" ht="13" x14ac:dyDescent="0.15">
+      <c r="B77" s="122" t="s">
+        <v>355</v>
+      </c>
+      <c r="D77" s="116">
+        <f t="shared" ref="D77:M77" si="30">D51/D45</f>
+        <v>4.5578334591551986E-2</v>
+      </c>
+      <c r="E77" s="116">
+        <f t="shared" si="30"/>
+        <v>0.62345911859579217</v>
+      </c>
+      <c r="F77" s="116">
+        <f t="shared" si="30"/>
+        <v>0.79926331009640328</v>
+      </c>
+      <c r="G77" s="116">
+        <f t="shared" si="30"/>
+        <v>1.0267107457749316</v>
+      </c>
+      <c r="H77" s="116">
+        <f t="shared" si="30"/>
+        <v>1.3260871011330753</v>
+      </c>
+      <c r="I77" s="116">
+        <f t="shared" si="30"/>
+        <v>1.7287817665522114</v>
+      </c>
+      <c r="J77" s="116">
+        <f t="shared" si="30"/>
+        <v>2.2831497157736638</v>
+      </c>
+      <c r="K77" s="116">
+        <f t="shared" si="30"/>
+        <v>3.0873629873159598</v>
+      </c>
+      <c r="L77" s="116">
+        <f t="shared" si="30"/>
+        <v>4.3340615500292294</v>
+      </c>
+      <c r="M77" s="116">
+        <f t="shared" si="30"/>
+        <v>6.4629009352057816</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14" ht="13" x14ac:dyDescent="0.15">
+      <c r="B78" s="122" t="s">
+        <v>356</v>
+      </c>
+      <c r="D78" s="116">
+        <f t="shared" ref="D78:M78" si="31">D19/D15</f>
+        <v>0.62961538461538458</v>
+      </c>
+      <c r="E78" s="116">
+        <f t="shared" si="31"/>
+        <v>0.66241654571843256</v>
+      </c>
+      <c r="F78" s="116">
+        <f t="shared" si="31"/>
+        <v>0.673244379330175</v>
+      </c>
+      <c r="G78" s="116">
+        <f t="shared" si="31"/>
+        <v>0.68365431504892271</v>
+      </c>
+      <c r="H78" s="116">
+        <f t="shared" si="31"/>
+        <v>0.69366264904412145</v>
+      </c>
+      <c r="I78" s="116">
+        <f t="shared" si="31"/>
+        <v>0.70328503273706977</v>
+      </c>
+      <c r="J78" s="116">
+        <f t="shared" si="31"/>
+        <v>0.71253649881773762</v>
+      </c>
+      <c r="K78" s="116">
+        <f t="shared" si="31"/>
+        <v>0.72143148618434361</v>
+      </c>
+      <c r="L78" s="116">
+        <f t="shared" si="31"/>
+        <v>0.72998386385174818</v>
+      </c>
+      <c r="M78" s="116">
+        <f t="shared" si="31"/>
+        <v>0.73820695387267088</v>
+      </c>
     </row>
     <row r="79" spans="2:14" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="122" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D79" s="116">
-        <f t="shared" ref="D79:M79" si="32">D51/D45</f>
-        <v>6.5754886223256911E-2</v>
+        <f t="shared" ref="D79:M79" si="32">D26/D15</f>
+        <v>0.10125128205128205</v>
       </c>
       <c r="E79" s="116">
         <f t="shared" si="32"/>
-        <v>0.9935691448714028</v>
+        <v>0.33228827476805911</v>
       </c>
       <c r="F79" s="116">
         <f t="shared" si="32"/>
-        <v>1.398696739354045</v>
+        <v>0.34812743984591493</v>
       </c>
       <c r="G79" s="116">
         <f t="shared" si="32"/>
-        <v>2.0614052039292154</v>
+        <v>0.36306831940608708</v>
       </c>
       <c r="H79" s="116">
         <f t="shared" si="32"/>
-        <v>3.305657344133226</v>
+        <v>0.37719161035093962</v>
       </c>
       <c r="I79" s="116">
         <f t="shared" si="32"/>
-        <v>6.3788967054391819</v>
+        <v>0.39056171559165892</v>
       </c>
       <c r="J79" s="116">
         <f t="shared" si="32"/>
-        <v>24.60250191963048</v>
+        <v>0.40321891391598519</v>
       </c>
       <c r="K79" s="116">
         <f t="shared" si="32"/>
-        <v>-18.779593361439836</v>
+        <v>0.41524670704261962</v>
       </c>
       <c r="L79" s="116">
         <f t="shared" si="32"/>
-        <v>-7.7266983681312933</v>
+        <v>0.42669273779047479</v>
       </c>
       <c r="M79" s="116">
         <f t="shared" si="32"/>
-        <v>-5.2365998091655221</v>
+        <v>0.43758277603358253</v>
       </c>
     </row>
     <row r="80" spans="2:14" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="122" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D80" s="116">
-        <f t="shared" ref="D80:M80" si="33">D19/D15</f>
-        <v>0.66807692307692312</v>
+        <f t="shared" ref="D80:M80" si="33">D32/D15</f>
+        <v>0.18328205128205127</v>
       </c>
       <c r="E80" s="116">
         <f t="shared" si="33"/>
-        <v>0.69942670537010154</v>
+        <v>0.35422351233671989</v>
       </c>
       <c r="F80" s="116">
         <f t="shared" si="33"/>
-        <v>0.70885792918366786</v>
+        <v>0.36749623463044617</v>
       </c>
       <c r="G80" s="116">
         <f t="shared" si="33"/>
-        <v>0.7179239573607743</v>
+        <v>0.38021266910578227</v>
       </c>
       <c r="H80" s="116">
         <f t="shared" si="33"/>
-        <v>0.72663909730646925</v>
+        <v>0.39239694532417757</v>
       </c>
       <c r="I80" s="116">
         <f t="shared" si="33"/>
-        <v>0.7350170867253667</v>
+        <v>0.40407210469938687</v>
       </c>
       <c r="J80" s="116">
         <f t="shared" si="33"/>
-        <v>0.74307111680647608</v>
+        <v>0.41526015161237639</v>
       </c>
       <c r="K80" s="116">
         <f t="shared" si="33"/>
-        <v>0.75081385443765813</v>
+        <v>0.42598210202834252</v>
       </c>
       <c r="L80" s="116">
         <f t="shared" si="33"/>
-        <v>0.75825746349172995</v>
+        <v>0.43625802974231315</v>
       </c>
       <c r="M80" s="116">
         <f t="shared" si="33"/>
-        <v>0.76541362522435141</v>
+        <v>0.44610711037320377</v>
       </c>
     </row>
     <row r="81" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B81" s="122" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D81" s="116">
-        <f t="shared" ref="D81:M81" si="34">D26/D15</f>
-        <v>0.13471282051282052</v>
+        <f t="shared" ref="D81:M81" si="34">D38/D15</f>
+        <v>9.0094239827971601E-2</v>
       </c>
       <c r="E81" s="116">
         <f t="shared" si="34"/>
-        <v>0.3642984344197282</v>
+        <v>6.3417344877889333E-3</v>
       </c>
       <c r="F81" s="116">
         <f t="shared" si="34"/>
-        <v>0.37874098969940778</v>
+        <v>2.1819700977411408E-3</v>
       </c>
       <c r="G81" s="116">
         <f t="shared" si="34"/>
-        <v>0.39233796171793872</v>
+        <v>-1.6689321229994411E-3</v>
       </c>
       <c r="H81" s="116">
         <f t="shared" si="34"/>
-        <v>0.40516805861328742</v>
+        <v>-5.2475235407964792E-3</v>
       </c>
       <c r="I81" s="116">
         <f t="shared" si="34"/>
-        <v>0.4172937695799559</v>
+        <v>-8.582349989274065E-3</v>
       </c>
       <c r="J81" s="116">
         <f t="shared" si="34"/>
-        <v>0.42875353190472371</v>
+        <v>-1.1691511762987605E-2</v>
       </c>
       <c r="K81" s="116">
         <f t="shared" si="34"/>
-        <v>0.43962907529593415</v>
+        <v>-1.4608992496266328E-2</v>
       </c>
       <c r="L81" s="116">
         <f t="shared" si="34"/>
-        <v>0.4499663374304565</v>
+        <v>-1.7353683589399971E-2</v>
       </c>
       <c r="M81" s="116">
         <f t="shared" si="34"/>
-        <v>0.45978944738526339</v>
-      </c>
-    </row>
-    <row r="82" spans="2:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="B82" s="122" t="s">
-        <v>358</v>
-      </c>
-      <c r="D82" s="116">
-        <f t="shared" ref="D82:M82" si="35">D32/D15</f>
-        <v>0.21674358974358973</v>
-      </c>
-      <c r="E82" s="116">
-        <f t="shared" si="35"/>
-        <v>0.38623367198838898</v>
-      </c>
-      <c r="F82" s="116">
-        <f t="shared" si="35"/>
-        <v>0.39810978448393902</v>
-      </c>
-      <c r="G82" s="116">
-        <f t="shared" si="35"/>
-        <v>0.40948231141763392</v>
-      </c>
-      <c r="H82" s="116">
-        <f t="shared" si="35"/>
-        <v>0.42037339358652531</v>
-      </c>
-      <c r="I82" s="116">
-        <f t="shared" si="35"/>
-        <v>0.43080415868768379</v>
-      </c>
-      <c r="J82" s="116">
-        <f t="shared" si="35"/>
-        <v>0.44079476960111491</v>
-      </c>
-      <c r="K82" s="116">
-        <f t="shared" si="35"/>
-        <v>0.45036447028165705</v>
-      </c>
-      <c r="L82" s="116">
-        <f t="shared" si="35"/>
-        <v>0.45953162938229491</v>
-      </c>
-      <c r="M82" s="116">
-        <f t="shared" si="35"/>
-        <v>0.46831378172488458</v>
+        <v>-1.996034708663787E-2</v>
       </c>
     </row>
     <row r="83" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B83" s="122" t="s">
-        <v>359</v>
-      </c>
-      <c r="D83" s="116">
-        <f t="shared" ref="D83:M83" si="36">D38/D15</f>
-        <v>-2.2203905727039838E-2</v>
-      </c>
-      <c r="E83" s="116">
+        <v>360</v>
+      </c>
+      <c r="D83" s="118">
+        <f>D80/D81</f>
+        <v>2.0343370634128779</v>
+      </c>
+      <c r="E83" s="118">
+        <f t="shared" ref="E83:M83" si="35">E80/E81</f>
+        <v>55.855935472981479</v>
+      </c>
+      <c r="F83" s="118">
+        <f t="shared" si="35"/>
+        <v>168.42404715394238</v>
+      </c>
+      <c r="G83" s="118">
+        <f t="shared" si="35"/>
+        <v>-227.81793451399079</v>
+      </c>
+      <c r="H83" s="118">
+        <f t="shared" si="35"/>
+        <v>-74.777548356575608</v>
+      </c>
+      <c r="I83" s="118">
+        <f t="shared" si="35"/>
+        <v>-47.081755603579758</v>
+      </c>
+      <c r="J83" s="118">
+        <f t="shared" si="35"/>
+        <v>-35.518088680968177</v>
+      </c>
+      <c r="K83" s="118">
+        <f t="shared" si="35"/>
+        <v>-29.158896627348689</v>
+      </c>
+      <c r="L83" s="118">
+        <f t="shared" si="35"/>
+        <v>-25.139217705270919</v>
+      </c>
+      <c r="M83" s="118">
+        <f t="shared" si="35"/>
+        <v>-22.349666989099749</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="B84" s="122" t="s">
+        <v>361</v>
+      </c>
+      <c r="D84" s="119">
+        <f>(D77-WACC!$B$18)*'Estado de resultados'!D45</f>
+        <v>-2228779375.3255625</v>
+      </c>
+      <c r="E84" s="119">
+        <f>(E77-WACC!$B$18)*'Estado de resultados'!E45</f>
+        <v>5299869634.522913</v>
+      </c>
+      <c r="F84" s="119">
+        <f>(F77-WACC!$B$18)*'Estado de resultados'!F45</f>
+        <v>6960356196.8722801</v>
+      </c>
+      <c r="G84" s="119">
+        <f>(G77-WACC!$B$18)*'Estado de resultados'!G45</f>
+        <v>8823082767.5671406</v>
+      </c>
+      <c r="H84" s="119">
+        <f>(H77-WACC!$B$18)*'Estado de resultados'!H45</f>
+        <v>10913365772.851055</v>
+      </c>
+      <c r="I84" s="119">
+        <f>(I77-WACC!$B$18)*'Estado de resultados'!I45</f>
+        <v>13256107779.996792</v>
+      </c>
+      <c r="J84" s="119">
+        <f>(J77-WACC!$B$18)*'Estado de resultados'!J45</f>
+        <v>15854016990.570087</v>
+      </c>
+      <c r="K84" s="119">
+        <f>(K77-WACC!$B$18)*'Estado de resultados'!K45</f>
+        <v>18780685616.550236</v>
+      </c>
+      <c r="L84" s="119">
+        <f>(L77-WACC!$B$18)*'Estado de resultados'!L45</f>
+        <v>22099630860.323975</v>
+      </c>
+      <c r="M84" s="119">
+        <f>(M77-WACC!$B$18)*'Estado de resultados'!M45</f>
+        <v>25844781248.580288</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13" ht="26" x14ac:dyDescent="0.15">
+      <c r="B86" s="122" t="s">
+        <v>362</v>
+      </c>
+      <c r="D86" s="118">
+        <f t="shared" ref="D86:M86" si="36">D26/D27</f>
+        <v>5.6238042487891438</v>
+      </c>
+      <c r="E86" s="118">
         <f t="shared" si="36"/>
-        <v>-0.10176554659590724</v>
-      </c>
-      <c r="F83" s="116">
+        <v>71.709779148660303</v>
+      </c>
+      <c r="F86" s="118">
         <f t="shared" si="36"/>
-        <v>-0.10492440729726207</v>
-      </c>
-      <c r="G83" s="116">
+        <v>94.947383974939228</v>
+      </c>
+      <c r="G86" s="118">
         <f t="shared" si="36"/>
-        <v>-0.10781217577982644</v>
-      </c>
-      <c r="H83" s="116">
+        <v>126.54177993389611</v>
+      </c>
+      <c r="H86" s="118">
         <f t="shared" si="36"/>
-        <v>-0.11046397812881238</v>
-      </c>
-      <c r="I83" s="116">
+        <v>170.60297427875173</v>
+      </c>
+      <c r="I86" s="118">
         <f t="shared" si="36"/>
-        <v>-0.11290698868088685</v>
-      </c>
-      <c r="J83" s="116">
+        <v>234.15623931383431</v>
+      </c>
+      <c r="J86" s="118">
         <f t="shared" si="36"/>
-        <v>-0.11515798798825023</v>
-      </c>
-      <c r="K83" s="116">
+        <v>329.88645010627937</v>
+      </c>
+      <c r="K86" s="118">
         <f t="shared" si="36"/>
-        <v>-0.11724968974447506</v>
-      </c>
-      <c r="L83" s="116">
+        <v>486.16826535952748</v>
+      </c>
+      <c r="L86" s="118">
         <f t="shared" si="36"/>
-        <v>-0.11919976333138693</v>
-      </c>
-      <c r="M83" s="116">
+        <v>774.27308389223572</v>
+      </c>
+      <c r="M86" s="118">
         <f t="shared" si="36"/>
-        <v>-0.12104179488867572</v>
-      </c>
-    </row>
-    <row r="85" spans="2:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="B85" s="122" t="s">
-        <v>360</v>
-      </c>
-      <c r="D85" s="118">
-        <f>D82/D83</f>
-        <v>-9.7615073855965875</v>
-      </c>
-      <c r="E85" s="118">
-        <f t="shared" ref="E85:M85" si="37">E82/E83</f>
-        <v>-3.7953284280194919</v>
-      </c>
-      <c r="F85" s="118">
-        <f t="shared" si="37"/>
-        <v>-3.794253355713999</v>
-      </c>
-      <c r="G85" s="118">
-        <f t="shared" si="37"/>
-        <v>-3.7981082234522097</v>
-      </c>
-      <c r="H85" s="118">
-        <f t="shared" si="37"/>
-        <v>-3.8055246670215572</v>
-      </c>
-      <c r="I85" s="118">
-        <f t="shared" si="37"/>
-        <v>-3.8155668105300493</v>
-      </c>
-      <c r="J85" s="118">
-        <f t="shared" si="37"/>
-        <v>-3.827739415229189</v>
-      </c>
-      <c r="K85" s="118">
-        <f t="shared" si="37"/>
-        <v>-3.8410717440971203</v>
-      </c>
-      <c r="L85" s="118">
-        <f t="shared" si="37"/>
-        <v>-3.8551387732604159</v>
-      </c>
-      <c r="M85" s="118">
-        <f t="shared" si="37"/>
-        <v>-3.8690254234547745</v>
-      </c>
-    </row>
-    <row r="86" spans="2:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="B86" s="122" t="s">
-        <v>361</v>
-      </c>
-      <c r="D86" s="119">
-        <f>(D79-WACC!$B$18)*'Estado de resultados'!D45</f>
-        <v>-1793478653.7849333</v>
-      </c>
-      <c r="E86" s="119">
-        <f>(E79-WACC!$B$18)*'Estado de resultados'!E45</f>
-        <v>6862201586.9203444</v>
-      </c>
-      <c r="F86" s="119">
-        <f>(F79-WACC!$B$18)*'Estado de resultados'!F45</f>
-        <v>8683790747.3030453</v>
-      </c>
-      <c r="G86" s="119">
-        <f>(G79-WACC!$B$18)*'Estado de resultados'!G45</f>
-        <v>10720217143.950525</v>
-      </c>
-      <c r="H86" s="119">
-        <f>(H79-WACC!$B$18)*'Estado de resultados'!H45</f>
-        <v>12998272906.196072</v>
-      </c>
-      <c r="I86" s="119">
-        <f>(I79-WACC!$B$18)*'Estado de resultados'!I45</f>
-        <v>15543929387.198647</v>
-      </c>
-      <c r="J86" s="119">
-        <f>(J79-WACC!$B$18)*'Estado de resultados'!J45</f>
-        <v>18357655711.156792</v>
-      </c>
-      <c r="K86" s="119">
-        <f>(K79-WACC!$B$18)*'Estado de resultados'!K45</f>
-        <v>21520522347.328396</v>
-      </c>
-      <c r="L86" s="119">
-        <f>(L79-WACC!$B$18)*'Estado de resultados'!L45</f>
-        <v>25100818510.761791</v>
-      </c>
-      <c r="M86" s="119">
-        <f>(M79-WACC!$B$18)*'Estado de resultados'!M45</f>
-        <v>29132766304.14537</v>
+        <v>1871.0964705705787</v>
+      </c>
+    </row>
+    <row r="87" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="B87" s="122" t="s">
+        <v>363</v>
+      </c>
+      <c r="D87" s="114" cm="1">
+        <f t="array" ref="D87:M87">TRANSPOSE(Bancos!L20:L29)*1000000</f>
+        <v>1755395380.6492343</v>
+      </c>
+      <c r="E87" s="114">
+        <v>2529568053.8748879</v>
+      </c>
+      <c r="F87" s="114">
+        <v>2354028515.8099647</v>
+      </c>
+      <c r="G87" s="114">
+        <v>2178488977.7450414</v>
+      </c>
+      <c r="H87" s="114">
+        <v>2002949439.6801176</v>
+      </c>
+      <c r="I87" s="114">
+        <v>1827409901.6151943</v>
+      </c>
+      <c r="J87" s="114">
+        <v>1651870363.5502708</v>
+      </c>
+      <c r="K87" s="114">
+        <v>1476330825.4853475</v>
+      </c>
+      <c r="L87" s="114">
+        <v>1300791287.4204242</v>
+      </c>
+      <c r="M87" s="114">
+        <v>1899424422.5811543</v>
       </c>
     </row>
     <row r="88" spans="2:13" ht="26" x14ac:dyDescent="0.15">
       <c r="B88" s="122" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D88" s="118">
-        <f t="shared" ref="D88:M88" si="38">D26/D27</f>
-        <v>14.96471979451398</v>
+        <f t="shared" ref="D88:M88" si="37">D62/D87</f>
+        <v>0.32076030726993726</v>
       </c>
       <c r="E88" s="118">
-        <f t="shared" si="38"/>
-        <v>78.617761323886896</v>
+        <f t="shared" si="37"/>
+        <v>3.6853300476169677</v>
       </c>
       <c r="F88" s="118">
-        <f t="shared" si="38"/>
-        <v>103.29684494837487</v>
+        <f t="shared" si="37"/>
+        <v>4.3690545612813434</v>
       </c>
       <c r="G88" s="118">
-        <f t="shared" si="38"/>
-        <v>136.743255629239</v>
+        <f t="shared" si="37"/>
+        <v>5.4979017576853888</v>
       </c>
       <c r="H88" s="118">
-        <f t="shared" si="38"/>
-        <v>183.25666315287984</v>
+        <f t="shared" si="37"/>
+        <v>6.9368368302814751</v>
       </c>
       <c r="I88" s="118">
-        <f t="shared" si="38"/>
-        <v>250.18309750589123</v>
+        <f t="shared" si="37"/>
+        <v>8.7886020149714206</v>
       </c>
       <c r="J88" s="118">
-        <f t="shared" si="38"/>
-        <v>350.77714791932891</v>
+        <f t="shared" si="37"/>
+        <v>11.185461356218461</v>
       </c>
       <c r="K88" s="118">
-        <f t="shared" si="38"/>
-        <v>514.71499066288914</v>
+        <f t="shared" si="37"/>
+        <v>14.373653423098013</v>
       </c>
       <c r="L88" s="118">
-        <f t="shared" si="38"/>
-        <v>816.50516372521986</v>
+        <f t="shared" si="37"/>
+        <v>18.721701366388462</v>
       </c>
       <c r="M88" s="118">
-        <f t="shared" si="38"/>
-        <v>1966.0518176842911</v>
+        <f t="shared" si="37"/>
+        <v>14.692999424182331</v>
       </c>
     </row>
     <row r="89" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B89" s="122" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D89" s="114" cm="1">
-        <f t="array" ref="D89:M89">TRANSPOSE(Bancos!L20:L29)*1000000</f>
-        <v>1755395380.6492343</v>
+        <f t="array" ref="D89:M89">TRANSPOSE(Bancos!M20:M29)*1000000</f>
+        <v>8400000000</v>
       </c>
       <c r="E89" s="114">
-        <v>2529568053.8748879</v>
+        <v>7560000000</v>
       </c>
       <c r="F89" s="114">
-        <v>2354028515.8099647</v>
+        <v>6720000000</v>
       </c>
       <c r="G89" s="114">
-        <v>2178488977.7450414</v>
+        <v>5880000000</v>
       </c>
       <c r="H89" s="114">
-        <v>2002949439.6801176</v>
+        <v>5040000000</v>
       </c>
       <c r="I89" s="114">
-        <v>1827409901.6151943</v>
+        <v>4200000000</v>
       </c>
       <c r="J89" s="114">
-        <v>1651870363.5502708</v>
+        <v>3360000000</v>
       </c>
       <c r="K89" s="114">
-        <v>1476330825.4853475</v>
+        <v>2520000000</v>
       </c>
       <c r="L89" s="114">
-        <v>1300791287.4204242</v>
+        <v>1680000000</v>
       </c>
       <c r="M89" s="114">
-        <v>1899424422.5811543</v>
-      </c>
-    </row>
-    <row r="90" spans="2:13" ht="26" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B90" s="122" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D90" s="118">
-        <f t="shared" ref="D90:M90" si="39">D62/D89</f>
-        <v>1.0653044900613822</v>
+        <f t="shared" ref="D90:M90" si="38">D89/D32</f>
+        <v>4.7006155567991046</v>
       </c>
       <c r="E90" s="118">
-        <f t="shared" si="39"/>
-        <v>5.1106863155835649</v>
+        <f t="shared" si="38"/>
+        <v>0.58533615855585863</v>
       </c>
       <c r="F90" s="118">
-        <f t="shared" si="39"/>
-        <v>4.9224288924288082</v>
+        <f t="shared" si="38"/>
+        <v>0.44283055306381452</v>
       </c>
       <c r="G90" s="118">
-        <f t="shared" si="39"/>
-        <v>6.1481050730758042</v>
+        <f t="shared" si="38"/>
+        <v>0.33150521051659215</v>
       </c>
       <c r="H90" s="118">
-        <f t="shared" si="39"/>
-        <v>7.705310216552598</v>
+        <f t="shared" si="38"/>
+        <v>0.24418529722095608</v>
       </c>
       <c r="I90" s="118">
-        <f t="shared" si="39"/>
-        <v>9.7025466023144791</v>
+        <f t="shared" si="38"/>
+        <v>0.1755807411854434</v>
       </c>
       <c r="J90" s="118">
-        <f t="shared" si="39"/>
-        <v>12.274503363325364</v>
+        <f t="shared" si="38"/>
+        <v>0.12181723815691056</v>
       </c>
       <c r="K90" s="118">
-        <f t="shared" si="39"/>
-        <v>15.697996625822482</v>
+        <f t="shared" si="38"/>
+        <v>7.9404628226345531E-2</v>
       </c>
       <c r="L90" s="118">
-        <f t="shared" si="39"/>
-        <v>20.362159977095107</v>
+        <f t="shared" si="38"/>
+        <v>4.6055624797924695E-2</v>
       </c>
       <c r="M90" s="118">
-        <f t="shared" si="39"/>
-        <v>15.915731551638485</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B91" s="122" t="s">
-        <v>365</v>
-      </c>
-      <c r="D91" s="114" cm="1">
-        <f t="array" ref="D91:M91">TRANSPOSE(Bancos!M20:M29)*1000000</f>
-        <v>8400000000</v>
-      </c>
-      <c r="E91" s="114">
-        <v>7560000000</v>
-      </c>
-      <c r="F91" s="114">
-        <v>6720000000</v>
-      </c>
-      <c r="G91" s="114">
-        <v>5880000000</v>
-      </c>
-      <c r="H91" s="114">
-        <v>5040000000</v>
-      </c>
-      <c r="I91" s="114">
-        <v>4200000000</v>
-      </c>
-      <c r="J91" s="114">
-        <v>3360000000</v>
-      </c>
-      <c r="K91" s="114">
-        <v>2520000000</v>
-      </c>
-      <c r="L91" s="114">
-        <v>1680000000</v>
-      </c>
-      <c r="M91" s="114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="2:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="B92" s="122" t="s">
-        <v>366</v>
-      </c>
-      <c r="D92" s="118">
-        <f t="shared" ref="D92:M92" si="40">D91/D32</f>
-        <v>3.9749201466934818</v>
-      </c>
-      <c r="E92" s="118">
-        <f t="shared" si="40"/>
-        <v>0.53682484210639336</v>
-      </c>
-      <c r="F92" s="118">
-        <f t="shared" si="40"/>
-        <v>0.40877809883829974</v>
-      </c>
-      <c r="G92" s="118">
-        <f t="shared" si="40"/>
-        <v>0.30780934218288158</v>
-      </c>
-      <c r="H92" s="118">
-        <f t="shared" si="40"/>
-        <v>0.22793441779244636</v>
-      </c>
-      <c r="I92" s="118">
-        <f t="shared" si="40"/>
-        <v>0.16468568885592963</v>
-      </c>
-      <c r="J92" s="118">
-        <f t="shared" si="40"/>
-        <v>0.11476053772556309</v>
-      </c>
-      <c r="K92" s="118">
-        <f t="shared" si="40"/>
-        <v>7.5105725861286693E-2</v>
-      </c>
-      <c r="L92" s="118">
-        <f t="shared" si="40"/>
-        <v>4.3723075514740542E-2</v>
-      </c>
-      <c r="M92" s="118">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="2:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="B93" s="122" t="s">
         <v>367</v>
       </c>
     </row>
@@ -19511,56 +19395,56 @@
     <row r="24" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A24" s="110">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="B24" s="122" t="s">
         <v>44</v>
       </c>
       <c r="D24" s="112">
         <f>D15*Datos!$C$27</f>
-        <v>194748604.84787637</v>
+        <v>146061453.63590726</v>
       </c>
       <c r="E24" s="112">
         <f>E15*Datos!$C$27</f>
-        <v>218489238.77325189</v>
+        <v>163866929.07993889</v>
       </c>
       <c r="F24" s="112">
         <f>F15*Datos!$C$27</f>
-        <v>247439936.86766291</v>
+        <v>185579952.65074715</v>
       </c>
       <c r="G24" s="112">
         <f>G15*Datos!$C$27</f>
-        <v>419317160.69455272</v>
+        <v>314487870.52091449</v>
       </c>
       <c r="H24" s="112">
         <f>H15*Datos!$C$27</f>
-        <v>472789323.66064346</v>
+        <v>354591992.74548256</v>
       </c>
       <c r="I24" s="112">
         <f>I15*Datos!$C$27</f>
-        <v>532103108.26048952</v>
+        <v>399077331.1953671</v>
       </c>
       <c r="J24" s="112">
         <f>J15*Datos!$C$27</f>
-        <v>995041680.83225334</v>
+        <v>746281260.62418997</v>
       </c>
       <c r="K24" s="112">
         <f>K15*Datos!$C$27</f>
-        <v>1116077555.8470078</v>
+        <v>837058166.88525581</v>
       </c>
       <c r="L24" s="112">
         <f>L15*Datos!$C$27</f>
-        <v>1252605091.0986605</v>
+        <v>939453818.32399523</v>
       </c>
       <c r="M24" s="112">
         <f>M15*Datos!$C$27</f>
-        <v>1405568214.4032645</v>
+        <v>1054176160.8024483</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A25" s="110">
         <f t="shared" si="1"/>
-        <v>0.17509397974353896</v>
+        <v>0.18009397974353897</v>
       </c>
       <c r="B25" s="124" t="s">
         <v>314</v>
@@ -19568,43 +19452,43 @@
       <c r="C25" s="107"/>
       <c r="D25" s="120">
         <f t="shared" ref="D25:M25" si="6">D19-D20-D21-D22-D23-D24</f>
-        <v>1704965413.6158268</v>
+        <v>1753652564.827796</v>
       </c>
       <c r="E25" s="120">
         <f t="shared" si="6"/>
-        <v>2242656608.5972505</v>
+        <v>2297278918.2905636</v>
       </c>
       <c r="F25" s="120">
         <f t="shared" si="6"/>
-        <v>2896479875.5556235</v>
+        <v>2958339859.7725391</v>
       </c>
       <c r="G25" s="120">
         <f t="shared" si="6"/>
-        <v>7080348742.2951069</v>
+        <v>7185178032.4687452</v>
       </c>
       <c r="H25" s="120">
         <f t="shared" si="6"/>
-        <v>8421729891.266614</v>
+        <v>8539927222.1817751</v>
       </c>
       <c r="I25" s="120">
         <f t="shared" si="6"/>
-        <v>9936566985.0316315</v>
+        <v>10069592762.096754</v>
       </c>
       <c r="J25" s="120">
         <f t="shared" si="6"/>
-        <v>21814127164.195122</v>
+        <v>22062887584.403183</v>
       </c>
       <c r="K25" s="120">
         <f t="shared" si="6"/>
-        <v>25105850304.805119</v>
+        <v>25384869693.766869</v>
       </c>
       <c r="L25" s="120">
         <f t="shared" si="6"/>
-        <v>28853096010.047581</v>
+        <v>29166247282.822247</v>
       </c>
       <c r="M25" s="120">
         <f t="shared" si="6"/>
-        <v>33092119231.49165</v>
+        <v>33443511285.092464</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="13" x14ac:dyDescent="0.15">
@@ -19650,7 +19534,7 @@
     <row r="27" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A27" s="110">
         <f t="shared" si="1"/>
-        <v>-5.1789810841314857E-3</v>
+        <v>-1.7898108413148071E-4</v>
       </c>
       <c r="B27" s="124" t="s">
         <v>316</v>
@@ -19658,43 +19542,43 @@
       <c r="C27" s="107"/>
       <c r="D27" s="120">
         <f>D25-D26</f>
-        <v>-50429967.03340745</v>
+        <v>-1742815.8214383125</v>
       </c>
       <c r="E27" s="120">
         <f t="shared" ref="E27:M27" si="7">E25-E26</f>
-        <v>-286911445.27763748</v>
+        <v>-232289135.58432436</v>
       </c>
       <c r="F27" s="120">
         <f t="shared" si="7"/>
-        <v>542451359.74565887</v>
+        <v>604311343.96257448</v>
       </c>
       <c r="G27" s="120">
         <f t="shared" si="7"/>
-        <v>4901859764.550066</v>
+        <v>5006689054.7237034</v>
       </c>
       <c r="H27" s="120">
         <f t="shared" si="7"/>
-        <v>6418780451.5864964</v>
+        <v>6536977782.5016575</v>
       </c>
       <c r="I27" s="120">
         <f t="shared" si="7"/>
-        <v>8109157083.4164371</v>
+        <v>8242182860.4815598</v>
       </c>
       <c r="J27" s="120">
         <f t="shared" si="7"/>
-        <v>20162256800.644852</v>
+        <v>20411017220.852913</v>
       </c>
       <c r="K27" s="120">
         <f t="shared" si="7"/>
-        <v>23629519479.319771</v>
+        <v>23908538868.281521</v>
       </c>
       <c r="L27" s="120">
         <f t="shared" si="7"/>
-        <v>27552304722.627155</v>
+        <v>27865455995.401821</v>
       </c>
       <c r="M27" s="120">
         <f t="shared" si="7"/>
-        <v>31192694808.910496</v>
+        <v>31544086862.511311</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="13" x14ac:dyDescent="0.15">
@@ -19715,41 +19599,41 @@
       </c>
       <c r="F28" s="112">
         <f t="shared" si="8"/>
-        <v>189857975.91098058</v>
+        <v>211508970.38690105</v>
       </c>
       <c r="G28" s="112">
         <f t="shared" si="8"/>
-        <v>1715650917.5925231</v>
+        <v>1752341169.153296</v>
       </c>
       <c r="H28" s="112">
         <f t="shared" si="8"/>
-        <v>2246573158.0552735</v>
+        <v>2287942223.8755798</v>
       </c>
       <c r="I28" s="112">
         <f t="shared" si="8"/>
-        <v>2838204979.1957526</v>
+        <v>2884764001.1685457</v>
       </c>
       <c r="J28" s="112">
         <f t="shared" si="8"/>
-        <v>7056789880.2256975</v>
+        <v>7143856027.2985191</v>
       </c>
       <c r="K28" s="112">
         <f t="shared" si="8"/>
-        <v>8270331817.761919</v>
+        <v>8367988603.8985319</v>
       </c>
       <c r="L28" s="112">
         <f t="shared" si="8"/>
-        <v>9643306652.9195042</v>
+        <v>9752909598.3906364</v>
       </c>
       <c r="M28" s="112">
         <f t="shared" si="8"/>
-        <v>10917443183.118673</v>
+        <v>11040430401.878958</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A29" s="110">
         <f t="shared" si="1"/>
-        <v>-5.1789810841314857E-3</v>
+        <v>-1.7898108413148071E-4</v>
       </c>
       <c r="B29" s="124" t="s">
         <v>318</v>
@@ -19757,43 +19641,43 @@
       <c r="C29" s="107"/>
       <c r="D29" s="120">
         <f>D27-D28</f>
-        <v>-50429967.03340745</v>
+        <v>-1742815.8214383125</v>
       </c>
       <c r="E29" s="120">
         <f t="shared" ref="E29:M29" si="9">E27-E28</f>
-        <v>-286911445.27763748</v>
+        <v>-232289135.58432436</v>
       </c>
       <c r="F29" s="120">
         <f t="shared" si="9"/>
-        <v>352593383.83467829</v>
+        <v>392802373.57567346</v>
       </c>
       <c r="G29" s="120">
         <f t="shared" si="9"/>
-        <v>3186208846.9575429</v>
+        <v>3254347885.5704074</v>
       </c>
       <c r="H29" s="120">
         <f t="shared" si="9"/>
-        <v>4172207293.5312228</v>
+        <v>4249035558.6260777</v>
       </c>
       <c r="I29" s="120">
         <f t="shared" si="9"/>
-        <v>5270952104.2206841</v>
+        <v>5357418859.313014</v>
       </c>
       <c r="J29" s="120">
         <f t="shared" si="9"/>
-        <v>13105466920.419155</v>
+        <v>13267161193.554394</v>
       </c>
       <c r="K29" s="120">
         <f t="shared" si="9"/>
-        <v>15359187661.557852</v>
+        <v>15540550264.382988</v>
       </c>
       <c r="L29" s="120">
         <f t="shared" si="9"/>
-        <v>17908998069.707649</v>
+        <v>18112546397.011185</v>
       </c>
       <c r="M29" s="120">
         <f t="shared" si="9"/>
-        <v>20275251625.791824</v>
+        <v>20503656460.632355</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.15">
@@ -19817,43 +19701,43 @@
       <c r="C31" s="107"/>
       <c r="D31" s="120">
         <f>D25+D22+D23</f>
-        <v>2784765413.6158266</v>
+        <v>2833452564.827796</v>
       </c>
       <c r="E31" s="120">
         <f>E25+E22+E23</f>
-        <v>3322456608.5972505</v>
+        <v>3377078918.2905636</v>
       </c>
       <c r="F31" s="120">
         <f t="shared" ref="F31:M31" si="10">F25+F22+F23</f>
-        <v>3976279875.5556235</v>
+        <v>4038139859.7725391</v>
       </c>
       <c r="G31" s="120">
         <f t="shared" si="10"/>
-        <v>8160148742.2951069</v>
+        <v>8264978032.4687452</v>
       </c>
       <c r="H31" s="120">
         <f t="shared" si="10"/>
-        <v>9501529891.266613</v>
+        <v>9619727222.1817741</v>
       </c>
       <c r="I31" s="120">
         <f t="shared" si="10"/>
-        <v>11016366985.031631</v>
+        <v>11149392762.096754</v>
       </c>
       <c r="J31" s="120">
         <f t="shared" si="10"/>
-        <v>22893927164.195122</v>
+        <v>23142687584.403183</v>
       </c>
       <c r="K31" s="120">
         <f t="shared" si="10"/>
-        <v>26185650304.805119</v>
+        <v>26464669693.766869</v>
       </c>
       <c r="L31" s="120">
         <f t="shared" si="10"/>
-        <v>29932896010.047581</v>
+        <v>30246047282.822247</v>
       </c>
       <c r="M31" s="120">
         <f t="shared" si="10"/>
-        <v>34171919231.49165</v>
+        <v>34523311285.092468</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.15">
@@ -19863,50 +19747,50 @@
     <row r="33" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A33" s="110">
         <f t="shared" si="1"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="B33" s="134" t="s">
         <v>320</v>
       </c>
       <c r="D33" s="112">
         <f>(Datos!$C$28/360)*'Breakeven Precio'!D15</f>
-        <v>811452520.19948483</v>
+        <v>1622905040.3989697</v>
       </c>
       <c r="E33" s="112">
         <f>(Datos!$C$28/360)*'Breakeven Precio'!E15</f>
-        <v>910371828.22188282</v>
+        <v>1820743656.4437656</v>
       </c>
       <c r="F33" s="112">
         <f>(Datos!$C$28/360)*'Breakeven Precio'!F15</f>
-        <v>1030999736.9485953</v>
+        <v>2061999473.8971906</v>
       </c>
       <c r="G33" s="112">
         <f>(Datos!$C$28/360)*'Breakeven Precio'!G15</f>
-        <v>1747154836.2273028</v>
+        <v>3494309672.4546056</v>
       </c>
       <c r="H33" s="112">
         <f>(Datos!$C$28/360)*'Breakeven Precio'!H15</f>
-        <v>1969955515.252681</v>
+        <v>3939911030.505362</v>
       </c>
       <c r="I33" s="112">
         <f>(Datos!$C$28/360)*'Breakeven Precio'!I15</f>
-        <v>2217096284.4187059</v>
+        <v>4434192568.8374119</v>
       </c>
       <c r="J33" s="112">
         <f>(Datos!$C$28/360)*'Breakeven Precio'!J15</f>
-        <v>4146007003.4677219</v>
+        <v>8292014006.9354439</v>
       </c>
       <c r="K33" s="112">
         <f>(Datos!$C$28/360)*'Breakeven Precio'!K15</f>
-        <v>4650323149.3625317</v>
+        <v>9300646298.7250633</v>
       </c>
       <c r="L33" s="112">
         <f>(Datos!$C$28/360)*'Breakeven Precio'!L15</f>
-        <v>5219187879.5777512</v>
+        <v>10438375759.155502</v>
       </c>
       <c r="M33" s="112">
         <f>(Datos!$C$28/360)*'Breakeven Precio'!M15</f>
-        <v>5856534226.6802683</v>
+        <v>11713068453.360537</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="13" x14ac:dyDescent="0.15">
@@ -19916,92 +19800,92 @@
       </c>
       <c r="D34" s="112">
         <f>D33</f>
-        <v>811452520.19948483</v>
+        <v>1622905040.3989697</v>
       </c>
       <c r="E34" s="112">
         <f t="shared" ref="E34:M34" si="11">E33</f>
-        <v>910371828.22188282</v>
+        <v>1820743656.4437656</v>
       </c>
       <c r="F34" s="112">
         <f t="shared" si="11"/>
-        <v>1030999736.9485953</v>
+        <v>2061999473.8971906</v>
       </c>
       <c r="G34" s="112">
         <f t="shared" si="11"/>
-        <v>1747154836.2273028</v>
+        <v>3494309672.4546056</v>
       </c>
       <c r="H34" s="112">
         <f t="shared" si="11"/>
-        <v>1969955515.252681</v>
+        <v>3939911030.505362</v>
       </c>
       <c r="I34" s="112">
         <f t="shared" si="11"/>
-        <v>2217096284.4187059</v>
+        <v>4434192568.8374119</v>
       </c>
       <c r="J34" s="112">
         <f t="shared" si="11"/>
-        <v>4146007003.4677219</v>
+        <v>8292014006.9354439</v>
       </c>
       <c r="K34" s="112">
         <f t="shared" si="11"/>
-        <v>4650323149.3625317</v>
+        <v>9300646298.7250633</v>
       </c>
       <c r="L34" s="112">
         <f t="shared" si="11"/>
-        <v>5219187879.5777512</v>
+        <v>10438375759.155502</v>
       </c>
       <c r="M34" s="112">
         <f t="shared" si="11"/>
-        <v>5856534226.6802683</v>
+        <v>11713068453.360537</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A35" s="110">
         <f t="shared" si="1"/>
-        <v>5.1348249749009922E-2</v>
+        <v>3.4232166499339946E-2</v>
       </c>
       <c r="B35" s="134" t="s">
         <v>322</v>
       </c>
       <c r="D35" s="112">
         <f>(Datos!$C$29/360)*'Breakeven Precio'!D16</f>
-        <v>500000000</v>
+        <v>333333333.33333331</v>
       </c>
       <c r="E35" s="112">
         <f>(Datos!$C$29/360)*'Breakeven Precio'!E16</f>
-        <v>539784000</v>
+        <v>359856000</v>
       </c>
       <c r="F35" s="112">
         <f>(Datos!$C$29/360)*'Breakeven Precio'!F16</f>
-        <v>588239330.11199999</v>
+        <v>392159553.40799999</v>
       </c>
       <c r="G35" s="112">
         <f>(Datos!$C$29/360)*'Breakeven Precio'!G16</f>
-        <v>959226581.39105546</v>
+        <v>639484387.59403694</v>
       </c>
       <c r="H35" s="112">
         <f>(Datos!$C$29/360)*'Breakeven Precio'!H16</f>
-        <v>1040735900.9181792</v>
+        <v>693823933.94545269</v>
       </c>
       <c r="I35" s="112">
         <f>(Datos!$C$29/360)*'Breakeven Precio'!I16</f>
-        <v>1127101369.6558743</v>
+        <v>751400913.10391617</v>
       </c>
       <c r="J35" s="112">
         <f>(Datos!$C$29/360)*'Breakeven Precio'!J16</f>
-        <v>2028162559.6272631</v>
+        <v>1352108373.084842</v>
       </c>
       <c r="K35" s="112">
         <f>(Datos!$C$29/360)*'Breakeven Precio'!K16</f>
-        <v>2189022216.7189803</v>
+        <v>1459348144.47932</v>
       </c>
       <c r="L35" s="112">
         <f>(Datos!$C$29/360)*'Breakeven Precio'!L16</f>
-        <v>2364091457.5232978</v>
+        <v>1576060971.6821985</v>
       </c>
       <c r="M35" s="112">
         <f>(Datos!$C$29/360)*'Breakeven Precio'!M16</f>
-        <v>2552679761.2728462</v>
+        <v>1701786507.5152307</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="13" x14ac:dyDescent="0.15">
@@ -20022,35 +19906,35 @@
       </c>
       <c r="F36" s="112">
         <f t="shared" si="12"/>
-        <v>189857975.91098058</v>
+        <v>211508970.38690105</v>
       </c>
       <c r="G36" s="112">
         <f t="shared" si="12"/>
-        <v>1715650917.5925231</v>
+        <v>1752341169.153296</v>
       </c>
       <c r="H36" s="112">
         <f t="shared" si="12"/>
-        <v>2246573158.0552735</v>
+        <v>2287942223.8755798</v>
       </c>
       <c r="I36" s="112">
         <f t="shared" si="12"/>
-        <v>2838204979.1957526</v>
+        <v>2884764001.1685457</v>
       </c>
       <c r="J36" s="112">
         <f t="shared" si="12"/>
-        <v>7056789880.2256975</v>
+        <v>7143856027.2985191</v>
       </c>
       <c r="K36" s="112">
         <f t="shared" si="12"/>
-        <v>8270331817.761919</v>
+        <v>8367988603.8985319</v>
       </c>
       <c r="L36" s="112">
         <f t="shared" si="12"/>
-        <v>9643306652.9195042</v>
+        <v>9752909598.3906364</v>
       </c>
       <c r="M36" s="112">
         <f t="shared" si="12"/>
-        <v>10917443183.118673</v>
+        <v>11040430401.878958</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="13" x14ac:dyDescent="0.15">
@@ -20061,43 +19945,43 @@
       <c r="C37" s="107"/>
       <c r="D37" s="120">
         <f>D34-D35-D36</f>
-        <v>311452520.19948483</v>
+        <v>1289571707.0656364</v>
       </c>
       <c r="E37" s="120">
         <f>E34-E35-E36</f>
-        <v>370587828.22188282</v>
+        <v>1460887656.4437656</v>
       </c>
       <c r="F37" s="120">
         <f t="shared" ref="F37:M37" si="13">F34-F35-F36</f>
-        <v>252902430.92561471</v>
+        <v>1458330950.1022894</v>
       </c>
       <c r="G37" s="120">
         <f t="shared" si="13"/>
-        <v>-927722662.75627577</v>
+        <v>1102484115.7072725</v>
       </c>
       <c r="H37" s="120">
         <f t="shared" si="13"/>
-        <v>-1317353543.7207718</v>
+        <v>958144872.68432951</v>
       </c>
       <c r="I37" s="120">
         <f t="shared" si="13"/>
-        <v>-1748210064.4329209</v>
+        <v>798027654.56494999</v>
       </c>
       <c r="J37" s="120">
         <f t="shared" si="13"/>
-        <v>-4938945436.3852386</v>
+        <v>-203950393.44791698</v>
       </c>
       <c r="K37" s="120">
         <f t="shared" si="13"/>
-        <v>-5809030885.1183681</v>
+        <v>-526690449.65278912</v>
       </c>
       <c r="L37" s="120">
         <f t="shared" si="13"/>
-        <v>-6788210230.8650513</v>
+        <v>-890594810.9173317</v>
       </c>
       <c r="M37" s="120">
         <f t="shared" si="13"/>
-        <v>-7613588717.7112513</v>
+        <v>-1029148456.0336514</v>
       </c>
       <c r="O37" s="108" t="s">
         <v>325</v>
@@ -20114,43 +19998,43 @@
       <c r="C38" s="107"/>
       <c r="D38" s="120">
         <f>D37</f>
-        <v>311452520.19948483</v>
+        <v>1289571707.0656364</v>
       </c>
       <c r="E38" s="120">
         <f>E37-D37</f>
-        <v>59135308.022397995</v>
+        <v>171315949.37812924</v>
       </c>
       <c r="F38" s="120">
         <f t="shared" ref="F38:M38" si="14">F37-E37</f>
-        <v>-117685397.29626811</v>
+        <v>-2556706.341476202</v>
       </c>
       <c r="G38" s="120">
         <f t="shared" si="14"/>
-        <v>-1180625093.6818905</v>
+        <v>-355846834.39501691</v>
       </c>
       <c r="H38" s="120">
         <f t="shared" si="14"/>
-        <v>-389630880.96449602</v>
+        <v>-144339243.02294302</v>
       </c>
       <c r="I38" s="120">
         <f t="shared" si="14"/>
-        <v>-430856520.71214914</v>
+        <v>-160117218.11937952</v>
       </c>
       <c r="J38" s="120">
         <f t="shared" si="14"/>
-        <v>-3190735371.9523177</v>
+        <v>-1001978048.012867</v>
       </c>
       <c r="K38" s="120">
         <f t="shared" si="14"/>
-        <v>-870085448.7331295</v>
+        <v>-322740056.20487213</v>
       </c>
       <c r="L38" s="120">
         <f t="shared" si="14"/>
-        <v>-979179345.74668312</v>
+        <v>-363904361.26454258</v>
       </c>
       <c r="M38" s="120">
         <f t="shared" si="14"/>
-        <v>-825378486.84619999</v>
+        <v>-138553645.11631966</v>
       </c>
       <c r="O38" s="108" t="s">
         <v>327</v>
@@ -20366,43 +20250,43 @@
       <c r="C44" s="107"/>
       <c r="D44" s="120">
         <f>D42+D37</f>
-        <v>13511652520.199486</v>
+        <v>14489771707.065636</v>
       </c>
       <c r="E44" s="120">
         <f>E42+E37</f>
-        <v>12770987828.221882</v>
+        <v>13861287656.443766</v>
       </c>
       <c r="F44" s="120">
         <f t="shared" ref="F44:L44" si="18">F42+F37</f>
-        <v>11853502430.925615</v>
+        <v>13058930950.102289</v>
       </c>
       <c r="G44" s="120">
         <f t="shared" si="18"/>
-        <v>9873077337.2437248</v>
+        <v>11903284115.707272</v>
       </c>
       <c r="H44" s="120">
         <f t="shared" si="18"/>
-        <v>8683646456.2792282</v>
+        <v>10959144872.68433</v>
       </c>
       <c r="I44" s="120">
         <f t="shared" si="18"/>
-        <v>7452989935.5670795</v>
+        <v>9999227654.564949</v>
       </c>
       <c r="J44" s="120">
         <f t="shared" si="18"/>
-        <v>3462454563.6147614</v>
+        <v>8197449606.552083</v>
       </c>
       <c r="K44" s="120">
         <f t="shared" si="18"/>
-        <v>1792569114.8816319</v>
+        <v>7074909550.3472109</v>
       </c>
       <c r="L44" s="120">
         <f t="shared" si="18"/>
-        <v>13589769.13494873</v>
+        <v>5911205189.0826683</v>
       </c>
       <c r="M44" s="120">
         <f>M42+M37</f>
-        <v>-1611588717.7112513</v>
+        <v>4972851543.9663486</v>
       </c>
       <c r="O44" s="108" t="s">
         <v>335</v>
@@ -20489,43 +20373,43 @@
       <c r="C48" s="112"/>
       <c r="D48" s="112">
         <f>D25</f>
-        <v>1704965413.6158268</v>
+        <v>1753652564.827796</v>
       </c>
       <c r="E48" s="112">
         <f t="shared" ref="E48:M48" si="19">E25</f>
-        <v>2242656608.5972505</v>
+        <v>2297278918.2905636</v>
       </c>
       <c r="F48" s="112">
         <f t="shared" si="19"/>
-        <v>2896479875.5556235</v>
+        <v>2958339859.7725391</v>
       </c>
       <c r="G48" s="112">
         <f t="shared" si="19"/>
-        <v>7080348742.2951069</v>
+        <v>7185178032.4687452</v>
       </c>
       <c r="H48" s="112">
         <f t="shared" si="19"/>
-        <v>8421729891.266614</v>
+        <v>8539927222.1817751</v>
       </c>
       <c r="I48" s="112">
         <f t="shared" si="19"/>
-        <v>9936566985.0316315</v>
+        <v>10069592762.096754</v>
       </c>
       <c r="J48" s="112">
         <f t="shared" si="19"/>
-        <v>21814127164.195122</v>
+        <v>22062887584.403183</v>
       </c>
       <c r="K48" s="112">
         <f t="shared" si="19"/>
-        <v>25105850304.805119</v>
+        <v>25384869693.766869</v>
       </c>
       <c r="L48" s="112">
         <f t="shared" si="19"/>
-        <v>28853096010.047581</v>
+        <v>29166247282.822247</v>
       </c>
       <c r="M48" s="112">
         <f t="shared" si="19"/>
-        <v>33092119231.49165</v>
+        <v>33443511285.092464</v>
       </c>
       <c r="O48" s="108" t="s">
         <v>339</v>
@@ -20542,43 +20426,43 @@
       <c r="C49" s="112"/>
       <c r="D49" s="112">
         <f t="shared" ref="D49:M49" si="20">IF(D48&lt;0,0,D48*D5)</f>
-        <v>596737894.76553941</v>
+        <v>613778397.6897285</v>
       </c>
       <c r="E49" s="112">
         <f t="shared" si="20"/>
-        <v>784929813.00903761</v>
+        <v>804047621.40169716</v>
       </c>
       <c r="F49" s="112">
         <f t="shared" si="20"/>
-        <v>1013767956.4444681</v>
+        <v>1035418950.9203886</v>
       </c>
       <c r="G49" s="112">
         <f t="shared" si="20"/>
-        <v>2478122059.803287</v>
+        <v>2514812311.3640609</v>
       </c>
       <c r="H49" s="112">
         <f t="shared" si="20"/>
-        <v>2947605461.9433146</v>
+        <v>2988974527.7636213</v>
       </c>
       <c r="I49" s="112">
         <f t="shared" si="20"/>
-        <v>3477798444.7610707</v>
+        <v>3524357466.7338638</v>
       </c>
       <c r="J49" s="112">
         <f t="shared" si="20"/>
-        <v>7634944507.4682922</v>
+        <v>7722010654.5411139</v>
       </c>
       <c r="K49" s="112">
         <f t="shared" si="20"/>
-        <v>8787047606.6817913</v>
+        <v>8884704392.8184032</v>
       </c>
       <c r="L49" s="112">
         <f t="shared" si="20"/>
-        <v>10098583603.516653</v>
+        <v>10208186548.987785</v>
       </c>
       <c r="M49" s="112">
         <f t="shared" si="20"/>
-        <v>11582241731.022078</v>
+        <v>11705228949.782362</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.15">
@@ -20588,43 +20472,43 @@
       <c r="C50" s="120"/>
       <c r="D50" s="120">
         <f>D48-D49</f>
-        <v>1108227518.8502874</v>
+        <v>1139874167.1380675</v>
       </c>
       <c r="E50" s="120">
         <f t="shared" ref="E50:M50" si="21">E48-E49</f>
-        <v>1457726795.588213</v>
+        <v>1493231296.8888664</v>
       </c>
       <c r="F50" s="120">
         <f t="shared" si="21"/>
-        <v>1882711919.1111555</v>
+        <v>1922920908.8521504</v>
       </c>
       <c r="G50" s="120">
         <f t="shared" si="21"/>
-        <v>4602226682.4918194</v>
+        <v>4670365721.1046848</v>
       </c>
       <c r="H50" s="120">
         <f t="shared" si="21"/>
-        <v>5474124429.3232994</v>
+        <v>5550952694.4181538</v>
       </c>
       <c r="I50" s="120">
         <f t="shared" si="21"/>
-        <v>6458768540.2705612</v>
+        <v>6545235295.3628902</v>
       </c>
       <c r="J50" s="120">
         <f t="shared" si="21"/>
-        <v>14179182656.72683</v>
+        <v>14340876929.862068</v>
       </c>
       <c r="K50" s="120">
         <f t="shared" si="21"/>
-        <v>16318802698.123327</v>
+        <v>16500165300.948465</v>
       </c>
       <c r="L50" s="120">
         <f t="shared" si="21"/>
-        <v>18754512406.53093</v>
+        <v>18958060733.834461</v>
       </c>
       <c r="M50" s="120">
         <f t="shared" si="21"/>
-        <v>21509877500.469574</v>
+        <v>21738282335.310104</v>
       </c>
     </row>
     <row r="51" spans="2:14" ht="13" x14ac:dyDescent="0.15">
@@ -20708,43 +20592,43 @@
       <c r="C53" s="120"/>
       <c r="D53" s="120">
         <f>D50+D51+D52</f>
-        <v>2188027518.8502874</v>
+        <v>2219674167.1380672</v>
       </c>
       <c r="E53" s="120">
         <f t="shared" ref="E53:M53" si="22">E50+E51+E52</f>
-        <v>2537526795.588213</v>
+        <v>2573031296.8888664</v>
       </c>
       <c r="F53" s="120">
         <f t="shared" si="22"/>
-        <v>2962511919.1111555</v>
+        <v>3002720908.8521504</v>
       </c>
       <c r="G53" s="120">
         <f t="shared" si="22"/>
-        <v>5682026682.4918194</v>
+        <v>5750165721.1046848</v>
       </c>
       <c r="H53" s="120">
         <f t="shared" si="22"/>
-        <v>6553924429.3232994</v>
+        <v>6630752694.4181538</v>
       </c>
       <c r="I53" s="120">
         <f t="shared" si="22"/>
-        <v>7538568540.2705612</v>
+        <v>7625035295.3628902</v>
       </c>
       <c r="J53" s="120">
         <f t="shared" si="22"/>
-        <v>15258982656.72683</v>
+        <v>15420676929.862068</v>
       </c>
       <c r="K53" s="120">
         <f t="shared" si="22"/>
-        <v>17398602698.123329</v>
+        <v>17579965300.948463</v>
       </c>
       <c r="L53" s="120">
         <f t="shared" si="22"/>
-        <v>19834312406.53093</v>
+        <v>20037860733.834461</v>
       </c>
       <c r="M53" s="120">
         <f t="shared" si="22"/>
-        <v>22589677500.469574</v>
+        <v>22818082335.310104</v>
       </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.15">
@@ -20823,43 +20707,43 @@
       <c r="C57" s="107"/>
       <c r="D57" s="137">
         <f>D31</f>
-        <v>2784765413.6158266</v>
+        <v>2833452564.827796</v>
       </c>
       <c r="E57" s="137">
         <f t="shared" ref="E57:M57" si="23">E31</f>
-        <v>3322456608.5972505</v>
+        <v>3377078918.2905636</v>
       </c>
       <c r="F57" s="137">
         <f t="shared" si="23"/>
-        <v>3976279875.5556235</v>
+        <v>4038139859.7725391</v>
       </c>
       <c r="G57" s="137">
         <f t="shared" si="23"/>
-        <v>8160148742.2951069</v>
+        <v>8264978032.4687452</v>
       </c>
       <c r="H57" s="137">
         <f t="shared" si="23"/>
-        <v>9501529891.266613</v>
+        <v>9619727222.1817741</v>
       </c>
       <c r="I57" s="137">
         <f t="shared" si="23"/>
-        <v>11016366985.031631</v>
+        <v>11149392762.096754</v>
       </c>
       <c r="J57" s="137">
         <f t="shared" si="23"/>
-        <v>22893927164.195122</v>
+        <v>23142687584.403183</v>
       </c>
       <c r="K57" s="137">
         <f t="shared" si="23"/>
-        <v>26185650304.805119</v>
+        <v>26464669693.766869</v>
       </c>
       <c r="L57" s="137">
         <f t="shared" si="23"/>
-        <v>29932896010.047581</v>
+        <v>30246047282.822247</v>
       </c>
       <c r="M57" s="137">
         <f t="shared" si="23"/>
-        <v>34171919231.49165</v>
+        <v>34523311285.092468</v>
       </c>
       <c r="N57" s="107"/>
     </row>
@@ -20870,43 +20754,43 @@
       <c r="C58" s="107"/>
       <c r="D58" s="137">
         <f>D49</f>
-        <v>596737894.76553941</v>
+        <v>613778397.6897285</v>
       </c>
       <c r="E58" s="137">
         <f t="shared" ref="E58:M58" si="24">E49</f>
-        <v>784929813.00903761</v>
+        <v>804047621.40169716</v>
       </c>
       <c r="F58" s="137">
         <f t="shared" si="24"/>
-        <v>1013767956.4444681</v>
+        <v>1035418950.9203886</v>
       </c>
       <c r="G58" s="137">
         <f t="shared" si="24"/>
-        <v>2478122059.803287</v>
+        <v>2514812311.3640609</v>
       </c>
       <c r="H58" s="137">
         <f t="shared" si="24"/>
-        <v>2947605461.9433146</v>
+        <v>2988974527.7636213</v>
       </c>
       <c r="I58" s="137">
         <f t="shared" si="24"/>
-        <v>3477798444.7610707</v>
+        <v>3524357466.7338638</v>
       </c>
       <c r="J58" s="137">
         <f t="shared" si="24"/>
-        <v>7634944507.4682922</v>
+        <v>7722010654.5411139</v>
       </c>
       <c r="K58" s="137">
         <f t="shared" si="24"/>
-        <v>8787047606.6817913</v>
+        <v>8884704392.8184032</v>
       </c>
       <c r="L58" s="137">
         <f t="shared" si="24"/>
-        <v>10098583603.516653</v>
+        <v>10208186548.987785</v>
       </c>
       <c r="M58" s="137">
         <f t="shared" si="24"/>
-        <v>11582241731.022078</v>
+        <v>11705228949.782362</v>
       </c>
       <c r="N58" s="107"/>
     </row>
@@ -20916,43 +20800,43 @@
       </c>
       <c r="D59" s="138">
         <f>D57-D58</f>
-        <v>2188027518.8502874</v>
+        <v>2219674167.1380672</v>
       </c>
       <c r="E59" s="138">
         <f t="shared" ref="E59:M59" si="25">E57-E58</f>
-        <v>2537526795.588213</v>
+        <v>2573031296.8888664</v>
       </c>
       <c r="F59" s="138">
         <f t="shared" si="25"/>
-        <v>2962511919.1111555</v>
+        <v>3002720908.8521504</v>
       </c>
       <c r="G59" s="138">
         <f t="shared" si="25"/>
-        <v>5682026682.4918194</v>
+        <v>5750165721.1046848</v>
       </c>
       <c r="H59" s="138">
         <f t="shared" si="25"/>
-        <v>6553924429.3232985</v>
+        <v>6630752694.4181528</v>
       </c>
       <c r="I59" s="138">
         <f t="shared" si="25"/>
-        <v>7538568540.2705612</v>
+        <v>7625035295.3628902</v>
       </c>
       <c r="J59" s="138">
         <f t="shared" si="25"/>
-        <v>15258982656.72683</v>
+        <v>15420676929.862068</v>
       </c>
       <c r="K59" s="138">
         <f t="shared" si="25"/>
-        <v>17398602698.123329</v>
+        <v>17579965300.948463</v>
       </c>
       <c r="L59" s="138">
         <f t="shared" si="25"/>
-        <v>19834312406.53093</v>
+        <v>20037860733.834461</v>
       </c>
       <c r="M59" s="138">
         <f t="shared" si="25"/>
-        <v>22589677500.469574</v>
+        <v>22818082335.310104</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="13" x14ac:dyDescent="0.15">
@@ -20962,43 +20846,43 @@
       <c r="C60" s="112"/>
       <c r="D60" s="112">
         <f>-D38</f>
-        <v>-311452520.19948483</v>
+        <v>-1289571707.0656364</v>
       </c>
       <c r="E60" s="112">
         <f t="shared" ref="E60:M60" si="26">-E38</f>
-        <v>-59135308.022397995</v>
+        <v>-171315949.37812924</v>
       </c>
       <c r="F60" s="112">
         <f t="shared" si="26"/>
-        <v>117685397.29626811</v>
+        <v>2556706.341476202</v>
       </c>
       <c r="G60" s="112">
         <f t="shared" si="26"/>
-        <v>1180625093.6818905</v>
+        <v>355846834.39501691</v>
       </c>
       <c r="H60" s="112">
         <f t="shared" si="26"/>
-        <v>389630880.96449602</v>
+        <v>144339243.02294302</v>
       </c>
       <c r="I60" s="112">
         <f t="shared" si="26"/>
-        <v>430856520.71214914</v>
+        <v>160117218.11937952</v>
       </c>
       <c r="J60" s="112">
         <f t="shared" si="26"/>
-        <v>3190735371.9523177</v>
+        <v>1001978048.012867</v>
       </c>
       <c r="K60" s="112">
         <f t="shared" si="26"/>
-        <v>870085448.7331295</v>
+        <v>322740056.20487213</v>
       </c>
       <c r="L60" s="112">
         <f t="shared" si="26"/>
-        <v>979179345.74668312</v>
+        <v>363904361.26454258</v>
       </c>
       <c r="M60" s="112">
         <f t="shared" si="26"/>
-        <v>825378486.84619999</v>
+        <v>138553645.11631966</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.15">
@@ -21008,43 +20892,43 @@
       <c r="C61" s="120"/>
       <c r="D61" s="120">
         <f>D59+D60</f>
-        <v>1876574998.6508026</v>
+        <v>930102460.07243085</v>
       </c>
       <c r="E61" s="120">
         <f>E53+E60</f>
-        <v>2478391487.565815</v>
+        <v>2401715347.5107374</v>
       </c>
       <c r="F61" s="120">
         <f>F53+F60</f>
-        <v>3080197316.4074235</v>
+        <v>3005277615.1936264</v>
       </c>
       <c r="G61" s="120">
         <f>G53+G60</f>
-        <v>6862651776.1737099</v>
+        <v>6106012555.4997015</v>
       </c>
       <c r="H61" s="120">
         <f t="shared" ref="H61:M61" si="27">H53+H60</f>
-        <v>6943555310.2877951</v>
+        <v>6775091937.4410973</v>
       </c>
       <c r="I61" s="120">
         <f t="shared" si="27"/>
-        <v>7969425060.9827099</v>
+        <v>7785152513.4822693</v>
       </c>
       <c r="J61" s="120">
         <f t="shared" si="27"/>
-        <v>18449718028.679146</v>
+        <v>16422654977.874935</v>
       </c>
       <c r="K61" s="120">
         <f t="shared" si="27"/>
-        <v>18268688146.856461</v>
+        <v>17902705357.153336</v>
       </c>
       <c r="L61" s="120">
         <f t="shared" si="27"/>
-        <v>20813491752.277611</v>
+        <v>20401765095.099003</v>
       </c>
       <c r="M61" s="120">
         <f t="shared" si="27"/>
-        <v>23415055987.315773</v>
+        <v>22956635980.426422</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="13" x14ac:dyDescent="0.15">
@@ -21097,43 +20981,43 @@
       </c>
       <c r="D63" s="120">
         <f>D61+D62</f>
-        <v>1876574998.6508026</v>
+        <v>930102460.07243085</v>
       </c>
       <c r="E63" s="120">
         <f t="shared" ref="E63:L63" si="28">E61+E62</f>
-        <v>2478391487.565815</v>
+        <v>2401715347.5107374</v>
       </c>
       <c r="F63" s="120">
         <f>F61+F62</f>
-        <v>3080197316.4074235</v>
+        <v>3005277615.1936264</v>
       </c>
       <c r="G63" s="120">
         <f>G61+G62</f>
-        <v>6862651776.1737099</v>
+        <v>6106012555.4997015</v>
       </c>
       <c r="H63" s="120">
         <f>H61+H62</f>
-        <v>-2856444689.7122049</v>
+        <v>-3024908062.5589027</v>
       </c>
       <c r="I63" s="120">
         <f t="shared" si="28"/>
-        <v>7969425060.9827099</v>
+        <v>7785152513.4822693</v>
       </c>
       <c r="J63" s="120">
         <f t="shared" si="28"/>
-        <v>18449718028.679146</v>
+        <v>16422654977.874935</v>
       </c>
       <c r="K63" s="120">
         <f t="shared" si="28"/>
-        <v>18268688146.856461</v>
+        <v>17902705357.153336</v>
       </c>
       <c r="L63" s="120">
         <f t="shared" si="28"/>
-        <v>20813491752.277611</v>
+        <v>20401765095.099003</v>
       </c>
       <c r="M63" s="120">
         <f>M61+M62</f>
-        <v>23415055987.315773</v>
+        <v>22956635980.426422</v>
       </c>
       <c r="N63" s="121">
         <f>P48</f>
@@ -21161,7 +21045,7 @@
       </c>
       <c r="C66" s="141">
         <f>NPV(WACC!B18,'Breakeven Precio'!D63:N63)+'Breakeven Precio'!C63</f>
-        <v>12897002824.030399</v>
+        <v>10742459416.647499</v>
       </c>
       <c r="D66" s="112"/>
       <c r="E66" s="112"/>
@@ -21181,7 +21065,7 @@
       </c>
       <c r="C67" s="143">
         <f>MIRR(C63:N63,WACC!B18,WACC!B18)</f>
-        <v>0.27328727038518763</v>
+        <v>0.26385231100204409</v>
       </c>
       <c r="D67" s="112"/>
       <c r="E67" s="112"/>
@@ -21271,43 +21155,43 @@
       <c r="C70" s="146"/>
       <c r="D70" s="112">
         <f>D63*D69</f>
-        <v>1558762299.3123131</v>
+        <v>772582311.01922762</v>
       </c>
       <c r="E70" s="112">
         <f t="shared" ref="E70:N70" si="29">E63*E69</f>
-        <v>1710006823.3673861</v>
+        <v>1657102863.9479508</v>
       </c>
       <c r="F70" s="112">
         <f t="shared" si="29"/>
-        <v>1765307799.5021253</v>
+        <v>1722370182.4265602</v>
       </c>
       <c r="G70" s="112">
         <f t="shared" si="29"/>
-        <v>3266990199.758203</v>
+        <v>2906789362.047492</v>
       </c>
       <c r="H70" s="112">
         <f t="shared" si="29"/>
-        <v>-1129524500.2475228</v>
+        <v>-1196140005.7778785</v>
       </c>
       <c r="I70" s="112">
         <f t="shared" si="29"/>
-        <v>2617645282.6276631</v>
+        <v>2557118938.3818426</v>
       </c>
       <c r="J70" s="112">
         <f t="shared" si="29"/>
-        <v>5033702032.7601109</v>
+        <v>4480651228.2163744</v>
       </c>
       <c r="K70" s="112">
         <f t="shared" si="29"/>
-        <v>4140178832.475697</v>
+        <v>4057237233.8891549</v>
       </c>
       <c r="L70" s="112">
         <f t="shared" si="29"/>
-        <v>3918056107.0978074</v>
+        <v>3840550219.9158988</v>
       </c>
       <c r="M70" s="112">
         <f t="shared" si="29"/>
-        <v>3661296272.3870931</v>
+        <v>3589615407.5913453</v>
       </c>
       <c r="N70" s="112">
         <f t="shared" si="29"/>
@@ -21320,7 +21204,7 @@
       </c>
       <c r="C71" s="148">
         <f>ABS(SUM(D70:N70)/C63)</f>
-        <v>1.9212144874307431</v>
+        <v>1.7673185297605354</v>
       </c>
       <c r="D71" s="120"/>
       <c r="E71" s="120"/>
@@ -21339,43 +21223,43 @@
       </c>
       <c r="D74" s="116">
         <f t="shared" ref="D74:M74" si="30">D50/D44</f>
-        <v>8.202013167475429E-2</v>
+        <v>7.8667503545430714E-2</v>
       </c>
       <c r="E74" s="116">
         <f t="shared" si="30"/>
-        <v>0.11414362108832844</v>
+        <v>0.10772673750801937</v>
       </c>
       <c r="F74" s="116">
         <f t="shared" si="30"/>
-        <v>0.15883169806412556</v>
+        <v>0.14724948896655957</v>
       </c>
       <c r="G74" s="116">
         <f t="shared" si="30"/>
-        <v>0.46613902892577025</v>
+        <v>0.39235942582785105</v>
       </c>
       <c r="H74" s="116">
         <f t="shared" si="30"/>
-        <v>0.63039466851680814</v>
+        <v>0.50651330545450712</v>
       </c>
       <c r="I74" s="116">
         <f t="shared" si="30"/>
-        <v>0.86660100122342776</v>
+        <v>0.65457408526695493</v>
       </c>
       <c r="J74" s="116">
         <f t="shared" si="30"/>
-        <v>4.0951245413380768</v>
+        <v>1.7494315449526701</v>
       </c>
       <c r="K74" s="116">
         <f t="shared" si="30"/>
-        <v>9.1035835453412357</v>
+        <v>2.3322086570193252</v>
       </c>
       <c r="L74" s="116">
         <f t="shared" si="30"/>
-        <v>1380.0464320103906</v>
+        <v>3.2071396825892409</v>
       </c>
       <c r="M74" s="116">
         <f t="shared" si="30"/>
-        <v>-13.347001790269113</v>
+        <v>4.3713917745414212</v>
       </c>
     </row>
     <row r="75" spans="2:14" ht="13" x14ac:dyDescent="0.15">
@@ -21429,43 +21313,43 @@
       </c>
       <c r="D76" s="116">
         <f t="shared" ref="D76:M76" si="32">D25/D15</f>
-        <v>0.17509397974353896</v>
+        <v>0.18009397974353897</v>
       </c>
       <c r="E76" s="116">
         <f t="shared" si="32"/>
-        <v>0.20528760328783785</v>
+        <v>0.21028760328783785</v>
       </c>
       <c r="F76" s="116">
         <f t="shared" si="32"/>
-        <v>0.23411579490539022</v>
+        <v>0.23911579490539023</v>
       </c>
       <c r="G76" s="116">
         <f t="shared" si="32"/>
-        <v>0.33770851307717953</v>
+        <v>0.34270851307717953</v>
       </c>
       <c r="H76" s="116">
         <f t="shared" si="32"/>
-        <v>0.35625719405252576</v>
+        <v>0.36125719405252582</v>
       </c>
       <c r="I76" s="116">
         <f t="shared" si="32"/>
-        <v>0.37348276417762305</v>
+        <v>0.37848276417762305</v>
       </c>
       <c r="J76" s="116">
         <f t="shared" si="32"/>
-        <v>0.43845655080397794</v>
+        <v>0.44345655080397789</v>
       </c>
       <c r="K76" s="116">
         <f t="shared" si="32"/>
-        <v>0.44989436752452061</v>
+        <v>0.45489436752452056</v>
       </c>
       <c r="L76" s="116">
         <f t="shared" si="32"/>
-        <v>0.46068942582279493</v>
+        <v>0.46568942582279493</v>
       </c>
       <c r="M76" s="116">
         <f t="shared" si="32"/>
-        <v>0.47087176406505388</v>
+        <v>0.47587176406505383</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="13" x14ac:dyDescent="0.15">
@@ -21474,43 +21358,43 @@
       </c>
       <c r="D77" s="116">
         <f t="shared" ref="D77:M77" si="33">D31/D15</f>
-        <v>0.28598565990150077</v>
+        <v>0.29098565990150083</v>
       </c>
       <c r="E77" s="116">
         <f t="shared" si="33"/>
-        <v>0.30412999992601886</v>
+        <v>0.30912999992601886</v>
       </c>
       <c r="F77" s="116">
         <f t="shared" si="33"/>
-        <v>0.32139354106626999</v>
+        <v>0.32639354106627</v>
       </c>
       <c r="G77" s="116">
         <f t="shared" si="33"/>
-        <v>0.38921129432330981</v>
+        <v>0.39421129432330981</v>
       </c>
       <c r="H77" s="116">
         <f t="shared" si="33"/>
-        <v>0.40193504445910783</v>
+        <v>0.40693504445910789</v>
       </c>
       <c r="I77" s="116">
         <f t="shared" si="33"/>
-        <v>0.4140688830420664</v>
+        <v>0.41906888304206641</v>
       </c>
       <c r="J77" s="116">
         <f t="shared" si="33"/>
-        <v>0.46016016424651945</v>
+        <v>0.4651601642465194</v>
       </c>
       <c r="K77" s="116">
         <f t="shared" si="33"/>
-        <v>0.46924427729276291</v>
+        <v>0.47424427729276286</v>
       </c>
       <c r="L77" s="116">
         <f t="shared" si="33"/>
-        <v>0.47793029459577602</v>
+        <v>0.48293029459577602</v>
       </c>
       <c r="M77" s="116">
         <f t="shared" si="33"/>
-        <v>0.48623636876989818</v>
+        <v>0.49123636876989818</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="13" x14ac:dyDescent="0.15">
@@ -21519,43 +21403,43 @@
       </c>
       <c r="D78" s="116">
         <f t="shared" ref="D78:M78" si="34">D37/D15</f>
-        <v>3.1985083584323407E-2</v>
+        <v>0.13243450016732672</v>
       </c>
       <c r="E78" s="116">
         <f t="shared" si="34"/>
-        <v>3.3922753386172844E-2</v>
+        <v>0.13372628003522632</v>
       </c>
       <c r="F78" s="116">
         <f t="shared" si="34"/>
-        <v>2.0441520809219516E-2</v>
+        <v>0.1178735307293779</v>
       </c>
       <c r="G78" s="116">
         <f t="shared" si="34"/>
-        <v>-4.4249210369525796E-2</v>
+        <v>5.2584736283205251E-2</v>
       </c>
       <c r="H78" s="116">
         <f t="shared" si="34"/>
-        <v>-5.5726873590163206E-2</v>
+        <v>4.0531578220326409E-2</v>
       </c>
       <c r="I78" s="116">
         <f t="shared" si="34"/>
-        <v>-6.5709447559817294E-2</v>
+        <v>2.9995226194930547E-2</v>
       </c>
       <c r="J78" s="116">
         <f t="shared" si="34"/>
-        <v>-9.9271126657816039E-2</v>
+        <v>-4.0993336736875746E-3</v>
       </c>
       <c r="K78" s="116">
         <f t="shared" si="34"/>
-        <v>-0.10409726196330163</v>
+        <v>-9.4382410414673365E-3</v>
       </c>
       <c r="L78" s="116">
         <f t="shared" si="34"/>
-        <v>-0.10838548045355795</v>
+        <v>-1.4219881704874609E-2</v>
       </c>
       <c r="M78" s="116">
         <f t="shared" si="34"/>
-        <v>-0.10833467404417094</v>
+        <v>-1.4643877763991375E-2</v>
       </c>
     </row>
     <row r="80" spans="2:14" ht="13" x14ac:dyDescent="0.15">
@@ -21564,43 +21448,43 @@
       </c>
       <c r="D80" s="118">
         <f>D77/D78</f>
-        <v>8.9412197141066283</v>
+        <v>2.1972043503305394</v>
       </c>
       <c r="E80" s="118">
         <f t="shared" ref="E80:M80" si="35">E77/E78</f>
-        <v>8.9653689505635601</v>
+        <v>2.3116622988733964</v>
       </c>
       <c r="F80" s="118">
         <f t="shared" si="35"/>
-        <v>15.722584638678908</v>
+        <v>2.769014714725281</v>
       </c>
       <c r="G80" s="118">
         <f t="shared" si="35"/>
-        <v>-8.7958924254919051</v>
+        <v>7.4966867229343661</v>
       </c>
       <c r="H80" s="118">
         <f t="shared" si="35"/>
-        <v>-7.2125891614715769</v>
+        <v>10.039950634220105</v>
       </c>
       <c r="I80" s="118">
         <f t="shared" si="35"/>
-        <v>-6.3015121633023474</v>
+        <v>13.97118595868074</v>
       </c>
       <c r="J80" s="118">
         <f t="shared" si="35"/>
-        <v>-4.6353877480677212</v>
+        <v>-113.47213993148365</v>
       </c>
       <c r="K80" s="118">
         <f t="shared" si="35"/>
-        <v>-4.5077485079116677</v>
+        <v>-50.247103799230104</v>
       </c>
       <c r="L80" s="118">
         <f t="shared" si="35"/>
-        <v>-4.4095416894937713</v>
+        <v>-33.961625322820119</v>
       </c>
       <c r="M80" s="118">
         <f t="shared" si="35"/>
-        <v>-4.4882801656988107</v>
+        <v>-33.545511420330612</v>
       </c>
     </row>
     <row r="81" spans="2:13" ht="13" x14ac:dyDescent="0.15">
@@ -21609,43 +21493,43 @@
       </c>
       <c r="D81" s="119">
         <f>(D74-WACC!$B$18)*'Breakeven Precio'!D44</f>
-        <v>-1646634310.860882</v>
+        <v>-1814414284.0598049</v>
       </c>
       <c r="E81" s="119">
         <f>(E74-WACC!$B$18)*'Breakeven Precio'!E44</f>
-        <v>-1146122499.905287</v>
+        <v>-1332916890.2626889</v>
       </c>
       <c r="F81" s="119">
         <f>(F74-WACC!$B$18)*'Breakeven Precio'!F44</f>
-        <v>-534073248.10119808</v>
+        <v>-739636491.69440186</v>
       </c>
       <c r="G81" s="119">
         <f>(G74-WACC!$B$18)*'Breakeven Precio'!G44</f>
-        <v>2589226136.666832</v>
+        <v>2243430673.0381074</v>
       </c>
       <c r="H81" s="119">
         <f>(H74-WACC!$B$18)*'Breakeven Precio'!H44</f>
-        <v>3703634392.716207</v>
+        <v>3316516170.0257106</v>
       </c>
       <c r="I81" s="119">
         <f>(I74-WACC!$B$18)*'Breakeven Precio'!I44</f>
-        <v>4939194420.079072</v>
+        <v>4506514232.1197233</v>
       </c>
       <c r="J81" s="119">
         <f>(J74-WACC!$B$18)*'Breakeven Precio'!J44</f>
-        <v>13473230227.876867</v>
+        <v>12669516525.328978</v>
       </c>
       <c r="K81" s="119">
         <f>(K74-WACC!$B$18)*'Breakeven Precio'!K44</f>
-        <v>15953319629.02249</v>
+        <v>15057677178.953543</v>
       </c>
       <c r="L81" s="119">
         <f>(L74-WACC!$B$18)*'Breakeven Precio'!L44</f>
-        <v>18751741617.672314</v>
+        <v>17752837796.177536</v>
       </c>
       <c r="M81" s="119">
         <f>(M74-WACC!$B$18)*'Breakeven Precio'!M44</f>
-        <v>21838460864.864025</v>
+        <v>20724378308.188862</v>
       </c>
     </row>
     <row r="86" spans="2:13" ht="13" x14ac:dyDescent="0.15">
@@ -22022,7 +21906,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD018FB3-B0AA-4047-8EFD-11093237ECF3}">
-  <dimension ref="A4:K16"/>
+  <dimension ref="A4:K18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
@@ -22371,9 +22255,18 @@
       <c r="A16" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="B16" s="154">
+      <c r="B16" s="21">
         <f>SUM(B14:K14)</f>
         <v>26880322416.543213</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="31" t="s">
+        <v>374</v>
+      </c>
+      <c r="B18" s="21">
+        <f>B10</f>
+        <v>2800000000</v>
       </c>
     </row>
   </sheetData>
@@ -22670,10 +22563,10 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="159" t="s">
+      <c r="A26" s="156" t="s">
         <v>136</v>
       </c>
-      <c r="B26" s="159"/>
+      <c r="B26" s="156"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="43" t="s">
@@ -22845,22 +22738,22 @@
       <c r="D42" s="55"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A44" s="160" t="s">
+      <c r="A44" s="157" t="s">
         <v>167</v>
       </c>
-      <c r="B44" s="160"/>
-      <c r="C44" s="160"/>
-      <c r="D44" s="160"/>
-      <c r="E44" s="160"/>
-      <c r="F44" s="160"/>
-      <c r="G44" s="160"/>
-      <c r="I44" s="161"/>
-      <c r="J44" s="161"/>
-      <c r="K44" s="161"/>
-      <c r="L44" s="161"/>
-      <c r="M44" s="161"/>
-      <c r="N44" s="161"/>
-      <c r="O44" s="161"/>
+      <c r="B44" s="157"/>
+      <c r="C44" s="157"/>
+      <c r="D44" s="157"/>
+      <c r="E44" s="157"/>
+      <c r="F44" s="157"/>
+      <c r="G44" s="157"/>
+      <c r="I44" s="158"/>
+      <c r="J44" s="158"/>
+      <c r="K44" s="158"/>
+      <c r="L44" s="158"/>
+      <c r="M44" s="158"/>
+      <c r="N44" s="158"/>
+      <c r="O44" s="158"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
@@ -24185,15 +24078,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="163" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
+      <c r="G1" s="163"/>
       <c r="P1" s="63" t="s">
         <v>189</v>
       </c>
@@ -24205,17 +24098,17 @@
       <c r="V1" s="63"/>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A3" s="163" t="s">
+      <c r="A3" s="164" t="s">
         <v>190</v>
       </c>
-      <c r="B3" s="163"/>
+      <c r="B3" s="164"/>
       <c r="D3" s="64" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="164" t="s">
+      <c r="P3" s="159" t="s">
         <v>190</v>
       </c>
-      <c r="Q3" s="164"/>
+      <c r="Q3" s="159"/>
       <c r="S3" s="64" t="s">
         <v>191</v>
       </c>
@@ -24480,13 +24373,13 @@
         <f>AG9*AG10</f>
         <v>682.10548276114309</v>
       </c>
-      <c r="AM13" s="166" t="s">
+      <c r="AM13" s="161" t="s">
         <v>233</v>
       </c>
-      <c r="AN13" s="167"/>
-      <c r="AO13" s="167"/>
-      <c r="AP13" s="167"/>
-      <c r="AQ13" s="167"/>
+      <c r="AN13" s="162"/>
+      <c r="AO13" s="162"/>
+      <c r="AP13" s="162"/>
+      <c r="AQ13" s="162"/>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -24572,22 +24465,22 @@
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A17" s="163" t="s">
+      <c r="A17" s="164" t="s">
         <v>243</v>
       </c>
-      <c r="B17" s="163"/>
-      <c r="C17" s="163"/>
-      <c r="D17" s="163"/>
-      <c r="E17" s="163"/>
-      <c r="F17" s="163"/>
-      <c r="G17" s="163"/>
-      <c r="I17" s="163" t="s">
+      <c r="B17" s="164"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="164"/>
+      <c r="E17" s="164"/>
+      <c r="F17" s="164"/>
+      <c r="G17" s="164"/>
+      <c r="I17" s="164" t="s">
         <v>233</v>
       </c>
-      <c r="J17" s="163"/>
-      <c r="K17" s="163"/>
-      <c r="L17" s="163"/>
-      <c r="M17" s="163"/>
+      <c r="J17" s="164"/>
+      <c r="K17" s="164"/>
+      <c r="L17" s="164"/>
+      <c r="M17" s="164"/>
       <c r="P17" s="64" t="s">
         <v>244</v>
       </c>
@@ -24668,22 +24561,22 @@
       <c r="M19" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="P19" s="165" t="s">
+      <c r="P19" s="160" t="s">
         <v>243</v>
       </c>
-      <c r="Q19" s="165"/>
-      <c r="R19" s="165"/>
-      <c r="S19" s="165"/>
-      <c r="T19" s="165"/>
-      <c r="U19" s="165"/>
-      <c r="V19" s="165"/>
-      <c r="X19" s="165" t="s">
+      <c r="Q19" s="160"/>
+      <c r="R19" s="160"/>
+      <c r="S19" s="160"/>
+      <c r="T19" s="160"/>
+      <c r="U19" s="160"/>
+      <c r="V19" s="160"/>
+      <c r="X19" s="160" t="s">
         <v>233</v>
       </c>
-      <c r="Y19" s="165"/>
-      <c r="Z19" s="165"/>
-      <c r="AA19" s="165"/>
-      <c r="AB19" s="165"/>
+      <c r="Y19" s="160"/>
+      <c r="Z19" s="160"/>
+      <c r="AA19" s="160"/>
+      <c r="AB19" s="160"/>
       <c r="AF19" s="72" t="s">
         <v>249</v>
       </c>
@@ -26141,13 +26034,13 @@
         <f t="shared" si="5"/>
         <v>6510</v>
       </c>
-      <c r="I32" s="163" t="s">
+      <c r="I32" s="164" t="s">
         <v>253</v>
       </c>
-      <c r="J32" s="163"/>
-      <c r="K32" s="163"/>
-      <c r="L32" s="163"/>
-      <c r="M32" s="163"/>
+      <c r="J32" s="164"/>
+      <c r="K32" s="164"/>
+      <c r="L32" s="164"/>
+      <c r="M32" s="164"/>
       <c r="P32" s="79">
         <v>11</v>
       </c>
@@ -28219,6 +28112,7 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="I32:M32"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P19:V19"/>
     <mergeCell ref="X19:AB19"/>
@@ -28227,7 +28121,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="I17:M17"/>
-    <mergeCell ref="I32:M32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D9" r:id="rId1" xr:uid="{FE201A1B-6C8C-4A0F-801E-10AC66BA1A74}"/>
